--- a/site/reversal_signals.xlsx
+++ b/site/reversal_signals.xlsx
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.511</v>
+        <v>0.669</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>8</v>
@@ -596,10 +596,10 @@
         <v>8</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>86.98999999999999</v>
+        <v>86.78</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>11.06</v>
+        <v>10.8</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>14</v>
@@ -608,11 +608,11 @@
         <v>4</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>75.59999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 50% of range | Time count: TD setup 13 | Fib 61.8% retrace @ 87.58 | Volume POC @ 88.76 | RSI overbought (76) | Tagged upper Bollinger band | Extended 5.2 ATR from 20 EMA | Volume 1.9x average</t>
+          <t>Topping tail (new high rejected), tail 54% of range | Time count: TD setup 13 | Fib 61.8% retrace @ 87.58 | Volume POC @ 88.76 | RSI overbought (75) | Tagged upper Bollinger band | Extended 5.2 ATR from 20 EMA | Volume 1.9x average</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.835</v>
+        <v>0.892</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>7.75</v>
@@ -652,10 +652,10 @@
         <v>7</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>494.1</v>
+        <v>494.58</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>0.88</v>
+        <v>0.97</v>
       </c>
       <c r="I3" s="7" t="n">
         <v>1</v>
@@ -664,7 +664,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>44.8</v>
+        <v>45.2</v>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.712</v>
+        <v>0.765</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>7.5</v>
@@ -708,10 +708,10 @@
         <v>6</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>54.6</v>
+        <v>54.55</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>-2.89</v>
+        <v>-2.97</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>-1</v>
@@ -720,7 +720,7 @@
         <v>-2</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>54.4</v>
+        <v>54.1</v>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
@@ -749,13 +749,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.972</v>
+        <v>0.97</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>7.25</v>
@@ -764,10 +764,10 @@
         <v>6</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>33.33</v>
+        <v>33.36</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>-2.36</v>
+        <v>-2.26</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>13</v>
@@ -776,7 +776,7 @@
         <v>-1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>69</v>
+        <v>69.3</v>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.603</v>
+        <v>0.589</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>7</v>
@@ -820,10 +820,10 @@
         <v>7</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>114.37</v>
+        <v>114.39</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1</v>
@@ -832,7 +832,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>71.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>7</v>
@@ -876,10 +876,10 @@
         <v>7</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>419.39</v>
+        <v>419.14</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>13</v>
@@ -888,7 +888,7 @@
         <v>4</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -923,32 +923,32 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.596</v>
+        <v>0.823</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1026.45</v>
+        <v>42.06</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1.86</v>
+        <v>1.14</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>55.7</v>
+        <v>70.2</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 65% of range | Fib 78.6% retrace @ 1078.54 | Major pivot zone (8 touches, 1.8x vol) @ 1043.32 | High-volume node @ 1073.68 | Trendline (falling resistance) @ 1028.20 | Tagged upper Bollinger band</t>
+          <t>Topping tail (new high rejected), tail 78% of range | Time count: TD setup 20 | Prior pivot (2 touches, 1.1x vol) @ 42.24 | High-volume node @ 42.32 | RSI overbought (70) | Extended 3.2 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -973,13 +973,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.649</v>
+        <v>0.753</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>6.5</v>
@@ -988,10 +988,10 @@
         <v>6</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>306.12</v>
+        <v>305.7</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.51</v>
+        <v>0.37</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>11</v>
@@ -1000,11 +1000,11 @@
         <v>1</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>59.1</v>
+        <v>58.7</v>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 55% of range | Time count: TD setup 10 | Fib 50.0% retrace @ 310.98 | Prior pivot (1 touch, 1.4x vol) @ 312.88 | High-volume node @ 311.94 | Tagged upper Bollinger band</t>
+          <t>Topping tail (new high rejected), tail 59% of range | Time count: TD setup 10 | Fib 50.0% retrace @ 310.98 | Prior pivot (1 touch, 1.4x vol) @ 312.88 | High-volume node @ 311.94 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.774</v>
+        <v>0.879</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>6.5</v>
@@ -1044,10 +1044,10 @@
         <v>6</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>562.5700000000001</v>
+        <v>561.47</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>16</v>
@@ -1056,7 +1056,7 @@
         <v>2</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.987</v>
+        <v>0.993</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>6.5</v>
@@ -1100,10 +1100,10 @@
         <v>6</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>88.53</v>
+        <v>88.5</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>-2.11</v>
+        <v>-2.14</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>-2</v>
@@ -1112,11 +1112,11 @@
         <v>-1</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>Bearish engulfing | Fib 78.6% retrace @ 92.43 | Major pivot zone (14 touches, 2.7x vol) @ 92.79 | Volume POC @ 91.53 | Bearish RSI divergence (51) | Volume 1.8x average</t>
+          <t>Bearish engulfing | Fib 78.6% retrace @ 92.43 | Major pivot zone (14 touches, 2.7x vol) @ 92.79 | Volume POC @ 91.53 | Bearish RSI divergence (51) | Volume 1.7x average</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>DOV</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1141,102 +1141,102 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>At risk</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.985</v>
+        <v>0.326</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>208.99</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I12" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G12" s="2" t="n">
-        <v>501.58</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="I12" s="2" t="n">
+      <c r="J12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | Fib 50.0% retrace @ 208.52 | Major pivot zone (3 touches, 1.6x vol) @ 209.50 | RSI overbought (73) | Tagged upper Bollinger band | Extended 3.1 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>LIN</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>502.02</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="I13" s="2" t="n">
         <v>-2</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="J13" s="2" t="n">
         <v>-2</v>
       </c>
-      <c r="K12" s="2" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>Bearish engulfing | Fib 61.8% retrace @ 511.18 | Major pivot zone (3 touches, 1.4x vol) @ 505.57 | High-volume node @ 505.80 | Bearish RSI divergence (59)</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>0.877</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>427.78</v>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>-4.61</v>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J13" s="7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="L13" s="10" t="inlineStr">
-        <is>
-          <t>Bottoming tail (new low rejected), tail 59% of range | Major pivot zone (3 touches, 1.5x vol) @ 414.52 | High-volume node @ 423.56 | Tagged lower Bollinger band | Extended 2.9 ATR from 20 EMA | Volume 1.6x average</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="K13" s="2" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>Bearish engulfing | Fib 61.8% retrace @ 511.18 | Major pivot zone (3 touches, 1.4x vol) @ 505.57 | High-volume node @ 505.80 | Bearish RSI divergence (60)</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1245,7 +1245,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -1253,38 +1253,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.602</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>6</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>129.9</v>
+        <v>428.79</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>-3.56</v>
+        <v>-4.39</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>31.1</v>
+        <v>37.1</v>
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>Bottoming tail (new low rejected), tail 59% of range | Time count: 9 down bars since the last up bar | Prior pivot (2 touches, 1.7x vol) @ 128.64 | Tagged lower Bollinger band | Extended 2.6 ATR from 20 EMA | Volume 2.3x average</t>
+          <t>Bottoming tail (new low rejected), tail 59% of range | Major pivot zone (3 touches, 1.5x vol) @ 414.52 | High-volume node @ 423.56 | Tagged lower Bollinger band | Extended 2.9 ATR from 20 EMA | Volume 1.6x average</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
@@ -1299,56 +1299,56 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>APP</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E15" s="7" t="n">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>EQIX</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>5.75</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G15" s="7" t="n">
-        <v>256.89</v>
-      </c>
-      <c r="H15" s="7" t="n">
-        <v>-1.18</v>
-      </c>
-      <c r="I15" s="7" t="n">
-        <v>-7</v>
-      </c>
-      <c r="J15" s="7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="L15" s="10" t="inlineStr">
-        <is>
-          <t>Bottoming tail (new low rejected), tail 53% of range | Time count: 9 down bars since the last up bar | Trendline (falling support) @ 253.65 | Bullish RSI divergence (35) | Tagged lower Bollinger band</t>
-        </is>
-      </c>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="G15" s="2" t="n">
+        <v>1028.51</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 65% of range | Fib 78.6% retrace @ 1078.54 | Major pivot zone (8 touches, 1.8x vol) @ 1043.32 | High-volume node @ 1073.68 | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1357,7 +1357,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -1371,96 +1371,96 @@
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.775</v>
+        <v>0.642</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>5.75</v>
       </c>
       <c r="F16" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>130.04</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>-3.46</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="L16" s="10" t="inlineStr">
+        <is>
+          <t>Bottoming tail (new low rejected), tail 60% of range | Time count: 9 down bars since the last up bar | Prior pivot (2 touches, 1.7x vol) @ 128.64 | Tagged lower Bollinger band | Extended 2.6 ATR from 20 EMA | Volume 2.3x average</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>UHS</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="F17" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="7" t="n">
-        <v>175.69</v>
-      </c>
-      <c r="H16" s="7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="I16" s="7" t="n">
+      <c r="G17" s="7" t="n">
+        <v>175.56</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I17" s="7" t="n">
         <v>-3</v>
       </c>
-      <c r="J16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="L16" s="10" t="inlineStr">
+      <c r="J17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
         <is>
           <t>Bottoming tail, tail 59% of range | Fib 38.2% retrace @ 171.84 | Major pivot zone (4 touches, 1.5x vol) @ 174.58 | High-volume node @ 168.36 | Tagged lower Bollinger band</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N16" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>LLY</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>0.642</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>1365.57</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 55% of range | Fib 1.27 extension @ 1424.82 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 1.6x average</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N17" s="6" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1469,7 +1469,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1477,38 +1477,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.845</v>
+        <v>0.674</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>5.5</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>181.45</v>
+        <v>1365.03</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1.15</v>
+        <v>5.96</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>70.3</v>
+        <v>73.7</v>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 54% of range | Time count: TD setup 15 | Prior pivot (1 touch, 1.7x vol) @ 185.27 | RSI overbought (70) | Extended 3.4 ATR from 20 EMA</t>
+          <t>Topping tail (new high rejected), tail 55% of range | Fib 1.27 extension @ 1424.82 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 1.6x average</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1533,13 +1533,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.902</v>
+        <v>0.793</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>5.5</v>
@@ -1548,23 +1548,23 @@
         <v>5</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>41.99</v>
+        <v>181.65</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.97</v>
+        <v>1.26</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>69.8</v>
+        <v>70.5</v>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 84% of range | Time count: TD setup 20 | Prior pivot (2 touches, 1.1x vol) @ 42.24 | High-volume node @ 42.32 | Extended 3.2 ATR from 20 EMA</t>
+          <t>Topping tail (new high rejected), tail 54% of range | Time count: TD setup 15 | Prior pivot (1 touch, 1.7x vol) @ 185.27 | RSI overbought (70) | Extended 3.4 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.866</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>5.5</v>
@@ -1604,10 +1604,10 @@
         <v>5</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>141.04</v>
+        <v>140.91</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1.03</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>16</v>
@@ -1616,7 +1616,7 @@
         <v>1</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>73.09999999999999</v>
+        <v>73</v>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.99</v>
+        <v>0.992</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>5.5</v>
@@ -1660,10 +1660,10 @@
         <v>5</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>105.18</v>
+        <v>105.25</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.28</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>8</v>
@@ -1672,7 +1672,7 @@
         <v>-1</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>73.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.759</v>
+        <v>0.799</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>5.5</v>
@@ -1716,10 +1716,10 @@
         <v>5</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>340.98</v>
+        <v>340.88</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>1</v>
@@ -1747,112 +1747,112 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>RVTY</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>165.09</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>Topping tail, tail 47% of range | Time count: 7 up bars since the last down bar | Prior pivot (1 touch, 1.4x vol) @ 166.18 | RSI overbought (72) | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D23" s="9" t="n">
-        <v>0.622</v>
-      </c>
-      <c r="E23" s="7" t="n">
+      <c r="D24" s="9" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="E24" s="7" t="n">
         <v>5.5</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="F24" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G23" s="7" t="n">
-        <v>65.54000000000001</v>
-      </c>
-      <c r="H23" s="7" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="I23" s="7" t="n">
+      <c r="G24" s="7" t="n">
+        <v>65.47</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I24" s="7" t="n">
         <v>-12</v>
       </c>
-      <c r="J23" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="L23" s="10" t="inlineStr">
+      <c r="J24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
         <is>
           <t>Bottoming tail (new low rejected), tail 74% of range | Time count: TD setup 11 | Prior pivot (1 touch, 1.4x vol) @ 65.41 | Trendline (falling support) @ 64.82 | Tagged lower Bollinger band</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N23" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>BLK</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>0.826</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>1168.41</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 73% of range | Time count: 7 up bars since the last down bar | Prior pivot (2 touches, 1.0x vol) @ 1180.97 | Tagged upper Bollinger band | Extended 2.5 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N24" s="6" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N24" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1861,7 +1861,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TFC</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1869,13 +1869,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.4</v>
+        <v>0.796</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>5.25</v>
@@ -1884,23 +1884,23 @@
         <v>5</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>49.26</v>
+        <v>1169.42</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1.72</v>
+        <v>1</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>61.3</v>
+        <v>66.3</v>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>Doji (indecision at extreme) | Fib 50.0% retrace @ 49.37 | Major pivot zone (7 touches, 1.4x vol) @ 49.39 | High-volume node @ 49.73 | Tagged upper Bollinger band</t>
+          <t>Topping tail (new high rejected), tail 73% of range | Time count: 7 up bars since the last down bar | Prior pivot (2 touches, 1.0x vol) @ 1180.97 | Tagged upper Bollinger band | Extended 2.5 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.339</v>
+        <v>0.372</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>5</v>
@@ -1940,10 +1940,10 @@
         <v>5</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>375.43</v>
+        <v>375.08</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0.39</v>
+        <v>0.29</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>9</v>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>Doji (indecision at extreme) | Time count: 8 up bars since the last down bar | RSI overbought (81) | Tagged upper Bollinger band | Extended 3.8 ATR from 20 EMA</t>
+          <t>Doji (indecision at extreme) | Time count: 8 up bars since the last down bar | RSI overbought (80) | Tagged upper Bollinger band | Extended 3.8 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -1973,7 +1973,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1987,32 +1987,32 @@
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.466</v>
+        <v>0.912</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>165.29</v>
+        <v>62.57</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>-0.02</v>
+        <v>-5.71</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>8</v>
+        <v>-3</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>72.7</v>
+        <v>46.9</v>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>Doji (indecision at extreme) | Time count: 7 up bars since the last down bar | Prior pivot (1 touch, 1.4x vol) @ 166.18 | RSI overbought (73) | Tagged upper Bollinger band</t>
+          <t>Topping tail, tail 71% of range | Major pivot zone (4 touches, 1.8x vol) @ 65.08 | High-volume node @ 63.60 | Trendline (rising resistance) @ 64.96</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>KEY</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.908</v>
+        <v>0.602</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>5</v>
@@ -2052,23 +2052,23 @@
         <v>4</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>62.52</v>
+        <v>21.45</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>-5.79</v>
+        <v>1.2</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>46.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>Topping tail, tail 71% of range | Major pivot zone (4 touches, 1.8x vol) @ 65.08 | High-volume node @ 63.60 | Trendline (rising resistance) @ 64.96</t>
+          <t>Topping tail (new high rejected), tail 52% of range | Fib 50.0% retrace @ 21.65 | Major pivot zone (3 touches, 1.3x vol) @ 21.45 | High-volume node @ 21.64</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>KEY</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.595</v>
+        <v>0.548</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>5</v>
@@ -2108,23 +2108,23 @@
         <v>4</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>21.45</v>
+        <v>82</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>64.59999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 52% of range | Fib 50.0% retrace @ 21.65 | Major pivot zone (3 touches, 1.3x vol) @ 21.45 | High-volume node @ 21.64</t>
+          <t>Topping tail (new high rejected), tail 78% of range | Fib 38.2% retrace @ 82.04 | Major pivot zone (3 touches, 2.4x vol) @ 82.62 | Volume POC @ 82.88</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2139,14 +2139,14 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>NEE</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>bearish</t>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>BF-B</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>bullish</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2154,41 +2154,41 @@
           <t>Developing</t>
         </is>
       </c>
-      <c r="D30" s="4" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E30" s="2" t="n">
+      <c r="D30" s="9" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="E30" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="F30" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G30" s="2" t="n">
-        <v>81.95999999999999</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="I30" s="2" t="n">
+      <c r="G30" s="7" t="n">
+        <v>27.99</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I30" s="7" t="n">
         <v>-2</v>
       </c>
-      <c r="J30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 82% of range | Fib 38.2% retrace @ 82.04 | Major pivot zone (3 touches, 2.4x vol) @ 82.62 | Volume POC @ 82.88</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N30" s="6" t="inlineStr">
+      <c r="J30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="7" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="L30" s="10" t="inlineStr">
+        <is>
+          <t>Bottoming tail (new low rejected), tail 60% of range | Fib 50.0% retrace @ 27.22 | Major pivot zone (4 touches, 4.9x vol) @ 27.85 | High-volume node @ 27.83</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N30" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2197,7 +2197,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -2205,38 +2205,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>97.84</v>
+        <v>92.95</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>-2.94</v>
+        <v>1.37</v>
       </c>
       <c r="I31" s="7" t="n">
         <v>-4</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>29.5</v>
+        <v>56.8</v>
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>Doji (indecision at extreme) | Time count: 11 down bars since the last up bar | Prior pivot (2 touches, 1.0x vol) @ 95.80 | RSI oversold (29) | Tagged lower Bollinger band</t>
+          <t>Bottoming tail, tail 98% of range | Fib 38.2% retrace @ 92.09 | Major pivot zone (4 touches, 1.2x vol) @ 91.65 | High-volume node @ 91.89</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>BF-B</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -2261,13 +2261,13 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.66</v>
+        <v>0.988</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>5</v>
@@ -2276,23 +2276,23 @@
         <v>4</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>27.99</v>
+        <v>238.96</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>0.85</v>
+        <v>0.18</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>52.2</v>
+        <v>60.4</v>
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
-          <t>Bottoming tail (new low rejected), tail 59% of range | Fib 50.0% retrace @ 27.22 | Major pivot zone (4 touches, 4.9x vol) @ 27.85 | High-volume node @ 27.83</t>
+          <t>Bottoming tail, tail 77% of range | Major pivot zone (2 touches, 2.1x vol) @ 229.88 | High-volume node @ 233.72 | Trendline (rising support) @ 236.19</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -2307,112 +2307,112 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="n">
-        <v>0.874</v>
-      </c>
-      <c r="E33" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F33" s="7" t="n">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>COF</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F33" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G33" s="7" t="n">
-        <v>92.81999999999999</v>
-      </c>
-      <c r="H33" s="7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="I33" s="7" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J33" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="L33" s="10" t="inlineStr">
-        <is>
-          <t>Bottoming tail, tail 91% of range | Fib 38.2% retrace @ 92.09 | Major pivot zone (4 touches, 1.2x vol) @ 91.65 | High-volume node @ 91.89</t>
-        </is>
-      </c>
-      <c r="M33" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N33" s="11" t="inlineStr">
+      <c r="G33" s="2" t="n">
+        <v>208.11</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 61% of range | Major pivot zone (8 touches, 1.8x vol) @ 210.88 | Trendline (falling resistance) @ 209.74 | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N33" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>IEX</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F34" s="7" t="n">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>HBAN</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F34" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G34" s="7" t="n">
-        <v>238.94</v>
-      </c>
-      <c r="H34" s="7" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="I34" s="7" t="n">
+      <c r="G34" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J34" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="L34" s="10" t="inlineStr">
-        <is>
-          <t>Bottoming tail, tail 81% of range | Major pivot zone (2 touches, 2.1x vol) @ 229.88 | High-volume node @ 233.72 | Trendline (rising support) @ 236.19</t>
-        </is>
-      </c>
-      <c r="M34" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N34" s="11" t="inlineStr">
+      <c r="J34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 59% of range | Time count: 8 up bars since the last down bar | Fib 38.2% retrace @ 16.19 | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N34" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2421,7 +2421,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>IRM</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.59</v>
+        <v>0.668</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>4.75</v>
@@ -2444,23 +2444,23 @@
         <v>4</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>208.21</v>
+        <v>118.11</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>1.63</v>
+        <v>2.11</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>60</v>
+        <v>59.1</v>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 58% of range | Major pivot zone (8 touches, 1.8x vol) @ 210.88 | Trendline (falling resistance) @ 209.74 | Tagged upper Bollinger band</t>
+          <t>Topping tail (new high rejected), tail 64% of range | Fib 50.0% retrace @ 120.42 | Major pivot zone (7 touches, 1.6x vol) @ 118.99 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>HBAN</t>
+          <t>WMB</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>4.75</v>
@@ -2500,23 +2500,23 @@
         <v>4</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>15.91</v>
+        <v>74.87</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>1.34</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>58</v>
+        <v>59.6</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 59% of range | Time count: 8 up bars since the last down bar | Fib 38.2% retrace @ 16.19 | Tagged upper Bollinger band</t>
+          <t>Topping tail (new high rejected), tail 72% of range | Fib 78.6% retrace @ 76.45 | Major pivot zone (10 touches, 1.5x vol) @ 75.24 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2531,14 +2531,14 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>IRM</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>bearish</t>
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>bullish</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2546,41 +2546,41 @@
           <t>Developing</t>
         </is>
       </c>
-      <c r="D37" s="4" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E37" s="2" t="n">
+      <c r="D37" s="9" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="E37" s="7" t="n">
         <v>4.75</v>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="F37" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G37" s="2" t="n">
-        <v>118</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 68% of range | Fib 50.0% retrace @ 120.42 | Major pivot zone (7 touches, 1.6x vol) @ 118.99 | Tagged upper Bollinger band</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N37" s="6" t="inlineStr">
+      <c r="G37" s="7" t="n">
+        <v>62.06</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J37" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" s="7" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="L37" s="10" t="inlineStr">
+        <is>
+          <t>Bottoming tail (new low rejected), tail 55% of range | Time count: TD setup 9 | Trendline (falling support) @ 60.70 | Extended 3.0 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N37" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2589,7 +2589,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>WMB</t>
+          <t>BAX</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2597,214 +2597,214 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>-6.85</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>Bearish engulfing | Prior pivot (2 touches, 0.9x vol) @ 25.84 | Bearish RSI divergence (42) | Tagged upper Bollinger band | Volume 2.0x average</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N38" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D38" s="4" t="n">
-        <v>0.764</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="F38" s="2" t="n">
+      <c r="D39" s="4" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F39" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G38" s="2" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I38" s="2" t="n">
+      <c r="G39" s="2" t="n">
+        <v>274.81</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 61% of range | Time count: TD setup 8 | Prior pivot (1 touch, 1.0x vol) @ 281.07 | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N39" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>USB</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 73% of range | Time count: 7 up bars since the last down bar | Prior pivot (1 touch, 0.8x vol) @ 60.89 | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N40" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>MGM</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F41" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="J38" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 72% of range | Fib 78.6% retrace @ 76.45 | Major pivot zone (10 touches, 1.5x vol) @ 75.24 | Tagged upper Bollinger band</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N38" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E39" s="7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="F39" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G39" s="7" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="H39" s="7" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="I39" s="7" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J39" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="L39" s="10" t="inlineStr">
-        <is>
-          <t>Bottoming tail (new low rejected), tail 58% of range | Time count: TD setup 9 | Trendline (falling support) @ 60.70 | Extended 3.0 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M39" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N39" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>TWLO</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E40" s="7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G40" s="7" t="n">
-        <v>240.03</v>
-      </c>
-      <c r="H40" s="7" t="n">
-        <v>-5.41</v>
-      </c>
-      <c r="I40" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J40" s="7" t="n">
-        <v>-3</v>
-      </c>
-      <c r="K40" s="7" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="L40" s="10" t="inlineStr">
-        <is>
-          <t>Bottoming tail (new low rejected), tail 51% of range | Fib 61.8% retrace @ 228.55 | Major pivot zone (3 touches, 1.4x vol) @ 238.69 | Tagged lower Bollinger band</t>
-        </is>
-      </c>
-      <c r="M40" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N40" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>BAX</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>-6.52</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K41" s="2" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>Bearish engulfing | Prior pivot (2 touches, 0.9x vol) @ 25.84 | Bearish RSI divergence (43) | Tagged upper Bollinger band | Volume 2.1x average</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N41" s="6" t="inlineStr">
+      <c r="G41" s="7" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="I41" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="7" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>Bullish engulfing | Bullish RSI divergence (36) | Tagged lower Bollinger band | Extended 2.7 ATR from 20 EMA | Volume 1.9x average</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N41" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2813,7 +2813,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ARES</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2827,32 +2827,32 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>0.52</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>125.91</v>
+        <v>65.08</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>1.69</v>
+        <v>1.25</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>8</v>
+        <v>-2</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>60.8</v>
+        <v>59.2</v>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 51% of range | Time count: 8 up bars since the last down bar | Prior pivot (2 touches, 1.3x vol) @ 129.72 | Tagged upper Bollinger band</t>
+          <t>Topping tail, tail 62% of range | Fib 50.0% retrace @ 65.85 | Prior pivot (2 touches, 1.4x vol) @ 65.45 | High-volume node @ 65.93</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2877,38 +2877,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>At risk</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>0.797</v>
+        <v>0.241</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>274.53</v>
+        <v>119.53</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>1.29</v>
+        <v>0.72</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>62.5</v>
+        <v>88.7</v>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 61% of range | Time count: TD setup 8 | Prior pivot (1 touch, 1.0x vol) @ 281.07 | Tagged upper Bollinger band</t>
+          <t>Doji (indecision at extreme) | Time count: TD setup 24 | RSI overbought (89) | Extended 4.5 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2933,38 +2933,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>At risk</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>0.763</v>
+        <v>0.015</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>60.42</v>
+        <v>222.64</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>60.1</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 73% of range | Time count: 7 up bars since the last down bar | Prior pivot (1 touch, 0.8x vol) @ 60.89 | Tagged upper Bollinger band</t>
+          <t>Doji (indecision at extreme) | Time count: TD setup 11 | Fib 50.0% retrace @ 224.11 | Prior pivot (2 touches, 1.5x vol) @ 221.25</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>MGM</t>
+          <t>SHW</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -2995,32 +2995,32 @@
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1</v>
+        <v>0.927</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>28.55</v>
+        <v>329.02</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>4.69</v>
+        <v>2.56</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="J45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>35.7</v>
+        <v>49.7</v>
       </c>
       <c r="L45" s="10" t="inlineStr">
         <is>
-          <t>Bullish engulfing | Bullish RSI divergence (36) | Tagged lower Bollinger band | Extended 2.7 ATR from 20 EMA | Volume 1.9x average</t>
+          <t>Bottoming tail, tail 92% of range | Fib 61.8% retrace @ 320.56 | Prior pivot (2 touches, 1.5x vol) @ 326.09 | Volume POC @ 320.98</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
@@ -3037,7 +3037,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3045,38 +3045,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>0.888</v>
+        <v>0.704</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>64.97</v>
+        <v>123.36</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>58.7</v>
+        <v>66.3</v>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>Topping tail, tail 62% of range | Fib 50.0% retrace @ 65.85 | Prior pivot (2 touches, 1.4x vol) @ 65.45 | High-volume node @ 65.93</t>
+          <t>Topping tail (new high rejected), tail 68% of range | Prior pivot (1 touch, 1.6x vol) @ 125.30 | Bearish RSI divergence (66) | Extended 2.5 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -3093,7 +3093,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3101,38 +3101,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C47" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D47" s="4" t="n">
-        <v>0.345</v>
+        <v>0.571</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="F47" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>44.19</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G47" s="2" t="n">
-        <v>119.34</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J47" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="K47" s="2" t="n">
-        <v>88.59999999999999</v>
+        <v>48.9</v>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>Doji (indecision at extreme) | Time count: TD setup 24 | RSI overbought (89) | Extended 4.5 ATR from 20 EMA</t>
+          <t>Topping tail (new high rejected), tail 73% of range | Major pivot zone (3 touches, 6.4x vol) @ 44.64 | Volume POC @ 44.23</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>AZO</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3157,102 +3157,102 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C48" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>0.03</v>
+        <v>0.871</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="F48" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>3133.83</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>Bearish engulfing | Fib 61.8% retrace @ 3243.91 | Major pivot zone (6 touches, 2.2x vol) @ 3190.97</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N48" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>CASY</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="E49" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G48" s="2" t="n">
-        <v>222.46</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="L48" s="5" t="inlineStr">
-        <is>
-          <t>Doji (indecision at extreme) | Time count: TD setup 11 | Fib 50.0% retrace @ 224.11 | Prior pivot (2 touches, 1.5x vol) @ 221.25</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N48" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>SHW</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="n">
-        <v>0.876</v>
-      </c>
-      <c r="E49" s="7" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="F49" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G49" s="7" t="n">
-        <v>328.61</v>
-      </c>
-      <c r="H49" s="7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="I49" s="7" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J49" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="L49" s="10" t="inlineStr">
-        <is>
-          <t>Bottoming tail, tail 89% of range | Fib 61.8% retrace @ 320.56 | Prior pivot (2 touches, 1.5x vol) @ 326.09 | Volume POC @ 320.98</t>
-        </is>
-      </c>
-      <c r="M49" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N49" s="11" t="inlineStr">
+      <c r="F49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>676.22</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>Topping tail, tail 47% of range | Major pivot zone (2 touches, 6.6x vol) @ 690.37 | High-volume node @ 681.51</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N49" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -3261,7 +3261,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>CIEN</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3275,320 +3275,320 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>0.668</v>
+        <v>0.54</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F50" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>350.44</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>-3.52</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>Topping tail, tail 52% of range | Major pivot zone (6 touches, 1.4x vol) @ 366.58 | Volume POC @ 351.24</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N50" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>FFIV</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>At risk</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="E51" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G50" s="2" t="n">
-        <v>123.39</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" s="2" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="L50" s="5" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 65% of range | Prior pivot (1 touch, 1.6x vol) @ 125.30 | Bearish RSI divergence (66) | Extended 2.5 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N50" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>APTV</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="F51" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G51" s="7" t="n">
+        <v>360.22</v>
+      </c>
+      <c r="H51" s="7" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="I51" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J51" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K51" s="7" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="L51" s="10" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | RSI oversold (26) | Tagged lower Bollinger band | Extended 4.2 ATR from 20 EMA | Volume 2.1x average</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N51" s="11" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>653.91</v>
+      </c>
+      <c r="H52" s="7" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I52" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K52" s="7" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="L52" s="10" t="inlineStr">
+        <is>
+          <t>Bullish engulfing | Fib 50.0% retrace @ 616.05 | Major pivot zone (3 touches, 1.5x vol) @ 619.72</t>
+        </is>
+      </c>
+      <c r="M52" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N52" s="11" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D51" s="4" t="n">
-        <v>0.702</v>
-      </c>
-      <c r="E51" s="2" t="n">
+      <c r="D53" s="9" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="E53" s="7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F53" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" s="7" t="n">
+        <v>150.23</v>
+      </c>
+      <c r="H53" s="7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J53" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" s="7" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="L53" s="10" t="inlineStr">
+        <is>
+          <t>Bottoming tail, tail 63% of range | Major pivot zone (2 touches, 2.4x vol) @ 149.50 | Tagged lower Bollinger band</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N53" s="11" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>At risk</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>183.59</v>
+      </c>
+      <c r="H54" s="7" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J54" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K54" s="7" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="L54" s="10" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | Fib 38.2% retrace @ 185.98 | Major pivot zone (10 touches, 2.3x vol) @ 180.72</t>
+        </is>
+      </c>
+      <c r="M54" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N54" s="11" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>WAB</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E55" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>283.84</v>
+      </c>
+      <c r="H55" s="7" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I55" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J55" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F51" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>44.08</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="2" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="L51" s="5" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 78% of range | Major pivot zone (3 touches, 6.4x vol) @ 44.64 | Volume POC @ 44.23</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N51" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>AZO</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>0.872</v>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>3132.19</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J52" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K52" s="2" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="L52" s="5" t="inlineStr">
-        <is>
-          <t>Bearish engulfing | Fib 61.8% retrace @ 3243.91 | Major pivot zone (6 touches, 2.2x vol) @ 3190.97</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N52" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CASY</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>0.861</v>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>675.03</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K53" s="2" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="L53" s="5" t="inlineStr">
-        <is>
-          <t>Topping tail, tail 47% of range | Major pivot zone (2 touches, 6.6x vol) @ 690.37 | High-volume node @ 681.51</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N53" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CIEN</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>0.516</v>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>350.74</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>-3.43</v>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K54" s="2" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="L54" s="5" t="inlineStr">
-        <is>
-          <t>Topping tail, tail 51% of range | Major pivot zone (6 touches, 1.4x vol) @ 366.58 | Volume POC @ 351.24</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N54" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>GNRC</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="n">
-        <v>0.513</v>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>204.23</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J55" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K55" s="2" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="L55" s="5" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 77% of range | Major pivot zone (2 touches, 3.0x vol) @ 211.79 | Volume POC @ 204.31</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N55" s="6" t="inlineStr">
+      <c r="K55" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="L55" s="10" t="inlineStr">
+        <is>
+          <t>Bullish engulfing | Fib 50.0% retrace @ 278.61 | Trendline (rising support) @ 277.12</t>
+        </is>
+      </c>
+      <c r="M55" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N55" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -3597,7 +3597,7 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -3605,38 +3605,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C56" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.439</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>360.47</v>
+        <v>151.27</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>-1.38</v>
+        <v>1.55</v>
       </c>
       <c r="I56" s="7" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="J56" s="7" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>26.2</v>
+        <v>46</v>
       </c>
       <c r="L56" s="10" t="inlineStr">
         <is>
-          <t>Doji (indecision at extreme) | RSI oversold (26) | Tagged lower Bollinger band | Extended 4.2 ATR from 20 EMA | Volume 2.1x average</t>
+          <t>Bottoming tail, tail 50% of range | Fib 38.2% retrace @ 149.71 | Prior pivot (1 touch, 1.1x vol) @ 150.46</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
@@ -3653,7 +3653,7 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -3667,32 +3667,32 @@
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.973</v>
+        <v>0.821</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F57" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>653.1799999999999</v>
+        <v>178.65</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>1.95</v>
+        <v>5.4</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="J57" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>51.1</v>
+        <v>43.4</v>
       </c>
       <c r="L57" s="10" t="inlineStr">
         <is>
-          <t>Bullish engulfing | Fib 50.0% retrace @ 616.05 | Major pivot zone (3 touches, 1.5x vol) @ 619.72</t>
+          <t>Bottoming tail, tail 67% of range | High-volume node @ 173.84 | Volume 2.1x average</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
@@ -3709,7 +3709,7 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -3717,38 +3717,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C58" s="8" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>At risk</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.735</v>
+        <v>1</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>3.75</v>
+        <v>7</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G58" s="7" t="n">
-        <v>150.45</v>
+        <v>39.78</v>
       </c>
       <c r="H58" s="7" t="n">
-        <v>1.69</v>
+        <v>-0.31</v>
       </c>
       <c r="I58" s="7" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="J58" s="7" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="K58" s="7" t="n">
-        <v>35.2</v>
+        <v>31.5</v>
       </c>
       <c r="L58" s="10" t="inlineStr">
         <is>
-          <t>Bottoming tail, tail 68% of range | Major pivot zone (2 touches, 2.4x vol) @ 149.50 | Tagged lower Bollinger band</t>
+          <t>Setup from 1 bar ago, still near entry (-0.1 ATR since signal; stop beyond 38.34) | Bottoming tail (new low rejected), tail 59% of range | Major pivot zone (1 touch, 2.5x vol) @ 38.32 | Trendline (falling support) @ 37.65 | Bullish RSI divergence (31) | Tagged lower Bollinger band | Extended 3.0 ATR from 20 EMA | Volume 2.3x average</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -3765,7 +3765,7 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -3773,38 +3773,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C59" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.254</v>
+        <v>1</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>183.88</v>
+        <v>128.48</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>-1.52</v>
+        <v>-2.08</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>3</v>
+        <v>-14</v>
       </c>
       <c r="J59" s="7" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>44.3</v>
+        <v>36.1</v>
       </c>
       <c r="L59" s="10" t="inlineStr">
         <is>
-          <t>Doji (indecision at extreme) | Fib 38.2% retrace @ 185.98 | Major pivot zone (10 touches, 2.3x vol) @ 180.72</t>
+          <t>Setup from 2 bars ago, still near entry (+0.3 ATR since signal; stop beyond 121.75) | Bottoming tail (new low rejected), tail 68% of range | Time count: TD setup 13 | Major pivot zone (1 touch, 1.9x vol) @ 119.60 | Bullish RSI divergence (36) | Volume 2.0x average</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
@@ -3821,7 +3821,7 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GPC</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -3835,32 +3835,32 @@
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.175</v>
+        <v>0.972</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>220.08</v>
+        <v>121.65</v>
       </c>
       <c r="H60" s="7" t="n">
-        <v>-3.51</v>
+        <v>0.21</v>
       </c>
       <c r="I60" s="7" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="J60" s="7" t="n">
         <v>-1</v>
       </c>
       <c r="K60" s="7" t="n">
-        <v>43.5</v>
+        <v>38.7</v>
       </c>
       <c r="L60" s="10" t="inlineStr">
         <is>
-          <t>Doji (indecision at extreme) | Major pivot zone (1 touch, 1.9x vol) @ 216.04 | High-volume node @ 216.25</t>
+          <t>Setup from 2 bars ago, still near entry (-0.0 ATR since signal; stop beyond 120.18) | Bottoming tail (new low rejected), tail 59% of range | Fib 38.2% retrace @ 119.82 | Major pivot zone (4 touches, 1.8x vol) @ 121.77 | Trendline (falling support) @ 121.46 | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
@@ -3877,7 +3877,7 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -3885,38 +3885,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C61" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.174</v>
+        <v>1</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>128.66</v>
+        <v>178.28</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>-1.93</v>
+        <v>2.53</v>
       </c>
       <c r="I61" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J61" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="J61" s="7" t="n">
-        <v>-1</v>
-      </c>
       <c r="K61" s="7" t="n">
-        <v>39.4</v>
+        <v>43.1</v>
       </c>
       <c r="L61" s="10" t="inlineStr">
         <is>
-          <t>Doji (indecision at extreme) | Major pivot zone (2 touches, 2.0x vol) @ 125.03 | Volume POC @ 129.44</t>
+          <t>Setup from 1 bar ago, still near entry (+0.9 ATR since signal; stop beyond 170.14) | Bullish engulfing | Major pivot zone (5 touches, 1.3x vol) @ 172.11 | Trendline (falling support) @ 170.53 | Bullish RSI divergence (43) | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
@@ -3933,7 +3933,7 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>WAB</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -3947,32 +3947,32 @@
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.6919999999999999</v>
+        <v>1</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>283.43</v>
+        <v>252.38</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>0.44</v>
+        <v>-0.57</v>
       </c>
       <c r="I62" s="7" t="n">
+        <v>-15</v>
+      </c>
+      <c r="J62" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="J62" s="7" t="n">
-        <v>4</v>
-      </c>
       <c r="K62" s="7" t="n">
-        <v>49.5</v>
+        <v>31.1</v>
       </c>
       <c r="L62" s="10" t="inlineStr">
         <is>
-          <t>Bullish engulfing | Fib 50.0% retrace @ 278.61 | Trendline (rising support) @ 277.12</t>
+          <t>Setup from 2 bars ago, still near entry (+0.8 ATR since signal; stop beyond 235.21) | Bottoming tail, tail 87% of range | Time count: TD setup 14 | Prior pivot (2 touches, 1.1x vol) @ 241.07 | High-volume node @ 234.92 | Extended 2.8 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
@@ -3989,7 +3989,7 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>FDXF</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
@@ -3997,38 +3997,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>At risk</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.781</v>
+        <v>1</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>151.22</v>
+        <v>107.53</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>1.52</v>
+        <v>-0.74</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="J63" s="7" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>45.9</v>
+        <v>38.5</v>
       </c>
       <c r="L63" s="10" t="inlineStr">
         <is>
-          <t>Bottoming tail, tail 50% of range | Fib 38.2% retrace @ 149.71 | Prior pivot (1 touch, 1.1x vol) @ 150.46</t>
+          <t>Setup from 1 bar ago, still near entry (-0.2 ATR since signal; stop beyond 103.48) | Bottoming tail (new low rejected), tail 90% of range | Prior pivot (2 touches, 1.8x vol) @ 106.96 | Trendline (falling support) @ 103.62 | Bullish RSI divergence (38) | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
@@ -4045,7 +4045,7 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -4059,32 +4059,32 @@
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.6870000000000001</v>
+        <v>1</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>177.9</v>
+        <v>887.85</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>4.96</v>
+        <v>1.12</v>
       </c>
       <c r="I64" s="7" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
       <c r="J64" s="7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K64" s="7" t="n">
-        <v>42.7</v>
+        <v>43</v>
       </c>
       <c r="L64" s="10" t="inlineStr">
         <is>
-          <t>Bottoming tail, tail 61% of range | High-volume node @ 173.84 | Volume 2.1x average</t>
+          <t>Setup from 1 bar ago, still near entry (+0.2 ATR since signal; stop beyond 836.24) | Bottoming tail, tail 72% of range | Time count: TD setup 10 | Major pivot zone (6 touches, 2.1x vol) @ 870.38 | Volume 2.3x average</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
@@ -4101,7 +4101,7 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
@@ -4109,38 +4109,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C65" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>40</v>
+        <v>85.09</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>0.23</v>
+        <v>3.16</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="J65" s="7" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>31.5</v>
+        <v>53.6</v>
       </c>
       <c r="L65" s="10" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.0 ATR since signal; stop beyond 38.34) | Bottoming tail (new low rejected), tail 59% of range | Major pivot zone (1 touch, 2.5x vol) @ 38.32 | Trendline (falling support) @ 37.65 | Bullish RSI divergence (31) | Tagged lower Bollinger band | Extended 3.0 ATR from 20 EMA | Volume 2.3x average</t>
+          <t>Setup from 1 bar ago, still near entry (+1.0 ATR since signal; stop beyond 79.25) | Bottoming tail, tail 48% of range | Fib 61.8% retrace @ 78.36 | Major pivot zone (8 touches, 1.6x vol) @ 78.06 | Volume POC @ 80.70</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
@@ -4157,7 +4157,7 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>GPC</t>
+          <t>HSIC</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -4171,32 +4171,32 @@
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>121.63</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="I66" s="7" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="J66" s="7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K66" s="7" t="n">
-        <v>38.7</v>
+        <v>48.1</v>
       </c>
       <c r="L66" s="10" t="inlineStr">
         <is>
-          <t>Setup from 2 bars ago, still near entry (-0.0 ATR since signal; stop beyond 120.18) | Bottoming tail (new low rejected), tail 59% of range | Fib 38.2% retrace @ 119.82 | Major pivot zone (4 touches, 1.8x vol) @ 121.77 | Trendline (falling support) @ 121.46 | Tagged lower Bollinger band</t>
+          <t>Setup from 1 bar ago, still near entry (+0.6 ATR since signal; stop beyond 83.97) | Bullish engulfing | Fib 38.2% retrace @ 83.21 | Major pivot zone (1 touch, 1.9x vol) @ 84.15 | High-volume node @ 84.67</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
@@ -4213,7 +4213,7 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
@@ -4221,38 +4221,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C67" s="8" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>177.86</v>
+        <v>631.35</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>2.29</v>
+        <v>4.03</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="J67" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>43.1</v>
+        <v>45.8</v>
       </c>
       <c r="L67" s="10" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.8 ATR since signal; stop beyond 170.14) | Bullish engulfing | Major pivot zone (5 touches, 1.3x vol) @ 172.11 | Trendline (falling support) @ 170.53 | Bullish RSI divergence (43) | Tagged lower Bollinger band</t>
+          <t>Setup from 1 bar ago, still near entry (+0.9 ATR since signal; stop beyond 581.78) | Bottoming tail, tail 66% of range | Time count: TD setup 12 | Major pivot zone (5 touches, 1.5x vol) @ 594.79 | Volume 1.8x average</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
@@ -4269,7 +4269,7 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -4286,29 +4286,29 @@
         <v>1</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>252.63</v>
+        <v>246.38</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>-0.47</v>
+        <v>1.42</v>
       </c>
       <c r="I68" s="7" t="n">
-        <v>-15</v>
+        <v>1</v>
       </c>
       <c r="J68" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K68" s="7" t="n">
-        <v>31.1</v>
+        <v>57</v>
       </c>
       <c r="L68" s="10" t="inlineStr">
         <is>
-          <t>Setup from 2 bars ago, still near entry (+0.8 ATR since signal; stop beyond 235.21) | Bottoming tail, tail 87% of range | Time count: TD setup 14 | Prior pivot (2 touches, 1.1x vol) @ 241.07 | High-volume node @ 234.92 | Extended 2.8 ATR from 20 EMA</t>
+          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 228.81) | Bottoming tail, tail 86% of range | Time count: TD setup 14 | Major pivot zone (5 touches, 3.3x vol) @ 226.83 | Volume 3.3x average</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>FDXF</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
@@ -4339,32 +4339,32 @@
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>1</v>
+        <v>0.994</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="F69" s="7" t="n">
         <v>5</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>107.79</v>
+        <v>102.06</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>-0.5</v>
+        <v>-0.36</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="J69" s="7" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>38.5</v>
+        <v>26</v>
       </c>
       <c r="L69" s="10" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (-0.1 ATR since signal; stop beyond 103.48) | Bottoming tail (new low rejected), tail 90% of range | Prior pivot (2 touches, 1.8x vol) @ 106.96 | Trendline (falling support) @ 103.62 | Bullish RSI divergence (38) | Tagged lower Bollinger band</t>
+          <t>Setup from 1 bar ago, still near entry (-0.1 ATR since signal; stop beyond 100.50) | Bottoming tail, tail 62% of range | Prior pivot (1 touch, 1.6x vol) @ 99.18 | RSI oversold (26) | Tagged lower Bollinger band | Extended 2.8 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
@@ -4381,7 +4381,7 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -4398,29 +4398,29 @@
         <v>1</v>
       </c>
       <c r="E70" s="7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F70" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F70" s="7" t="n">
-        <v>4</v>
-      </c>
       <c r="G70" s="7" t="n">
-        <v>886.49</v>
+        <v>57.27</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>0.96</v>
+        <v>1.27</v>
       </c>
       <c r="I70" s="7" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J70" s="7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K70" s="7" t="n">
-        <v>43</v>
+        <v>52.4</v>
       </c>
       <c r="L70" s="10" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.2 ATR since signal; stop beyond 836.24) | Bottoming tail, tail 72% of range | Time count: TD setup 10 | Major pivot zone (6 touches, 2.1x vol) @ 870.38 | Volume 2.3x average</t>
+          <t>Setup from 2 bars ago, still near entry (+0.8 ATR since signal; stop beyond 54.34) | Bottoming tail (new low rejected), tail 47% of range | Fib 38.2% retrace @ 53.99 | Prior pivot (2 touches, 1.3x vol) @ 54.64 | Trendline (rising support) @ 54.50 | Volume 1.8x average</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>EME</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
@@ -4445,38 +4445,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>At risk</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>85.02</v>
+        <v>679.66</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>3.08</v>
+        <v>0.16</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J71" s="7" t="n">
         <v>3</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>53.6</v>
+        <v>37</v>
       </c>
       <c r="L71" s="10" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.9 ATR since signal; stop beyond 79.25) | Bottoming tail, tail 48% of range | Fib 61.8% retrace @ 78.36 | Major pivot zone (8 touches, 1.6x vol) @ 78.06 | Volume POC @ 80.70</t>
+          <t>Setup from 1 bar ago, still near entry (+0.0 ATR since signal; stop beyond 665.55) | Bottoming tail, tail 68% of range | Time count: TD setup 12 | Major pivot zone (1 touch, 2.0x vol) @ 668.46</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
@@ -4493,7 +4493,7 @@
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>HSIC</t>
+          <t>GPN</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
@@ -4510,29 +4510,29 @@
         <v>1</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="F72" s="7" t="n">
         <v>4</v>
       </c>
       <c r="G72" s="7" t="n">
-        <v>86.05</v>
+        <v>85.64</v>
       </c>
       <c r="H72" s="7" t="n">
-        <v>1.28</v>
+        <v>2.5</v>
       </c>
       <c r="I72" s="7" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K72" s="7" t="n">
-        <v>48.1</v>
+        <v>49.7</v>
       </c>
       <c r="L72" s="10" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.6 ATR since signal; stop beyond 83.97) | Bullish engulfing | Fib 38.2% retrace @ 83.21 | Major pivot zone (1 touch, 1.9x vol) @ 84.15 | High-volume node @ 84.67</t>
+          <t>Setup from 1 bar ago, still near entry (+0.9 ATR since signal; stop beyond 80.85) | Bullish engulfing | Fib 38.2% retrace @ 82.29 | Prior pivot (2 touches, 1.7x vol) @ 82.12 | Trendline (rising support) @ 81.14</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
@@ -4549,7 +4549,7 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
@@ -4557,38 +4557,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C73" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F73" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>562.55</v>
+      </c>
+      <c r="H73" s="7" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="I73" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J73" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G73" s="7" t="n">
-        <v>626.59</v>
-      </c>
-      <c r="H73" s="7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I73" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="K73" s="7" t="n">
-        <v>45.8</v>
+        <v>53.6</v>
       </c>
       <c r="L73" s="10" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.7 ATR since signal; stop beyond 581.78) | Bottoming tail, tail 66% of range | Time count: TD setup 12 | Major pivot zone (5 touches, 1.5x vol) @ 594.79 | Volume 1.8x average</t>
+          <t>Setup from 1 bar ago, still near entry (-0.6 ATR since signal; stop beyond 560.52) | Bottoming tail, tail 67% of range | Fib 38.2% retrace @ 557.23 | Major pivot zone (4 touches, 1.1x vol) @ 571.91</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
@@ -4605,7 +4605,7 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
@@ -4619,19 +4619,19 @@
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G74" s="7" t="n">
-        <v>246.19</v>
+        <v>219.9</v>
       </c>
       <c r="H74" s="7" t="n">
-        <v>1.34</v>
+        <v>-3.58</v>
       </c>
       <c r="I74" s="7" t="n">
         <v>1</v>
@@ -4640,11 +4640,11 @@
         <v>3</v>
       </c>
       <c r="K74" s="7" t="n">
-        <v>57</v>
+        <v>45.7</v>
       </c>
       <c r="L74" s="10" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.2 ATR since signal; stop beyond 228.81) | Bottoming tail, tail 86% of range | Time count: TD setup 14 | Major pivot zone (5 touches, 3.3x vol) @ 226.83 | Volume 3.3x average</t>
+          <t>Setup from 1 bar ago, still near entry (-0.4 ATR since signal; stop beyond 217.90) | Bottoming tail, tail 59% of range | Major pivot zone (1 touch, 1.9x vol) @ 216.04 | High-volume node @ 216.25</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
@@ -4661,7 +4661,7 @@
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
@@ -4669,38 +4669,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>At risk</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.981</v>
+        <v>1</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>101.88</v>
+        <v>159.88</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>-0.53</v>
+        <v>0.96</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="J75" s="7" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="K75" s="7" t="n">
-        <v>26</v>
+        <v>35.4</v>
       </c>
       <c r="L75" s="10" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (-0.2 ATR since signal; stop beyond 100.50) | Bottoming tail, tail 62% of range | Prior pivot (1 touch, 1.6x vol) @ 99.18 | RSI oversold (26) | Tagged lower Bollinger band | Extended 2.8 ATR from 20 EMA</t>
+          <t>Setup from 1 bar ago, still near entry (+0.4 ATR since signal; stop beyond 156.20) | Bottoming tail, tail 50% of range | Fib 78.6% retrace @ 157.06 | Major pivot zone (3 touches, 2.4x vol) @ 156.30</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
@@ -4717,7 +4717,7 @@
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>IVZ</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
@@ -4734,29 +4734,29 @@
         <v>1</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G76" s="7" t="n">
-        <v>57.28</v>
+        <v>29.01</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="I76" s="7" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="J76" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K76" s="7" t="n">
-        <v>52.4</v>
+        <v>43</v>
       </c>
       <c r="L76" s="10" t="inlineStr">
         <is>
-          <t>Setup from 2 bars ago, still near entry (+0.8 ATR since signal; stop beyond 54.34) | Bottoming tail (new low rejected), tail 47% of range | Fib 38.2% retrace @ 53.99 | Prior pivot (2 touches, 1.3x vol) @ 54.64 | Trendline (rising support) @ 54.50 | Volume 1.8x average</t>
+          <t>Setup from 1 bar ago, still near entry (+0.4 ATR since signal; stop beyond 28.20) | Bottoming tail, tail 68% of range | Fib 61.8% retrace @ 28.57 | Major pivot zone (3 touches, 1.5x vol) @ 28.54</t>
         </is>
       </c>
       <c r="M76" s="7" t="inlineStr">
@@ -4773,7 +4773,7 @@
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>EME</t>
+          <t>GNRC</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
@@ -4781,25 +4781,25 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C77" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.964</v>
+        <v>1</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F77" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>677.28</v>
+        <v>204.46</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>-0.19</v>
+        <v>1.55</v>
       </c>
       <c r="I77" s="7" t="n">
         <v>1</v>
@@ -4808,11 +4808,11 @@
         <v>3</v>
       </c>
       <c r="K77" s="7" t="n">
-        <v>37</v>
+        <v>50.3</v>
       </c>
       <c r="L77" s="10" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (-0.0 ATR since signal; stop beyond 665.55) | Bottoming tail, tail 68% of range | Time count: TD setup 12 | Major pivot zone (1 touch, 2.0x vol) @ 668.46</t>
+          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 181.00) | Bottoming tail (new low rejected), tail 66% of range | Major pivot zone (7 touches, 7.7x vol) @ 179.18 | Volume 2.3x average</t>
         </is>
       </c>
       <c r="M77" s="7" t="inlineStr">
@@ -4827,224 +4827,224 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t>GPN</t>
-        </is>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D78" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="7" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="F78" s="7" t="n">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>HII</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>314.92</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>Time count: 11 up bars since the last down bar | Fib 78.6% retrace @ 319.32 | Prior pivot (1 touch, 1.2x vol) @ 322.62 | High-volume node @ 317.53 | RSI overbought (75) | Tagged upper Bollinger band | Extended 5.1 ATR from 20 EMA | Volume 2.8x average</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N78" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>NCLH</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J79" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G78" s="7" t="n">
-        <v>85.58</v>
-      </c>
-      <c r="H78" s="7" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="I78" s="7" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J78" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K78" s="7" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="L78" s="10" t="inlineStr">
-        <is>
-          <t>Setup from 1 bar ago, still near entry (+0.8 ATR since signal; stop beyond 80.85) | Bullish engulfing | Fib 38.2% retrace @ 82.29 | Prior pivot (2 touches, 1.7x vol) @ 82.12 | Trendline (rising support) @ 81.14</t>
-        </is>
-      </c>
-      <c r="M78" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N78" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D79" s="9" t="n">
-        <v>0.621</v>
-      </c>
-      <c r="E79" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F79" s="7" t="n">
+      <c r="K79" s="2" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>Time count: 8 up bars since the last down bar | Fib 61.8% retrace @ 18.77 | High-volume node @ 18.57 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 2.8x average</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N79" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>VMC</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>280.61</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G79" s="7" t="n">
-        <v>562.4</v>
-      </c>
-      <c r="H79" s="7" t="n">
-        <v>-2.77</v>
-      </c>
-      <c r="I79" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J79" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K79" s="7" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="L79" s="10" t="inlineStr">
-        <is>
-          <t>Setup from 1 bar ago, still near entry (-0.6 ATR since signal; stop beyond 560.52) | Bottoming tail, tail 67% of range | Fib 38.2% retrace @ 557.23 | Major pivot zone (4 touches, 1.1x vol) @ 571.91</t>
-        </is>
-      </c>
-      <c r="M79" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N79" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C80" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F80" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G80" s="7" t="n">
-        <v>159.82</v>
-      </c>
-      <c r="H80" s="7" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I80" s="7" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J80" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K80" s="7" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="L80" s="10" t="inlineStr">
-        <is>
-          <t>Setup from 1 bar ago, still near entry (+0.4 ATR since signal; stop beyond 156.20) | Bottoming tail, tail 50% of range | Fib 78.6% retrace @ 157.06 | Major pivot zone (3 touches, 2.4x vol) @ 156.30</t>
-        </is>
-      </c>
-      <c r="M80" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N80" s="11" t="inlineStr">
+      <c r="K80" s="2" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>Fib 61.8% retrace @ 288.65 | Major pivot zone (6 touches, 1.7x vol) @ 280.70 | Volume POC @ 289.56 | RSI overbought (73) | Tagged upper Bollinger band | Extended 3.8 ATR from 20 EMA | Volume 1.7x average</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N80" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t>IVZ</t>
-        </is>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D81" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F81" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G81" s="7" t="n">
-        <v>28.99</v>
-      </c>
-      <c r="H81" s="7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I81" s="7" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J81" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K81" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="L81" s="10" t="inlineStr">
-        <is>
-          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 28.20) | Bottoming tail, tail 68% of range | Fib 61.8% retrace @ 28.57 | Major pivot zone (3 touches, 1.5x vol) @ 28.54</t>
-        </is>
-      </c>
-      <c r="M81" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N81" s="11" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>TDY</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C81" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>674.76</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 12 | Fib 78.6% retrace @ 674.65 | Major pivot zone (2 touches, 3.2x vol) @ 672.68 | RSI overbought (75) | Tagged upper Bollinger band | Extended 3.2 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N81" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5053,7 +5053,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -5067,32 +5067,32 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>0.101</v>
+        <v>0.2</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>7.25</v>
+        <v>6.5</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>315.08</v>
+        <v>106.51</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>12.83</v>
+        <v>0.84</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>75.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>Time count: 11 up bars since the last down bar | Fib 78.6% retrace @ 319.32 | Prior pivot (1 touch, 1.2x vol) @ 322.62 | High-volume node @ 317.53 | RSI overbought (75) | Tagged upper Bollinger band | Extended 5.1 ATR from 20 EMA | Volume 2.8x average</t>
+          <t>Time count: TD setup 15 | Fib 61.8% retrace @ 107.01 | Major pivot zone (3 touches, 3.0x vol) @ 107.05 | RSI overbought (72) | Tagged upper Bollinger band | Extended 3.0 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -5109,7 +5109,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>NCLH</t>
+          <t>LHX</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -5123,32 +5123,32 @@
         </is>
       </c>
       <c r="D83" s="4" t="n">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>18.25</v>
+        <v>278.46</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>13.67</v>
+        <v>6.85</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>74</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>Time count: 8 up bars since the last down bar | Fib 61.8% retrace @ 18.77 | High-volume node @ 18.57 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 2.8x average</t>
+          <t>Time count: TD setup 15 | Major pivot zone (1 touch, 2.0x vol) @ 281.06 | RSI overbought (78) | Tagged upper Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 1.6x average</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>AON</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5179,32 +5179,32 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>280.13</v>
+        <v>320.52</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>5.71</v>
+        <v>1.52</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>3</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>72.40000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>Fib 61.8% retrace @ 288.65 | Major pivot zone (6 touches, 1.7x vol) @ 280.70 | Volume POC @ 289.56 | RSI overbought (72) | Tagged upper Bollinger band | Extended 3.8 ATR from 20 EMA | Volume 1.7x average</t>
+          <t>Time count: TD setup 10 | Fib 50.0% retrace @ 323.90 | Prior pivot (1 touch, 1.3x vol) @ 324.30 | Volume POC @ 320.45 | Tagged upper Bollinger band | Extended 3.4 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>TDY</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -5235,32 +5235,32 @@
         </is>
       </c>
       <c r="D85" s="4" t="n">
-        <v>0.404</v>
+        <v>0.143</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="F85" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>673.84</v>
+        <v>366.69</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>1.24</v>
+        <v>3.48</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>74.90000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>Time count: TD setup 12 | Fib 78.6% retrace @ 674.65 | Major pivot zone (2 touches, 3.2x vol) @ 672.68 | RSI overbought (75) | Tagged upper Bollinger band | Extended 3.2 ATR from 20 EMA</t>
+          <t>Time count: TD setup 14 | Fib 61.8% retrace @ 368.42 | Prior pivot (1 touch, 1.6x vol) @ 372.24 | RSI overbought (71) | Tagged upper Bollinger band | Extended 3.6 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -5277,7 +5277,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5291,32 +5291,32 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>0.23</v>
+        <v>0.142</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>106.49</v>
+        <v>44.76</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>0.82</v>
+        <v>2.03</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>72.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>Time count: TD setup 15 | Fib 61.8% retrace @ 107.01 | Major pivot zone (3 touches, 3.0x vol) @ 107.05 | RSI overbought (72) | Tagged upper Bollinger band | Extended 3.0 ATR from 20 EMA</t>
+          <t>Time count: TD setup 20 | Fib 61.8% retrace @ 44.89 | Major pivot zone (3 touches, 1.9x vol) @ 44.71 | RSI overbought (74) | Extended 3.2 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>LHX</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -5350,29 +5350,29 @@
         <v>0</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>278.41</v>
+        <v>262.36</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>6.83</v>
+        <v>4.24</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>77.59999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>Time count: TD setup 15 | Major pivot zone (1 touch, 2.0x vol) @ 281.06 | RSI overbought (78) | Tagged upper Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 1.6x average</t>
+          <t>Time count: 13 up bars since the last down bar | Fib 38.2% retrace @ 262.53 | Prior pivot (1 touch, 1.0x vol) @ 265.83 | Trendline (rising resistance) @ 263.21 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>AON</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5403,32 +5403,32 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>0.14</v>
+        <v>0.339</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>320.74</v>
+        <v>309.51</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>1.59</v>
+        <v>-0.1</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>Time count: TD setup 10 | Fib 50.0% retrace @ 323.90 | Prior pivot (1 touch, 1.3x vol) @ 324.30 | Volume POC @ 320.45 | Tagged upper Bollinger band | Extended 3.4 ATR from 20 EMA</t>
+          <t>Time count: 7 bars without a lower low | Fib 78.6% retrace @ 314.31 | Prior pivot (1 touch, 0.7x vol) @ 313.73 | RSI overbought (70) | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>URI</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5459,32 +5459,32 @@
         </is>
       </c>
       <c r="D89" s="4" t="n">
-        <v>0.055</v>
+        <v>0.142</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>367.62</v>
+        <v>1192.06</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>3.74</v>
+        <v>1.49</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>71.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>Time count: TD setup 14 | Fib 61.8% retrace @ 368.42 | Prior pivot (1 touch, 1.6x vol) @ 372.24 | RSI overbought (71) | Tagged upper Bollinger band | Extended 3.6 ATR from 20 EMA</t>
+          <t>Time count: 7 up bars since the last down bar | Trendline (rising resistance) @ 1185.31 | RSI overbought (73) | Tagged upper Bollinger band | Extended 2.7 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -5499,14 +5499,14 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>bearish</t>
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>TPR</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>bullish</t>
         </is>
       </c>
       <c r="C90" s="13" t="inlineStr">
@@ -5514,41 +5514,41 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D90" s="4" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="F90" s="2" t="n">
+      <c r="D90" s="9" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="E90" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G90" s="2" t="n">
-        <v>44.73</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J90" s="2" t="n">
+      <c r="F90" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="K90" s="2" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="L90" s="5" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 20 | Fib 61.8% retrace @ 44.89 | Major pivot zone (3 touches, 1.9x vol) @ 44.71 | RSI overbought (74) | Extended 3.2 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N90" s="6" t="inlineStr">
+      <c r="G90" s="7" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="H90" s="7" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="I90" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="L90" s="10" t="inlineStr">
+        <is>
+          <t>Time count: 9 down bars since the last up bar | Major pivot zone (2 touches, 1.9x vol) @ 112.16 | High-volume node @ 115.70 | Trendline (rising support) @ 115.23</t>
+        </is>
+      </c>
+      <c r="M90" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N90" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5557,7 +5557,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>DOV</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -5571,32 +5571,32 @@
         </is>
       </c>
       <c r="D91" s="4" t="n">
-        <v>0.427</v>
+        <v>0.113</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="F91" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>208.78</v>
+        <v>119.93</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>0.38</v>
+        <v>1.26</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>72.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>Fib 50.0% retrace @ 208.52 | Major pivot zone (3 touches, 1.6x vol) @ 209.50 | RSI overbought (73) | Tagged upper Bollinger band | Extended 3.1 ATR from 20 EMA</t>
+          <t>Time count: TD setup 10 | Prior pivot (2 touches, 0.9x vol) @ 119.91 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.2 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -5613,7 +5613,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -5627,32 +5627,32 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>0.001</v>
+        <v>0.033</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="F92" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>262.03</v>
+        <v>103.13</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>4.11</v>
+        <v>2.75</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>68.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>Time count: 13 up bars since the last down bar | Fib 38.2% retrace @ 262.53 | Prior pivot (1 touch, 1.0x vol) @ 265.83 | Trendline (rising resistance) @ 263.21 | Tagged upper Bollinger band</t>
+          <t>Time count: TD setup 12 | Prior pivot (1 touch, 1.0x vol) @ 103.78 | RSI overbought (76) | Tagged upper Bollinger band | Extended 3.0 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -5669,7 +5669,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>URI</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -5683,32 +5683,32 @@
         </is>
       </c>
       <c r="D93" s="4" t="n">
-        <v>0.153</v>
+        <v>0.066</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>1192.32</v>
+        <v>490.71</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>1.51</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>72.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>Time count: 7 up bars since the last down bar | Trendline (rising resistance) @ 1185.31 | RSI overbought (73) | Tagged upper Bollinger band | Extended 2.7 ATR from 20 EMA</t>
+          <t>Time count: 13 up bars since the last down bar | Major pivot zone (2 touches, 1.8x vol) @ 492.74 | RSI overbought (72) | Extended 2.8 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>TPR</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -5739,96 +5739,96 @@
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.982</v>
+        <v>0.798</v>
       </c>
       <c r="E94" s="7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F94" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G94" s="7" t="n">
+        <v>135.23</v>
+      </c>
+      <c r="H94" s="7" t="n">
+        <v>-22.32</v>
+      </c>
+      <c r="I94" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J94" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K94" s="7" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="L94" s="10" t="inlineStr">
+        <is>
+          <t>Fib 78.6% retrace @ 126.03 | Prior pivot (1 touch, 1.3x vol) @ 133.05 | RSI oversold (26) | Tagged lower Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 3.9x average</t>
+        </is>
+      </c>
+      <c r="M94" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N94" s="11" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C95" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="E95" s="7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F95" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F94" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G94" s="7" t="n">
-        <v>117.33</v>
-      </c>
-      <c r="H94" s="7" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="I94" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K94" s="7" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="L94" s="10" t="inlineStr">
-        <is>
-          <t>Time count: 9 down bars since the last up bar | Major pivot zone (2 touches, 1.9x vol) @ 112.16 | High-volume node @ 115.70 | Trendline (rising support) @ 115.23</t>
-        </is>
-      </c>
-      <c r="M94" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N94" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>PPG</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C95" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="n">
-        <v>0.168</v>
-      </c>
-      <c r="E95" s="2" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="F95" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>119.79</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J95" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K95" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="L95" s="5" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 10 | Prior pivot (2 touches, 0.9x vol) @ 119.91 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.2 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N95" s="6" t="inlineStr">
+      <c r="G95" s="7" t="n">
+        <v>642.24</v>
+      </c>
+      <c r="H95" s="7" t="n">
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="I95" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J95" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K95" s="7" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="L95" s="10" t="inlineStr">
+        <is>
+          <t>Major pivot zone (2 touches, 1.8x vol) @ 619.81 | RSI oversold (26) | Tagged lower Bollinger band | Extended 3.5 ATR from 20 EMA | Volume 2.6x average</t>
+        </is>
+      </c>
+      <c r="M95" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N95" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5837,7 +5837,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>TFC</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5851,96 +5851,96 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>0.037</v>
+        <v>0.53</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="F96" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>49.19</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="L96" s="5" t="inlineStr">
+        <is>
+          <t>Fib 50.0% retrace @ 49.37 | Major pivot zone (7 touches, 1.4x vol) @ 49.39 | High-volume node @ 49.73 | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N96" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>LII</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C97" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="E97" s="7" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F97" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G96" s="2" t="n">
-        <v>103.12</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="L96" s="5" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 12 | Prior pivot (1 touch, 1.0x vol) @ 103.78 | RSI overbought (76) | Tagged upper Bollinger band | Extended 3.0 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N96" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>MSI</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C97" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E97" s="2" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v>490.27</v>
-      </c>
-      <c r="H97" s="2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K97" s="2" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="L97" s="5" t="inlineStr">
-        <is>
-          <t>Time count: 13 up bars since the last down bar | Major pivot zone (2 touches, 1.8x vol) @ 492.74 | RSI overbought (72) | Extended 2.8 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N97" s="6" t="inlineStr">
+      <c r="G97" s="7" t="n">
+        <v>344.02</v>
+      </c>
+      <c r="H97" s="7" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="I97" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J97" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" s="7" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="L97" s="10" t="inlineStr">
+        <is>
+          <t>Prior pivot (1 touch, 1.4x vol) @ 340.32 | Trendline (falling support) @ 319.68 | Bullish RSI divergence (41) | Tagged lower Bollinger band | Extended 2.6 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M97" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N97" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5949,7 +5949,7 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -5963,32 +5963,32 @@
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.848</v>
+        <v>0.478</v>
       </c>
       <c r="E98" s="7" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="F98" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G98" s="7" t="n">
-        <v>135.82</v>
+        <v>256.46</v>
       </c>
       <c r="H98" s="7" t="n">
-        <v>-21.98</v>
+        <v>-1.35</v>
       </c>
       <c r="I98" s="7" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="J98" s="7" t="n">
         <v>-2</v>
       </c>
       <c r="K98" s="7" t="n">
-        <v>26.6</v>
+        <v>34.7</v>
       </c>
       <c r="L98" s="10" t="inlineStr">
         <is>
-          <t>Fib 78.6% retrace @ 126.03 | Prior pivot (1 touch, 1.3x vol) @ 133.05 | RSI oversold (27) | Tagged lower Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 3.9x average</t>
+          <t>Time count: 9 down bars since the last up bar | Trendline (falling support) @ 253.65 | Bullish RSI divergence (35) | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M98" s="7" t="inlineStr">
@@ -6003,14 +6003,14 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="7" t="inlineStr">
-        <is>
-          <t>CAT</t>
-        </is>
-      </c>
-      <c r="B99" s="7" t="inlineStr">
-        <is>
-          <t>bullish</t>
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>LYB</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>bearish</t>
         </is>
       </c>
       <c r="C99" s="13" t="inlineStr">
@@ -6018,41 +6018,41 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D99" s="9" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="E99" s="7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F99" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G99" s="7" t="n">
-        <v>641.46</v>
-      </c>
-      <c r="H99" s="7" t="n">
-        <v>-10.08</v>
-      </c>
-      <c r="I99" s="7" t="n">
+      <c r="D99" s="4" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>65.09</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="I99" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="J99" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K99" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="L99" s="10" t="inlineStr">
-        <is>
-          <t>Major pivot zone (2 touches, 1.8x vol) @ 619.81 | RSI oversold (26) | Tagged lower Bollinger band | Extended 3.5 ATR from 20 EMA | Volume 2.7x average</t>
-        </is>
-      </c>
-      <c r="M99" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N99" s="11" t="inlineStr">
+      <c r="J99" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="L99" s="5" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 19 | Fib 61.8% retrace @ 65.23 | Major pivot zone (3 touches, 1.6x vol) @ 67.19</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N99" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -6061,7 +6061,7 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>LII</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -6075,152 +6075,152 @@
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.825</v>
+        <v>0</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="F100" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G100" s="7" t="n">
-        <v>343.54</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="H100" s="7" t="n">
-        <v>3.28</v>
+        <v>-2.96</v>
       </c>
       <c r="I100" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J100" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K100" s="7" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="L100" s="10" t="inlineStr">
+        <is>
+          <t>Time count: 11 down bars since the last up bar | Prior pivot (2 touches, 1.0x vol) @ 95.80 | RSI oversold (29) | Tagged lower Bollinger band</t>
+        </is>
+      </c>
+      <c r="M100" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N100" s="11" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C101" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E101" s="7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F101" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G101" s="7" t="n">
+        <v>76.08</v>
+      </c>
+      <c r="H101" s="7" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="I101" s="7" t="n">
+        <v>-9</v>
+      </c>
+      <c r="J101" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K101" s="7" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="L101" s="10" t="inlineStr">
+        <is>
+          <t>Time count: 11 down bars since the last up bar | Major pivot zone (3 touches, 1.5x vol) @ 75.85 | Tagged lower Bollinger band</t>
+        </is>
+      </c>
+      <c r="M101" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N101" s="11" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>KEYS</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C102" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="E102" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F102" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G102" s="7" t="n">
+        <v>330.14</v>
+      </c>
+      <c r="H102" s="7" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="I102" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J102" s="7" t="n">
         <v>-2</v>
       </c>
-      <c r="J100" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K100" s="7" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="L100" s="10" t="inlineStr">
-        <is>
-          <t>Prior pivot (1 touch, 1.4x vol) @ 340.32 | Trendline (falling support) @ 319.68 | Bullish RSI divergence (41) | Tagged lower Bollinger band | Extended 2.6 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M100" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N100" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>TXN</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C101" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="n">
-        <v>0.366</v>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>309.42</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K101" s="2" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="L101" s="5" t="inlineStr">
-        <is>
-          <t>Time count: 7 bars without a lower low | Fib 78.6% retrace @ 314.31 | Prior pivot (1 touch, 0.7x vol) @ 313.73 | Tagged upper Bollinger band</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N101" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>LYB</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C102" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D102" s="4" t="n">
-        <v>0.604</v>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>65.11</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J102" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="K102" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="L102" s="5" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 19 | Fib 61.8% retrace @ 65.23 | Major pivot zone (3 touches, 1.6x vol) @ 67.19</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N102" s="6" t="inlineStr">
+      <c r="K102" s="7" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="L102" s="10" t="inlineStr">
+        <is>
+          <t>Fib 61.8% retrace @ 330.37 | Major pivot zone (6 touches, 3.1x vol) @ 327.50 | Volume POC @ 334.25</t>
+        </is>
+      </c>
+      <c r="M102" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N102" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -6229,7 +6229,7 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
@@ -6243,32 +6243,32 @@
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.02</v>
+        <v>0.666</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="F103" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>76.13</v>
+        <v>627.97</v>
       </c>
       <c r="H103" s="7" t="n">
-        <v>-1.42</v>
+        <v>2.53</v>
       </c>
       <c r="I103" s="7" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J103" s="7" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="K103" s="7" t="n">
-        <v>32.5</v>
+        <v>36.1</v>
       </c>
       <c r="L103" s="10" t="inlineStr">
         <is>
-          <t>Time count: 11 down bars since the last up bar | Major pivot zone (3 touches, 1.5x vol) @ 75.85 | Tagged lower Bollinger band</t>
+          <t>Time count: 11 down bars since the last up bar | Fib 61.8% retrace @ 621.77 | High-volume node @ 620.94</t>
         </is>
       </c>
       <c r="M103" s="7" t="inlineStr">
@@ -6285,7 +6285,7 @@
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
@@ -6299,7 +6299,7 @@
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.239</v>
+        <v>0.931</v>
       </c>
       <c r="E104" s="7" t="n">
         <v>3.5</v>
@@ -6308,23 +6308,23 @@
         <v>3</v>
       </c>
       <c r="G104" s="7" t="n">
-        <v>330.61</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="H104" s="7" t="n">
-        <v>-1.46</v>
+        <v>2.29</v>
       </c>
       <c r="I104" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J104" s="7" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="K104" s="7" t="n">
-        <v>43.7</v>
+        <v>50.2</v>
       </c>
       <c r="L104" s="10" t="inlineStr">
         <is>
-          <t>Fib 61.8% retrace @ 330.37 | Major pivot zone (6 touches, 3.1x vol) @ 327.50 | Volume POC @ 334.25</t>
+          <t>Fib 50.0% retrace @ 76.19 | Major pivot zone (3 touches, 1.0x vol) @ 75.26 | High-volume node @ 75.69</t>
         </is>
       </c>
       <c r="M104" s="7" t="inlineStr">
@@ -6341,7 +6341,7 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
@@ -6355,32 +6355,32 @@
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.666</v>
+        <v>0.368</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="F105" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>628.14</v>
+        <v>238.85</v>
       </c>
       <c r="H105" s="7" t="n">
-        <v>2.56</v>
+        <v>-5.88</v>
       </c>
       <c r="I105" s="7" t="n">
-        <v>-10</v>
+        <v>-1</v>
       </c>
       <c r="J105" s="7" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="K105" s="7" t="n">
-        <v>36.2</v>
+        <v>39.5</v>
       </c>
       <c r="L105" s="10" t="inlineStr">
         <is>
-          <t>Time count: 11 down bars since the last up bar | Fib 61.8% retrace @ 621.77 | High-volume node @ 620.94</t>
+          <t>Fib 61.8% retrace @ 228.55 | Major pivot zone (3 touches, 1.4x vol) @ 238.69 | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M105" s="7" t="inlineStr">
@@ -6397,7 +6397,7 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -6411,96 +6411,96 @@
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.887</v>
+        <v>0.065</v>
       </c>
       <c r="E106" s="7" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="F106" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G106" s="7" t="n">
-        <v>76.84</v>
+        <v>379.24</v>
       </c>
       <c r="H106" s="7" t="n">
-        <v>2.17</v>
+        <v>-2.38</v>
       </c>
       <c r="I106" s="7" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="J106" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K106" s="7" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="L106" s="10" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 8 | Fib 38.2% retrace @ 373.38 | Tagged lower Bollinger band</t>
+        </is>
+      </c>
+      <c r="M106" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N106" s="11" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>ARES</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C107" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="E107" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K106" s="7" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="L106" s="10" t="inlineStr">
-        <is>
-          <t>Fib 50.0% retrace @ 76.19 | Major pivot zone (3 touches, 1.0x vol) @ 75.26 | High-volume node @ 75.69</t>
-        </is>
-      </c>
-      <c r="M106" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N106" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="7" t="inlineStr">
-        <is>
-          <t>VLO</t>
-        </is>
-      </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C107" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D107" s="9" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="E107" s="7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="F107" s="7" t="n">
+      <c r="F107" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G107" s="7" t="n">
-        <v>380.59</v>
-      </c>
-      <c r="H107" s="7" t="n">
-        <v>-2.03</v>
-      </c>
-      <c r="I107" s="7" t="n">
-        <v>-9</v>
-      </c>
-      <c r="J107" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K107" s="7" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="L107" s="10" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 8 | Fib 38.2% retrace @ 373.38 | Tagged lower Bollinger band</t>
-        </is>
-      </c>
-      <c r="M107" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N107" s="11" t="inlineStr">
+      <c r="G107" s="2" t="n">
+        <v>126.03</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="L107" s="5" t="inlineStr">
+        <is>
+          <t>Time count: 8 up bars since the last down bar | Prior pivot (2 touches, 1.3x vol) @ 129.72 | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N107" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.278</v>
+        <v>0.252</v>
       </c>
       <c r="E108" s="7" t="n">
         <v>3</v>
@@ -6532,10 +6532,10 @@
         <v>4</v>
       </c>
       <c r="G108" s="7" t="n">
-        <v>280.92</v>
+        <v>280.84</v>
       </c>
       <c r="H108" s="7" t="n">
-        <v>-12.73</v>
+        <v>-12.75</v>
       </c>
       <c r="I108" s="7" t="n">
         <v>-1</v>
@@ -6544,7 +6544,7 @@
         <v>-1</v>
       </c>
       <c r="K108" s="7" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="L108" s="10" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.312</v>
+        <v>0.278</v>
       </c>
       <c r="E109" s="7" t="n">
         <v>3</v>
@@ -6588,10 +6588,10 @@
         <v>4</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>283.12</v>
+        <v>282.98</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v>-12.86</v>
+        <v>-12.9</v>
       </c>
       <c r="I109" s="7" t="n">
         <v>-1</v>
@@ -6600,11 +6600,11 @@
         <v>-1</v>
       </c>
       <c r="K109" s="7" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="L109" s="10" t="inlineStr">
         <is>
-          <t>RSI oversold (22) | Tagged lower Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 4.9x average</t>
+          <t>RSI oversold (22) | Tagged lower Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 4.8x average</t>
         </is>
       </c>
       <c r="M109" s="7" t="inlineStr">

--- a/site/reversal_signals.xlsx
+++ b/site/reversal_signals.xlsx
@@ -106,12 +106,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.909</v>
+        <v>0.997</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>7.75</v>
@@ -596,10 +596,10 @@
         <v>7</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>494.61</v>
+        <v>496.9</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.98</v>
+        <v>1.45</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
@@ -608,11 +608,11 @@
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>45.2</v>
+        <v>46.9</v>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>Bullish engulfing | Fib 61.8% retrace @ 485.63 | Major pivot zone (11 touches, 2.0x vol) @ 480.89 | High-volume node @ 491.45 | Trendline (falling support) @ 475.07 | Bullish RSI divergence (45) | Tagged lower Bollinger band</t>
+          <t>Bullish engulfing | Fib 61.8% retrace @ 485.63 | Major pivot zone (11 touches, 2.0x vol) @ 480.89 | High-volume node @ 491.45 | Trendline (falling support) @ 475.07 | Bullish RSI divergence (47) | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -637,13 +637,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>0.764</v>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>0.756</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>7.5</v>
@@ -652,10 +652,10 @@
         <v>6</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>54.57</v>
+        <v>54.62</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-2.93</v>
+        <v>-2.85</v>
       </c>
       <c r="I3" s="7" t="n">
         <v>-1</v>
@@ -664,9 +664,9 @@
         <v>-2</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="L3" s="9" t="inlineStr">
+        <v>54.5</v>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
         <is>
           <t>Topping tail, tail 54% of range | Time count: TD setup 7 | Fib 78.6% retrace @ 57.08 | Major pivot zone (9 touches, 2.4x vol) @ 55.40 | High-volume node @ 54.81 | Trendline (rising resistance) @ 56.84</t>
         </is>
@@ -676,7 +676,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N3" s="10" t="inlineStr">
+      <c r="N3" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -693,13 +693,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D4" s="8" t="n">
-        <v>0.9320000000000001</v>
+      <c r="D4" s="9" t="n">
+        <v>0.987</v>
       </c>
       <c r="E4" s="7" t="n">
         <v>7.25</v>
@@ -708,10 +708,10 @@
         <v>6</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>33.47</v>
+        <v>33.39</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>-1.95</v>
+        <v>-2.17</v>
       </c>
       <c r="I4" s="7" t="n">
         <v>13</v>
@@ -720,11 +720,11 @@
         <v>-1</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>Bearish engulfing | Time count: 12 up bars since the last down bar | Fib 61.8% retrace @ 34.41 | Major pivot zone (2 touches, 1.9x vol) @ 33.92 | RSI overbought (70) | Extended 3.4 ATR from 20 EMA</t>
+        <v>69.59999999999999</v>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>Bearish engulfing | Time count: 12 up bars since the last down bar | Fib 61.8% retrace @ 34.41 | Major pivot zone (2 touches, 1.9x vol) @ 33.92 | Bearish RSI divergence (70) | Extended 3.4 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
@@ -732,7 +732,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N4" s="10" t="inlineStr">
+      <c r="N4" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -749,13 +749,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
-        <v>0.572</v>
+      <c r="D5" s="9" t="n">
+        <v>0.629</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>7</v>
@@ -764,10 +764,10 @@
         <v>7</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>114.42</v>
+        <v>114.38</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>3.55</v>
+        <v>3.51</v>
       </c>
       <c r="I5" s="7" t="n">
         <v>1</v>
@@ -776,11 +776,11 @@
         <v>1</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 53% of range | Fib 78.6% retrace @ 114.79 | Major pivot zone (5 touches, 1.7x vol) @ 116.28 | RSI overbought (71) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 2.2x average</t>
+        <v>71.3</v>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 54% of range | Fib 78.6% retrace @ 114.79 | Major pivot zone (5 touches, 1.7x vol) @ 116.28 | RSI overbought (71) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 2.2x average</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
@@ -788,7 +788,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N5" s="10" t="inlineStr">
+      <c r="N5" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -805,12 +805,12 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="n">
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="7" t="n">
@@ -820,10 +820,10 @@
         <v>7</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>419.42</v>
+        <v>419.61</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>3.91</v>
+        <v>3.96</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>13</v>
@@ -832,11 +832,11 @@
         <v>4</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 77% of range | Time count: 15 up bars since the last down bar | Fib 1.27 extension @ 434.72 | RSI overbought (82) | Tagged upper Bollinger band | Extended 5.1 ATR from 20 EMA | Volume 2.5x average</t>
+        <v>81.7</v>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 77% of range | Time count: 15 up bars since the last down bar | Fib 1.27 extension @ 434.72 | RSI overbought (82) | Tagged upper Bollinger band | Extended 5.1 ATR from 20 EMA | Volume 2.6x average</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -844,7 +844,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N6" s="10" t="inlineStr">
+      <c r="N6" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -853,7 +853,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -861,38 +861,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>0.783</v>
+      <c r="D7" s="9" t="n">
+        <v>0.571</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="F7" s="7" t="n">
         <v>6</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>42.1</v>
+        <v>1027.25</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1.21</v>
+        <v>1.94</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 72% of range | Time count: TD setup 20 | Prior pivot (2 touches, 1.1x vol) @ 42.24 | High-volume node @ 42.32 | RSI overbought (70) | Extended 3.2 ATR from 20 EMA</t>
+        <v>55.9</v>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 65% of range | Fib 78.6% retrace @ 1078.54 | Major pivot zone (8 touches, 1.8x vol) @ 1043.32 | High-volume node @ 1073.68 | Trendline (falling resistance) @ 1028.20 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
@@ -900,7 +900,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N7" s="10" t="inlineStr">
+      <c r="N7" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -909,7 +909,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -917,13 +917,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>0.85</v>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>0.59</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>6.5</v>
@@ -932,23 +932,23 @@
         <v>6</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>305.27</v>
+        <v>42.18</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.23</v>
+        <v>1.42</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="L8" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 62% of range | Time count: TD setup 10 | Fib 50.0% retrace @ 310.98 | Prior pivot (1 touch, 1.4x vol) @ 312.88 | High-volume node @ 311.94 | Tagged upper Bollinger band</t>
+        <v>70.7</v>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 55% of range | Time count: TD setup 20 | Prior pivot (2 touches, 1.1x vol) @ 42.24 | High-volume node @ 42.32 | RSI overbought (71) | Extended 3.2 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
@@ -956,7 +956,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N8" s="10" t="inlineStr">
+      <c r="N8" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -965,7 +965,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -973,13 +973,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>0.847</v>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>0.633</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>6.5</v>
@@ -988,23 +988,23 @@
         <v>6</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>561.67</v>
+        <v>306.34</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1.61</v>
+        <v>0.58</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 65% of range | Time count: TD setup 15 | Fib 78.6% retrace @ 565.76 | Prior pivot (2 touches, 1.2x vol) @ 575.43 | Bearish RSI divergence (67) | Extended 2.9 ATR from 20 EMA</t>
+        <v>59.4</v>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 53% of range | Time count: TD setup 10 | Fib 50.0% retrace @ 310.98 | Prior pivot (1 touch, 1.4x vol) @ 312.88 | High-volume node @ 311.94 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
@@ -1012,7 +1012,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N9" s="10" t="inlineStr">
+      <c r="N9" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1021,7 +1021,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -1029,13 +1029,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>0.996</v>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>0.895</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>6.5</v>
@@ -1044,23 +1044,23 @@
         <v>6</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>88.5</v>
+        <v>561.58</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-2.15</v>
+        <v>1.59</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>-2</v>
+        <v>16</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="L10" s="9" t="inlineStr">
-        <is>
-          <t>Bearish engulfing | Fib 78.6% retrace @ 92.43 | Major pivot zone (14 touches, 2.7x vol) @ 92.79 | Volume POC @ 91.53 | Bearish RSI divergence (51) | Volume 1.7x average</t>
+        <v>66.59999999999999</v>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 65% of range | Time count: TD setup 15 | Fib 78.6% retrace @ 565.76 | Prior pivot (2 touches, 1.2x vol) @ 575.43 | Bearish RSI divergence (67) | Extended 2.9 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
@@ -1068,7 +1068,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N10" s="10" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1077,7 +1077,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>DOV</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -1085,38 +1085,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>0.241</v>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="F11" s="7" t="n">
         <v>6</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>209.17</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.57</v>
+        <v>-2.22</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>Doji (indecision at extreme) | Fib 50.0% retrace @ 208.52 | Major pivot zone (3 touches, 1.6x vol) @ 209.50 | RSI overbought (73) | Tagged upper Bollinger band | Extended 3.1 ATR from 20 EMA</t>
+        <v>50.8</v>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>Bearish engulfing | Fib 78.6% retrace @ 92.43 | Major pivot zone (14 touches, 2.7x vol) @ 92.79 | Volume POC @ 91.53 | Bearish RSI divergence (51) | Volume 1.7x average</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
@@ -1124,7 +1124,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N11" s="10" t="inlineStr">
+      <c r="N11" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1133,7 +1133,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>DOV</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -1141,158 +1141,158 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>0.969</v>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>At risk</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>0.14</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>6</v>
       </c>
       <c r="F12" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>209.34</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I12" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G12" s="7" t="n">
-        <v>502.6</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="I12" s="7" t="n">
+      <c r="J12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | Fib 50.0% retrace @ 208.52 | Major pivot zone (3 touches, 1.6x vol) @ 209.50 | RSI overbought (73) | Tagged upper Bollinger band | Extended 3.0 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>LIN</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>501.81</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="I13" s="7" t="n">
         <v>-2</v>
       </c>
-      <c r="J12" s="7" t="n">
+      <c r="J13" s="7" t="n">
         <v>-2</v>
       </c>
-      <c r="K12" s="7" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>Bearish engulfing | Fib 61.8% retrace @ 511.18 | Major pivot zone (3 touches, 1.4x vol) @ 505.57 | High-volume node @ 505.80 | Bearish RSI divergence (61)</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N12" s="10" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="K13" s="7" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>Bearish engulfing | Fib 61.8% retrace @ 511.18 | Major pivot zone (3 touches, 1.4x vol) @ 505.57 | High-volume node @ 505.80 | Bearish RSI divergence (60)</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Likely to confirm</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
-        <v>0.953</v>
-      </c>
-      <c r="E13" s="2" t="n">
+      <c r="D14" s="4" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="E14" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F14" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G13" s="2" t="n">
-        <v>428.83</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>-4.38</v>
-      </c>
-      <c r="I13" s="2" t="n">
+      <c r="G14" s="2" t="n">
+        <v>430.77</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="I14" s="2" t="n">
         <v>-6</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="J14" s="2" t="n">
         <v>-2</v>
       </c>
-      <c r="K13" s="2" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>Bottoming tail (new low rejected), tail 59% of range | Major pivot zone (3 touches, 1.5x vol) @ 414.52 | High-volume node @ 423.56 | Tagged lower Bollinger band | Extended 2.9 ATR from 20 EMA | Volume 1.6x average</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>EQIX</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>1028.83</v>
-      </c>
-      <c r="H14" s="7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I14" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 65% of range | Fib 78.6% retrace @ 1078.54 | Major pivot zone (8 touches, 1.8x vol) @ 1043.32 | High-volume node @ 1073.68 | Tagged upper Bollinger band</t>
-        </is>
-      </c>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N14" s="10" t="inlineStr">
+      <c r="K14" s="2" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Bottoming tail (new low rejected), tail 56% of range | Major pivot zone (3 touches, 1.5x vol) @ 414.52 | High-volume node @ 423.56 | Tagged lower Bollinger band | Extended 2.9 ATR from 20 EMA | Volume 1.6x average</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1301,7 +1301,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1309,13 +1309,13 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>At risk</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.882</v>
+        <v>0.504</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>5.75</v>
@@ -1324,87 +1324,87 @@
         <v>5</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>176.09</v>
+        <v>256.61</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>2.27</v>
+        <v>-1.29</v>
       </c>
       <c r="I15" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Bottoming tail (new low rejected), tail 50% of range | Time count: 9 down bars since the last up bar | Trendline (falling support) @ 253.65 | Bullish RSI divergence (35) | Tagged lower Bollinger band</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>UHS</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>176.52</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I16" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="J15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="J16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>Bottoming tail, tail 59% of range | Fib 38.2% retrace @ 171.84 | Major pivot zone (4 touches, 1.5x vol) @ 174.58 | High-volume node @ 168.36 | Tagged lower Bollinger band</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>LLY</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>0.527</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>1368.6</v>
-      </c>
-      <c r="H16" s="7" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>74</v>
-      </c>
-      <c r="L16" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 51% of range | Fib 1.27 extension @ 1424.82 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 1.6x average</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N16" s="10" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1413,7 +1413,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>ALGN</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -1421,38 +1421,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>0.096</v>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>0.5570000000000001</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>5.5</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>153.41</v>
+        <v>1368.15</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-0.14</v>
+        <v>6.2</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="L17" s="9" t="inlineStr">
-        <is>
-          <t>Doji (indecision at extreme) | Time count: 8 up bars since the last down bar | Fib 38.2% retrace @ 158.27 | Major pivot zone (3 touches, 2.4x vol) @ 154.53 | Volume 1.7x average</t>
+        <v>74</v>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 51% of range | Fib 1.27 extension @ 1424.82 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 1.6x average</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
@@ -1460,7 +1460,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N17" s="10" t="inlineStr">
+      <c r="N17" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1469,7 +1469,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>ALGN</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -1482,8 +1482,8 @@
           <t>At risk</t>
         </is>
       </c>
-      <c r="D18" s="8" t="n">
-        <v>0.621</v>
+      <c r="D18" s="9" t="n">
+        <v>0.012</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>5.5</v>
@@ -1492,23 +1492,23 @@
         <v>5</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>182.02</v>
+        <v>153.94</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>1.47</v>
+        <v>0.21</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>16</v>
+        <v>-2</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="L18" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 54% of range | Time count: TD setup 15 | Prior pivot (1 touch, 1.7x vol) @ 185.27 | RSI overbought (71) | Extended 3.4 ATR from 20 EMA</t>
+        <v>58.1</v>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | Time count: 8 up bars since the last down bar | Fib 38.2% retrace @ 158.27 | Major pivot zone (3 touches, 2.4x vol) @ 154.53 | Volume 1.7x average</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
@@ -1516,7 +1516,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N18" s="10" t="inlineStr">
+      <c r="N18" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1525,7 +1525,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>LDOS</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -1533,13 +1533,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>0.912</v>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>0.844</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>5.5</v>
@@ -1548,10 +1548,10 @@
         <v>5</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>140.79</v>
+        <v>181.66</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>0.85</v>
+        <v>1.27</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>16</v>
@@ -1560,11 +1560,11 @@
         <v>1</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="L19" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 58% of range | Time count: TD setup 15 | Prior pivot (1 touch, 0.9x vol) @ 142.02 | RSI overbought (73) | Extended 3.4 ATR from 20 EMA</t>
+        <v>70.5</v>
+      </c>
+      <c r="L19" s="10" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 54% of range | Time count: TD setup 15 | Prior pivot (1 touch, 1.7x vol) @ 185.27 | RSI overbought (71) | Extended 3.4 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
@@ -1572,7 +1572,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N19" s="10" t="inlineStr">
+      <c r="N19" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1581,7 +1581,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>LDOS</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -1594,8 +1594,8 @@
           <t>Likely to confirm</t>
         </is>
       </c>
-      <c r="D20" s="8" t="n">
-        <v>0.996</v>
+      <c r="D20" s="9" t="n">
+        <v>0.9350000000000001</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>5.5</v>
@@ -1604,23 +1604,23 @@
         <v>5</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>105.19</v>
+        <v>140.84</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>-0.34</v>
+        <v>0.89</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="L20" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 48% of range | Time count: 10 bars without a lower low | RSI overbought (73) | Tagged upper Bollinger band | Extended 4.1 ATR from 20 EMA</t>
+        <v>72.90000000000001</v>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 58% of range | Time count: TD setup 15 | Prior pivot (1 touch, 0.9x vol) @ 142.02 | RSI overbought (73) | Extended 3.4 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
@@ -1628,7 +1628,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N20" s="10" t="inlineStr">
+      <c r="N20" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1637,7 +1637,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>NSC</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -1645,13 +1645,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>0.872</v>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0.996</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>5.5</v>
@@ -1660,23 +1660,23 @@
         <v>5</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>340.59</v>
+        <v>105.37</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.74</v>
+        <v>-0.17</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="L21" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 57% of range | Major pivot zone (1 touch, 2.1x vol) @ 343.63 | Bearish RSI divergence (66) | Tagged upper Bollinger band | Extended 2.8 ATR from 20 EMA</t>
+        <v>73.90000000000001</v>
+      </c>
+      <c r="L21" s="10" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 47% of range | Time count: 10 bars without a lower low | RSI overbought (74) | Tagged upper Bollinger band | Extended 4.1 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
@@ -1684,7 +1684,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N21" s="10" t="inlineStr">
+      <c r="N21" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1693,7 +1693,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>NSC</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -1701,13 +1701,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>0.517</v>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>At risk</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>0.6870000000000001</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>5.5</v>
@@ -1716,143 +1716,143 @@
         <v>5</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>165.12</v>
+        <v>341.47</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>-0.12</v>
+        <v>1</v>
       </c>
       <c r="I22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="L22" s="10" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 57% of range | Major pivot zone (1 touch, 2.1x vol) @ 343.63 | Bearish RSI divergence (66) | Tagged upper Bollinger band | Extended 2.8 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>RVTY</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>165.1</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="I23" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="J22" s="7" t="n">
+      <c r="J23" s="7" t="n">
         <v>-1</v>
       </c>
-      <c r="K22" s="7" t="n">
+      <c r="K23" s="7" t="n">
         <v>72.2</v>
       </c>
-      <c r="L22" s="9" t="inlineStr">
+      <c r="L23" s="10" t="inlineStr">
         <is>
           <t>Topping tail, tail 47% of range | Time count: 7 up bars since the last down bar | Prior pivot (1 touch, 1.4x vol) @ 166.18 | RSI overbought (72) | Tagged upper Bollinger band</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N22" s="10" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N23" s="11" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>0.596</v>
-      </c>
-      <c r="E23" s="2" t="n">
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="E24" s="2" t="n">
         <v>5.5</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G23" s="2" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I23" s="2" t="n">
+      <c r="G24" s="2" t="n">
+        <v>65.63</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I24" s="2" t="n">
         <v>-12</v>
       </c>
-      <c r="J23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="J24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>Bottoming tail (new low rejected), tail 74% of range | Time count: TD setup 11 | Prior pivot (1 touch, 1.4x vol) @ 65.41 | Trendline (falling support) @ 64.82 | Tagged lower Bollinger band</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N23" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>BLK</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>1169.05</v>
-      </c>
-      <c r="H24" s="7" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I24" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="L24" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 73% of range | Time count: 7 up bars since the last down bar | Prior pivot (2 touches, 1.0x vol) @ 1180.97 | Tagged upper Bollinger band | Extended 2.5 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M24" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N24" s="10" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1861,7 +1861,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>CRL</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -1874,33 +1874,33 @@
           <t>At risk</t>
         </is>
       </c>
-      <c r="D25" s="8" t="n">
-        <v>0.319</v>
+      <c r="D25" s="9" t="n">
+        <v>0.745</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="F25" s="7" t="n">
         <v>5</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>375.41</v>
+        <v>1171.11</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>0.38</v>
+        <v>1.14</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="L25" s="9" t="inlineStr">
-        <is>
-          <t>Doji (indecision at extreme) | Time count: 8 up bars since the last down bar | RSI overbought (81) | Tagged upper Bollinger band | Extended 3.8 ATR from 20 EMA</t>
+        <v>66.59999999999999</v>
+      </c>
+      <c r="L25" s="10" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 66% of range | Time count: 7 up bars since the last down bar | Prior pivot (2 touches, 1.0x vol) @ 1180.97 | Tagged upper Bollinger band | Extended 2.5 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
@@ -1908,7 +1908,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N25" s="10" t="inlineStr">
+      <c r="N25" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1917,7 +1917,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>TFC</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -1925,38 +1925,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>0.903</v>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>At risk</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0.318</v>
       </c>
       <c r="E26" s="7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="F26" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F26" s="7" t="n">
-        <v>4</v>
-      </c>
       <c r="G26" s="7" t="n">
-        <v>62.65</v>
+        <v>49.28</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>-5.58</v>
+        <v>1.77</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="L26" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail, tail 70% of range | Major pivot zone (4 touches, 1.8x vol) @ 65.08 | High-volume node @ 63.60 | Trendline (rising resistance) @ 64.96</t>
+        <v>61.4</v>
+      </c>
+      <c r="L26" s="10" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | Fib 50.0% retrace @ 49.37 | Major pivot zone (7 touches, 1.4x vol) @ 49.39 | High-volume node @ 49.73 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -1964,7 +1964,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N26" s="10" t="inlineStr">
+      <c r="N26" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1973,7 +1973,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>KEY</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -1981,13 +1981,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D27" s="8" t="n">
-        <v>0.544</v>
+      <c r="D27" s="9" t="n">
+        <v>0.879</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>5</v>
@@ -1996,23 +1996,23 @@
         <v>4</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>21.44</v>
+        <v>62.83</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>1.16</v>
+        <v>-5.31</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="L27" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 52% of range | Fib 50.0% retrace @ 21.65 | Major pivot zone (3 touches, 1.3x vol) @ 21.45 | High-volume node @ 21.64</t>
+        <v>47.4</v>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
+          <t>Topping tail, tail 65% of range | Major pivot zone (4 touches, 1.8x vol) @ 65.08 | High-volume node @ 63.60 | Trendline (rising resistance) @ 64.96</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -2020,7 +2020,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N27" s="10" t="inlineStr">
+      <c r="N27" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2029,7 +2029,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>KEY</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -2037,13 +2037,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D28" s="8" t="n">
-        <v>0.577</v>
+      <c r="D28" s="9" t="n">
+        <v>0.572</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>5</v>
@@ -2052,23 +2052,23 @@
         <v>4</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>81.98999999999999</v>
+        <v>21.47</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="L28" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 80% of range | Fib 38.2% retrace @ 82.04 | Major pivot zone (3 touches, 2.4x vol) @ 82.62 | Volume POC @ 82.88</t>
+        <v>64.7</v>
+      </c>
+      <c r="L28" s="10" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 52% of range | Fib 50.0% retrace @ 21.65 | Major pivot zone (3 touches, 1.3x vol) @ 21.45 | High-volume node @ 21.64</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -2076,7 +2076,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N28" s="10" t="inlineStr">
+      <c r="N28" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2093,13 +2093,13 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.635</v>
+        <v>0.776</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>5</v>
@@ -2108,10 +2108,10 @@
         <v>4</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>27.97</v>
+        <v>28.01</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>0.77</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I29" s="2" t="n">
         <v>-2</v>
@@ -2120,11 +2120,11 @@
         <v>1</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>52</v>
+        <v>52.3</v>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>Bottoming tail (new low rejected), tail 56% of range | Fib 50.0% retrace @ 27.22 | Major pivot zone (4 touches, 4.9x vol) @ 27.85 | High-volume node @ 27.83</t>
+          <t>Bottoming tail (new low rejected), tail 62% of range | Fib 50.0% retrace @ 27.22 | Major pivot zone (4 touches, 4.9x vol) @ 27.85 | High-volume node @ 27.83</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.945</v>
+        <v>0.982</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>5</v>
@@ -2164,10 +2164,10 @@
         <v>4</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>92.95</v>
+        <v>93.08</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="I30" s="2" t="n">
         <v>-4</v>
@@ -2176,7 +2176,7 @@
         <v>1</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>56.8</v>
+        <v>57.1</v>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
@@ -2205,13 +2205,13 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.993</v>
+        <v>0.998</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>5</v>
@@ -2220,10 +2220,10 @@
         <v>4</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>239.02</v>
+        <v>238.93</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="I31" s="2" t="n">
         <v>2</v>
@@ -2232,7 +2232,7 @@
         <v>5</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>60.5</v>
+        <v>60.4</v>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>HBAN</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -2261,13 +2261,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D32" s="8" t="n">
-        <v>0.622</v>
+      <c r="D32" s="9" t="n">
+        <v>0.771</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>4.75</v>
@@ -2276,23 +2276,23 @@
         <v>4</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>208.16</v>
+        <v>15.93</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>2</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="L32" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 60% of range | Major pivot zone (8 touches, 1.8x vol) @ 210.88 | Trendline (falling resistance) @ 209.74 | Tagged upper Bollinger band</t>
+        <v>58.4</v>
+      </c>
+      <c r="L32" s="10" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 59% of range | Time count: 8 up bars since the last down bar | Fib 38.2% retrace @ 16.19 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -2300,7 +2300,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N32" s="10" t="inlineStr">
+      <c r="N32" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2309,7 +2309,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>HBAN</t>
+          <t>IRM</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -2317,13 +2317,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D33" s="8" t="n">
-        <v>0.845</v>
+      <c r="D33" s="9" t="n">
+        <v>0.573</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>4.75</v>
@@ -2332,23 +2332,23 @@
         <v>4</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>15.9</v>
+        <v>118.33</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>1.31</v>
+        <v>2.3</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="L33" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 59% of range | Time count: 8 up bars since the last down bar | Fib 38.2% retrace @ 16.19 | Tagged upper Bollinger band</t>
+        <v>59.4</v>
+      </c>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 55% of range | Fib 50.0% retrace @ 120.42 | Major pivot zone (7 touches, 1.6x vol) @ 118.99 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
@@ -2356,7 +2356,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N33" s="10" t="inlineStr">
+      <c r="N33" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2365,7 +2365,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>IRM</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -2373,13 +2373,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C34" s="11" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D34" s="8" t="n">
-        <v>0.756</v>
+      <c r="D34" s="9" t="n">
+        <v>0.604</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>4.75</v>
@@ -2388,23 +2388,23 @@
         <v>4</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>117.95</v>
+        <v>113.24</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>1.97</v>
+        <v>1.25</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="L34" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 71% of range | Fib 50.0% retrace @ 120.42 | Major pivot zone (7 touches, 1.6x vol) @ 118.99 | Tagged upper Bollinger band</t>
+        <v>58.7</v>
+      </c>
+      <c r="L34" s="10" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | Time count: 7 up bars since the last down bar | Major pivot zone (3 touches, 1.0x vol) @ 114.93 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
@@ -2412,7 +2412,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N34" s="10" t="inlineStr">
+      <c r="N34" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2421,7 +2421,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>WMB</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -2429,13 +2429,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="n">
-        <v>0.649</v>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>At risk</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0.701</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>4.75</v>
@@ -2444,23 +2444,23 @@
         <v>4</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>113.16</v>
+        <v>75.06</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="L35" s="9" t="inlineStr">
-        <is>
-          <t>Doji (indecision at extreme) | Time count: 7 up bars since the last down bar | Major pivot zone (3 touches, 1.0x vol) @ 114.93 | Tagged upper Bollinger band</t>
+        <v>60.1</v>
+      </c>
+      <c r="L35" s="10" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 68% of range | Fib 78.6% retrace @ 76.45 | Major pivot zone (10 touches, 1.5x vol) @ 75.24 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
@@ -2468,63 +2468,63 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N35" s="10" t="inlineStr">
+      <c r="N35" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>WMB</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="n">
-        <v>0.768</v>
-      </c>
-      <c r="E36" s="7" t="n">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="E36" s="2" t="n">
         <v>4.75</v>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F36" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G36" s="7" t="n">
-        <v>74.94</v>
-      </c>
-      <c r="H36" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I36" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J36" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="L36" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 72% of range | Fib 78.6% retrace @ 76.45 | Major pivot zone (10 touches, 1.5x vol) @ 75.24 | Tagged upper Bollinger band</t>
-        </is>
-      </c>
-      <c r="M36" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N36" s="10" t="inlineStr">
+      <c r="G36" s="2" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>Bottoming tail (new low rejected), tail 59% of range | Time count: TD setup 9 | Trendline (falling support) @ 60.70 | Extended 3.0 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N36" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2533,7 +2533,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2541,13 +2541,13 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>0.578</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>4.75</v>
@@ -2556,23 +2556,23 @@
         <v>4</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>62.08</v>
+        <v>240.37</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>0.14</v>
+        <v>-5.28</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>-10</v>
+        <v>-1</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>30.6</v>
+        <v>40</v>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>Bottoming tail (new low rejected), tail 57% of range | Time count: TD setup 9 | Trendline (falling support) @ 60.70 | Extended 3.0 ATR from 20 EMA</t>
+          <t>Bottoming tail (new low rejected), tail 53% of range | Fib 61.8% retrace @ 228.55 | Major pivot zone (3 touches, 1.4x vol) @ 238.69 | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
           <t>Likely to confirm</t>
         </is>
       </c>
-      <c r="D38" s="8" t="n">
+      <c r="D38" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E38" s="7" t="n">
@@ -2612,10 +2612,10 @@
         <v>5</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>23.75</v>
+        <v>23.73</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>-6.74</v>
+        <v>-6.79</v>
       </c>
       <c r="I38" s="7" t="n">
         <v>-2</v>
@@ -2624,9 +2624,9 @@
         <v>-1</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="L38" s="9" t="inlineStr">
+        <v>42.2</v>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
         <is>
           <t>Bearish engulfing | Prior pivot (2 touches, 0.9x vol) @ 25.84 | Bearish RSI divergence (42) | Tagged upper Bollinger band | Volume 2.0x average</t>
         </is>
@@ -2636,7 +2636,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N38" s="10" t="inlineStr">
+      <c r="N38" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2658,8 +2658,8 @@
           <t>At risk</t>
         </is>
       </c>
-      <c r="D39" s="8" t="n">
-        <v>0.141</v>
+      <c r="D39" s="9" t="n">
+        <v>0.122</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>4.5</v>
@@ -2668,10 +2668,10 @@
         <v>4</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>51.35</v>
+        <v>51.32</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
       <c r="I39" s="7" t="n">
         <v>-1</v>
@@ -2680,11 +2680,11 @@
         <v>2</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="L39" s="9" t="inlineStr">
-        <is>
-          <t>Doji (indecision at extreme) | Time count: TD setup 20 | Trendline (rising resistance) @ 51.68 | RSI overbought (71)</t>
+        <v>70.40000000000001</v>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | Time count: TD setup 20 | Trendline (rising resistance) @ 51.68 | RSI overbought (70)</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
@@ -2692,7 +2692,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N39" s="10" t="inlineStr">
+      <c r="N39" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2709,13 +2709,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>0.788</v>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>At risk</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>0.731</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>4.5</v>
@@ -2724,10 +2724,10 @@
         <v>4</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>274.73</v>
+        <v>275.11</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="I40" s="7" t="n">
         <v>9</v>
@@ -2736,9 +2736,9 @@
         <v>4</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="L40" s="9" t="inlineStr">
+        <v>63</v>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
         <is>
           <t>Topping tail (new high rejected), tail 61% of range | Time count: TD setup 8 | Prior pivot (1 touch, 1.0x vol) @ 281.07 | Tagged upper Bollinger band</t>
         </is>
@@ -2748,7 +2748,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N40" s="10" t="inlineStr">
+      <c r="N40" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2765,13 +2765,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="n">
-        <v>0.8070000000000001</v>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>0.73</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>4.5</v>
@@ -2780,10 +2780,10 @@
         <v>4</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>60.41</v>
+        <v>60.49</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="I41" s="7" t="n">
         <v>1</v>
@@ -2792,11 +2792,11 @@
         <v>1</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="L41" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 73% of range | Time count: 7 up bars since the last down bar | Prior pivot (1 touch, 0.8x vol) @ 60.89 | Tagged upper Bollinger band</t>
+        <v>60.4</v>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 65% of range | Time count: 7 up bars since the last down bar | Prior pivot (1 touch, 0.8x vol) @ 60.89 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
@@ -2804,7 +2804,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N41" s="10" t="inlineStr">
+      <c r="N41" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2821,13 +2821,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D42" s="8" t="n">
-        <v>0.8169999999999999</v>
+      <c r="D42" s="9" t="n">
+        <v>0.745</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>4.25</v>
@@ -2836,10 +2836,10 @@
         <v>4</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>65.09999999999999</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="I42" s="7" t="n">
         <v>-2</v>
@@ -2848,9 +2848,9 @@
         <v>1</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="L42" s="9" t="inlineStr">
+        <v>59.6</v>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
         <is>
           <t>Topping tail, tail 62% of range | Fib 50.0% retrace @ 65.85 | Prior pivot (2 touches, 1.4x vol) @ 65.45 | High-volume node @ 65.93</t>
         </is>
@@ -2860,7 +2860,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N42" s="10" t="inlineStr">
+      <c r="N42" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2882,8 +2882,8 @@
           <t>At risk</t>
         </is>
       </c>
-      <c r="D43" s="8" t="n">
-        <v>0.296</v>
+      <c r="D43" s="9" t="n">
+        <v>0.25</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>4.25</v>
@@ -2892,10 +2892,10 @@
         <v>4</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>119.39</v>
+        <v>119.41</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="I43" s="7" t="n">
         <v>25</v>
@@ -2906,7 +2906,7 @@
       <c r="K43" s="7" t="n">
         <v>88.59999999999999</v>
       </c>
-      <c r="L43" s="9" t="inlineStr">
+      <c r="L43" s="10" t="inlineStr">
         <is>
           <t>Doji (indecision at extreme) | Time count: TD setup 24 | RSI overbought (89) | Extended 4.5 ATR from 20 EMA</t>
         </is>
@@ -2916,7 +2916,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N43" s="10" t="inlineStr">
+      <c r="N43" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2938,8 +2938,8 @@
           <t>At risk</t>
         </is>
       </c>
-      <c r="D44" s="8" t="n">
-        <v>0.007</v>
+      <c r="D44" s="9" t="n">
+        <v>0.002</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>4.25</v>
@@ -2948,10 +2948,10 @@
         <v>4</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>222.8</v>
+        <v>222.73</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="I44" s="7" t="n">
         <v>12</v>
@@ -2960,9 +2960,9 @@
         <v>2</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="L44" s="9" t="inlineStr">
+        <v>66.5</v>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
         <is>
           <t>Doji (indecision at extreme) | Time count: TD setup 11 | Fib 50.0% retrace @ 224.11 | Prior pivot (2 touches, 1.5x vol) @ 221.25</t>
         </is>
@@ -2972,7 +2972,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N44" s="10" t="inlineStr">
+      <c r="N44" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2989,13 +2989,13 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D45" s="4" t="n">
-        <v>0.901</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>4.25</v>
@@ -3004,7 +3004,7 @@
         <v>4</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>328.54</v>
+        <v>328.52</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>2.41</v>
@@ -3037,7 +3037,7 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>CASY</t>
+          <t>AZO</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -3045,13 +3045,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C46" s="11" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D46" s="8" t="n">
-        <v>0.877</v>
+      <c r="D46" s="9" t="n">
+        <v>0.9330000000000001</v>
       </c>
       <c r="E46" s="7" t="n">
         <v>4</v>
@@ -3060,23 +3060,23 @@
         <v>3</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>675.41</v>
+        <v>3132.97</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>0.8</v>
+        <v>-0.75</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="L46" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail, tail 47% of range | Major pivot zone (2 touches, 6.6x vol) @ 690.37 | High-volume node @ 681.51</t>
+        <v>58.3</v>
+      </c>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>Bearish engulfing | Fib 61.8% retrace @ 3243.91 | Major pivot zone (6 touches, 2.2x vol) @ 3190.97</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
@@ -3084,7 +3084,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N46" s="10" t="inlineStr">
+      <c r="N46" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -3093,7 +3093,7 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>CIEN</t>
+          <t>CASY</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -3101,13 +3101,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D47" s="8" t="n">
-        <v>0.554</v>
+      <c r="D47" s="9" t="n">
+        <v>0.885</v>
       </c>
       <c r="E47" s="7" t="n">
         <v>4</v>
@@ -3116,23 +3116,23 @@
         <v>3</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>350.29</v>
+        <v>676.05</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>-3.56</v>
+        <v>0.9</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="L47" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail, tail 53% of range | Major pivot zone (6 touches, 1.4x vol) @ 366.58 | Volume POC @ 351.24</t>
+        <v>51.4</v>
+      </c>
+      <c r="L47" s="10" t="inlineStr">
+        <is>
+          <t>Topping tail, tail 47% of range | Major pivot zone (2 touches, 6.6x vol) @ 690.37 | High-volume node @ 681.51</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
@@ -3140,7 +3140,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N47" s="10" t="inlineStr">
+      <c r="N47" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -3149,7 +3149,7 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>CMI</t>
+          <t>CIEN</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -3157,13 +3157,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C48" s="11" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D48" s="8" t="n">
-        <v>0.513</v>
+      <c r="D48" s="9" t="n">
+        <v>0.512</v>
       </c>
       <c r="E48" s="7" t="n">
         <v>4</v>
@@ -3172,23 +3172,23 @@
         <v>3</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>514.91</v>
+        <v>350.85</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>-3.1</v>
+        <v>-3.4</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="J48" s="7" t="n">
         <v>-1</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="L48" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail, tail 69% of range | Major pivot zone (8 touches, 3.3x vol) @ 515.01 | Volume POC @ 524.39</t>
+        <v>47.2</v>
+      </c>
+      <c r="L48" s="10" t="inlineStr">
+        <is>
+          <t>Topping tail, tail 51% of range | Major pivot zone (6 touches, 1.4x vol) @ 366.58 | Volume POC @ 351.24</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
@@ -3196,7 +3196,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N48" s="10" t="inlineStr">
+      <c r="N48" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -3205,7 +3205,7 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>GNRC</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -3213,13 +3213,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C49" s="11" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D49" s="8" t="n">
-        <v>0.55</v>
+      <c r="D49" s="9" t="n">
+        <v>0.752</v>
       </c>
       <c r="E49" s="7" t="n">
         <v>4</v>
@@ -3228,87 +3228,87 @@
         <v>3</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>204.03</v>
+        <v>82.14</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J49" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="7" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="L49" s="10" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 66% of range | Major pivot zone (3 touches, 2.4x vol) @ 82.62 | Volume POC @ 82.88</t>
+        </is>
+      </c>
+      <c r="M49" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N49" s="11" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="E50" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K49" s="7" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="L49" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 79% of range | Major pivot zone (2 touches, 3.0x vol) @ 211.79 | Volume POC @ 204.31</t>
-        </is>
-      </c>
-      <c r="M49" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N49" s="10" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>UNH</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D50" s="8" t="n">
-        <v>0.902</v>
-      </c>
-      <c r="E50" s="7" t="n">
+      <c r="F50" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F50" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G50" s="7" t="n">
-        <v>406.38</v>
-      </c>
-      <c r="H50" s="7" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="I50" s="7" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J50" s="7" t="n">
-        <v>-5</v>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="L50" s="9" t="inlineStr">
-        <is>
-          <t>Bearish engulfing | Fib 50.0% retrace @ 410.70 | Major pivot zone (2 touches, 2.0x vol) @ 411.73</t>
-        </is>
-      </c>
-      <c r="M50" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N50" s="10" t="inlineStr">
+      <c r="G50" s="2" t="n">
+        <v>181.15</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>Bottoming tail, tail 67% of range | High-volume node @ 173.84 | Trendline (rising support) @ 179.82 | Volume 2.2x average</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N50" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -3317,7 +3317,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3325,38 +3325,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D51" s="4" t="n">
-        <v>0.414</v>
+        <v>1</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>360.3</v>
+        <v>657.05</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>-1.43</v>
+        <v>2.56</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>26.2</v>
+        <v>52.8</v>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>Doji (indecision at extreme) | RSI oversold (26) | Tagged lower Bollinger band | Extended 4.2 ATR from 20 EMA | Volume 2.0x average</t>
+          <t>Bullish engulfing | Fib 50.0% retrace @ 616.05 | Major pivot zone (3 touches, 1.5x vol) @ 619.72</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -3373,7 +3373,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3381,38 +3381,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C52" s="11" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>0.522</v>
+        <v>0.93</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>179.92</v>
+        <v>150.99</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>6.15</v>
+        <v>2.06</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>44.5</v>
+        <v>36.1</v>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>Bottoming tail, tail 67% of range | High-volume node @ 173.84 | Trendline (rising support) @ 179.82 | Volume 2.1x average</t>
+          <t>Bottoming tail, tail 72% of range | Major pivot zone (2 touches, 2.4x vol) @ 149.50 | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -3429,7 +3429,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3437,38 +3437,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>At risk</t>
         </is>
       </c>
       <c r="D53" s="4" t="n">
-        <v>0.995</v>
+        <v>0.159</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>654.61</v>
+        <v>183.74</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>2.18</v>
+        <v>-1.59</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>51.7</v>
+        <v>44.2</v>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>Bullish engulfing | Fib 50.0% retrace @ 616.05 | Major pivot zone (3 touches, 1.5x vol) @ 619.72</t>
+          <t>Doji (indecision at extreme) | Fib 38.2% retrace @ 185.98 | Major pivot zone (10 touches, 2.3x vol) @ 180.72</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -3485,7 +3485,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3493,38 +3493,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>At risk</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>0.805</v>
+        <v>0.134</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>150.59</v>
+        <v>128.89</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>1.79</v>
+        <v>-1.76</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>-7</v>
+        <v>2</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>35.5</v>
+        <v>39.5</v>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>Bottoming tail, tail 71% of range | Major pivot zone (2 touches, 2.4x vol) @ 149.50 | Tagged lower Bollinger band</t>
+          <t>Doji (indecision at extreme) | Major pivot zone (2 touches, 2.0x vol) @ 125.03 | Volume POC @ 129.44</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>WAB</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3549,13 +3549,13 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D55" s="4" t="n">
-        <v>0.177</v>
+        <v>0.951</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>3.5</v>
@@ -3564,23 +3564,23 @@
         <v>3</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>183.6</v>
+        <v>284.61</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>-1.67</v>
+        <v>0.86</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>44.1</v>
+        <v>50.9</v>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>Doji (indecision at extreme) | Fib 38.2% retrace @ 185.98 | Major pivot zone (10 touches, 2.3x vol) @ 180.72</t>
+          <t>Bullish engulfing | Fib 50.0% retrace @ 278.61 | Trendline (rising support) @ 277.12</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -3597,7 +3597,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3605,38 +3605,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C56" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>0.132</v>
+        <v>0.714</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>128.61</v>
+        <v>102.47</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>-1.97</v>
+        <v>0.05</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>39.3</v>
+        <v>26.2</v>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>Doji (indecision at extreme) | Major pivot zone (2 touches, 2.0x vol) @ 125.03 | Volume POC @ 129.44</t>
+          <t>Bottoming tail, tail 64% of range | RSI oversold (26) | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>WAB</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3661,38 +3661,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C57" s="11" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D57" s="4" t="n">
-        <v>0.782</v>
+        <v>0.908</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>283.72</v>
+        <v>151.41</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>0.55</v>
+        <v>1.64</v>
       </c>
       <c r="I57" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J57" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J57" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="K57" s="2" t="n">
-        <v>49.8</v>
+        <v>46.2</v>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>Bullish engulfing | Fib 50.0% retrace @ 278.61 | Trendline (rising support) @ 277.12</t>
+          <t>Bottoming tail, tail 50% of range | Fib 38.2% retrace @ 149.71 | Prior pivot (1 touch, 1.1x vol) @ 150.46</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -3709,7 +3709,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>HUBB</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3717,38 +3717,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C58" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>0.261</v>
+        <v>1</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>433.62</v>
+        <v>40.5</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>-0.85</v>
+        <v>1.48</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>35.8</v>
+        <v>31.5</v>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>Doji (indecision at extreme) | Major pivot zone (3 touches, 1.1x vol) @ 438.28 | Tagged lower Bollinger band</t>
+          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 38.34) | Bottoming tail (new low rejected), tail 59% of range | Major pivot zone (1 touch, 2.5x vol) @ 38.32 | Trendline (falling support) @ 37.65 | Bullish RSI divergence (31) | Tagged lower Bollinger band | Extended 3.0 ATR from 20 EMA | Volume 2.3x average</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>GPC</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3773,38 +3773,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>At risk</t>
         </is>
       </c>
       <c r="D59" s="4" t="n">
-        <v>0.847</v>
+        <v>0.989</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>3.25</v>
+        <v>5.75</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>151.33</v>
+        <v>121.57</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>1.59</v>
+        <v>0.14</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>46.1</v>
+        <v>38.7</v>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>Bottoming tail, tail 50% of range | Fib 38.2% retrace @ 149.71 | Prior pivot (1 touch, 1.1x vol) @ 150.46</t>
+          <t>Setup from 2 bars ago, still near entry (-0.1 ATR since signal; stop beyond 120.18) | Bottoming tail (new low rejected), tail 59% of range | Fib 38.2% retrace @ 119.82 | Major pivot zone (4 touches, 1.8x vol) @ 121.77 | Trendline (falling support) @ 121.46 | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3829,38 +3829,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C60" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>39.82</v>
+        <v>177.94</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>-0.23</v>
+        <v>2.33</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>31.5</v>
+        <v>43.1</v>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (-0.0 ATR since signal; stop beyond 38.34) | Bottoming tail (new low rejected), tail 59% of range | Major pivot zone (1 touch, 2.5x vol) @ 38.32 | Trendline (falling support) @ 37.65 | Bullish RSI divergence (31) | Tagged lower Bollinger band | Extended 3.0 ATR from 20 EMA | Volume 2.3x average</t>
+          <t>Setup from 1 bar ago, still near entry (+0.8 ATR since signal; stop beyond 170.14) | Bullish engulfing | Major pivot zone (5 touches, 1.3x vol) @ 172.11 | Trendline (falling support) @ 170.53 | Bullish RSI divergence (43) | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GPC</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3885,38 +3885,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C61" s="11" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
       <c r="D61" s="4" t="n">
-        <v>0.986</v>
+        <v>1</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>121.75</v>
+        <v>254.14</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>0.3</v>
+        <v>0.13</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>-7</v>
+        <v>-15</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>38.7</v>
+        <v>31.1</v>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>Setup from 2 bars ago, still near entry (-0.0 ATR since signal; stop beyond 120.18) | Bottoming tail (new low rejected), tail 59% of range | Fib 38.2% retrace @ 119.82 | Major pivot zone (4 touches, 1.8x vol) @ 121.77 | Trendline (falling support) @ 121.46 | Tagged lower Bollinger band</t>
+          <t>Setup from 2 bars ago, still near entry (+0.9 ATR since signal; stop beyond 235.21) | Bottoming tail, tail 87% of range | Time count: TD setup 14 | Prior pivot (2 touches, 1.1x vol) @ 241.07 | High-volume node @ 234.92 | Extended 2.8 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>FDXF</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3950,29 +3950,29 @@
         <v>1</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>177.97</v>
+        <v>107.9</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>2.35</v>
+        <v>-0.4</v>
       </c>
       <c r="I62" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J62" s="2" t="n">
         <v>-4</v>
       </c>
-      <c r="J62" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="K62" s="2" t="n">
-        <v>43.1</v>
+        <v>38.5</v>
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.9 ATR since signal; stop beyond 170.14) | Bullish engulfing | Major pivot zone (5 touches, 1.3x vol) @ 172.11 | Trendline (falling support) @ 170.53 | Bullish RSI divergence (43) | Tagged lower Bollinger band</t>
+          <t>Setup from 1 bar ago, still near entry (-0.1 ATR since signal; stop beyond 103.48) | Bottoming tail (new low rejected), tail 90% of range | Prior pivot (2 touches, 1.8x vol) @ 106.96 | Trendline (falling support) @ 103.62 | Bullish RSI divergence (38) | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C63" s="11" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
@@ -4006,29 +4006,29 @@
         <v>1</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>252.62</v>
+        <v>892.8200000000001</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>-0.47</v>
+        <v>1.68</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>-15</v>
+        <v>1</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>31.1</v>
+        <v>43</v>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>Setup from 2 bars ago, still near entry (+0.8 ATR since signal; stop beyond 235.21) | Bottoming tail, tail 87% of range | Time count: TD setup 14 | Prior pivot (2 touches, 1.1x vol) @ 241.07 | High-volume node @ 234.92 | Extended 2.8 ATR from 20 EMA</t>
+          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 836.24) | Bottoming tail, tail 72% of range | Time count: TD setup 10 | Major pivot zone (6 touches, 2.1x vol) @ 870.38 | Volume 2.3x average</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -4045,7 +4045,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>FDXF</t>
+          <t>HSIC</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4053,9 +4053,9 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C64" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D64" s="4" t="n">
@@ -4065,26 +4065,26 @@
         <v>5</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>107.44</v>
+        <v>86.19</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>-0.82</v>
+        <v>1.45</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>38.5</v>
+        <v>48.1</v>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (-0.2 ATR since signal; stop beyond 103.48) | Bottoming tail (new low rejected), tail 90% of range | Prior pivot (2 touches, 1.8x vol) @ 106.96 | Trendline (falling support) @ 103.62 | Bullish RSI divergence (38) | Tagged lower Bollinger band</t>
+          <t>Setup from 1 bar ago, still near entry (+0.7 ATR since signal; stop beyond 83.97) | Bullish engulfing | Fib 38.2% retrace @ 83.21 | Major pivot zone (1 touch, 1.9x vol) @ 84.15 | High-volume node @ 84.67</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -4101,7 +4101,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C65" s="11" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
@@ -4124,23 +4124,23 @@
         <v>4</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>887.51</v>
+        <v>247.56</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>1.08</v>
+        <v>1.9</v>
       </c>
       <c r="I65" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.2 ATR since signal; stop beyond 836.24) | Bottoming tail, tail 72% of range | Time count: TD setup 10 | Major pivot zone (6 touches, 2.1x vol) @ 870.38 | Volume 2.3x average</t>
+          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 228.81) | Bottoming tail, tail 86% of range | Time count: TD setup 14 | Major pivot zone (5 touches, 3.3x vol) @ 226.83 | Volume 3.3x average</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -4157,7 +4157,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4165,7 +4165,7 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C66" s="11" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
@@ -4174,29 +4174,29 @@
         <v>1</v>
       </c>
       <c r="E66" s="2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F66" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F66" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="G66" s="2" t="n">
-        <v>85.06999999999999</v>
+        <v>57.24</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>3.14</v>
+        <v>1.23</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>53.6</v>
+        <v>52.4</v>
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+1.0 ATR since signal; stop beyond 79.25) | Bottoming tail, tail 48% of range | Fib 61.8% retrace @ 78.36 | Major pivot zone (8 touches, 1.6x vol) @ 78.06 | Volume POC @ 80.70</t>
+          <t>Setup from 2 bars ago, still near entry (+0.8 ATR since signal; stop beyond 54.34) | Bottoming tail (new low rejected), tail 47% of range | Fib 38.2% retrace @ 53.99 | Prior pivot (2 touches, 1.3x vol) @ 54.64 | Trendline (rising support) @ 54.50 | Volume 1.8x average</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>HSIC</t>
+          <t>EME</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4221,38 +4221,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D67" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>86.11</v>
+        <v>687.39</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>48.1</v>
+        <v>37</v>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.6 ATR since signal; stop beyond 83.97) | Bullish engulfing | Fib 38.2% retrace @ 83.21 | Major pivot zone (1 touch, 1.9x vol) @ 84.15 | High-volume node @ 84.67</t>
+          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 665.55) | Bottoming tail, tail 68% of range | Time count: TD setup 12 | Major pivot zone (1 touch, 2.0x vol) @ 668.46</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>GPN</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4277,38 +4277,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C68" s="11" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D68" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>630.9</v>
+        <v>85.69</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>3.96</v>
+        <v>2.56</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>45.8</v>
+        <v>49.7</v>
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.9 ATR since signal; stop beyond 581.78) | Bottoming tail, tail 66% of range | Time count: TD setup 12 | Major pivot zone (5 touches, 1.5x vol) @ 594.79 | Volume 1.8x average</t>
+          <t>Setup from 1 bar ago, still near entry (+0.9 ATR since signal; stop beyond 80.85) | Bullish engulfing | Fib 38.2% retrace @ 82.29 | Prior pivot (2 touches, 1.7x vol) @ 82.12 | Trendline (rising support) @ 81.14</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4333,38 +4333,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C69" s="11" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
       <c r="D69" s="4" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F69" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>564.6</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>-2.39</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J69" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G69" s="2" t="n">
-        <v>246.65</v>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="I69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="K69" s="2" t="n">
-        <v>57</v>
+        <v>53.6</v>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 228.81) | Bottoming tail, tail 86% of range | Time count: TD setup 14 | Major pivot zone (5 touches, 3.3x vol) @ 226.83 | Volume 3.3x average</t>
+          <t>Setup from 1 bar ago, still near entry (-0.5 ATR since signal; stop beyond 560.52) | Bottoming tail, tail 67% of range | Fib 38.2% retrace @ 557.23 | Major pivot zone (4 touches, 1.1x vol) @ 571.91</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -4381,7 +4381,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4395,32 +4395,32 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>0.991</v>
+        <v>1</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>101.87</v>
+        <v>44.43</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>-0.54</v>
+        <v>0.79</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>26</v>
+        <v>48.2</v>
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (-0.2 ATR since signal; stop beyond 100.50) | Bottoming tail, tail 62% of range | Prior pivot (1 touch, 1.6x vol) @ 99.18 | RSI oversold (26) | Tagged lower Bollinger band | Extended 2.8 ATR from 20 EMA</t>
+          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 43.27) | Bottoming tail, tail 66% of range | Major pivot zone (3 touches, 1.1x vol) @ 42.78 | Trendline (rising support) @ 42.98</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4445,38 +4445,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C71" s="11" t="inlineStr">
+      <c r="C71" s="8" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
       <c r="D71" s="4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>57.28</v>
+        <v>222.08</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>1.29</v>
+        <v>-2.63</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>52.4</v>
+        <v>45.7</v>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>Setup from 2 bars ago, still near entry (+0.8 ATR since signal; stop beyond 54.34) | Bottoming tail (new low rejected), tail 47% of range | Fib 38.2% retrace @ 53.99 | Prior pivot (2 touches, 1.3x vol) @ 54.64 | Trendline (rising support) @ 54.50 | Volume 1.8x average</t>
+          <t>Setup from 1 bar ago, still near entry (-0.3 ATR since signal; stop beyond 217.90) | Bottoming tail, tail 59% of range | Major pivot zone (1 touch, 1.9x vol) @ 216.04 | High-volume node @ 216.25</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -4493,7 +4493,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>EME</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4507,32 +4507,32 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>0.992</v>
+        <v>1</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>679.29</v>
+        <v>159.79</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>0.11</v>
+        <v>0.9</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>3</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>37</v>
+        <v>35.4</v>
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.0 ATR since signal; stop beyond 665.55) | Bottoming tail, tail 68% of range | Time count: TD setup 12 | Major pivot zone (1 touch, 2.0x vol) @ 668.46</t>
+          <t>Setup from 1 bar ago, still near entry (+0.4 ATR since signal; stop beyond 156.20) | Bottoming tail, tail 50% of range | Fib 78.6% retrace @ 157.06 | Major pivot zone (3 touches, 2.4x vol) @ 156.30</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -4549,7 +4549,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GPN</t>
+          <t>IVZ</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4557,25 +4557,25 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D73" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>85.81999999999999</v>
+        <v>29.07</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>2.72</v>
+        <v>1.34</v>
       </c>
       <c r="I73" s="2" t="n">
         <v>-4</v>
@@ -4584,11 +4584,11 @@
         <v>1</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>49.7</v>
+        <v>43</v>
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.9 ATR since signal; stop beyond 80.85) | Bullish engulfing | Fib 38.2% retrace @ 82.29 | Prior pivot (2 touches, 1.7x vol) @ 82.12 | Trendline (rising support) @ 81.14</t>
+          <t>Setup from 1 bar ago, still near entry (+0.4 ATR since signal; stop beyond 28.20) | Bottoming tail, tail 68% of range | Fib 61.8% retrace @ 28.57 | Major pivot zone (3 touches, 1.5x vol) @ 28.54</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -4605,7 +4605,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4613,13 +4613,13 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C74" s="11" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>0.617</v>
+        <v>1</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>4</v>
@@ -4628,23 +4628,23 @@
         <v>3</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>562.09</v>
+        <v>488.37</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>-2.83</v>
+        <v>1.34</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>53.6</v>
+        <v>59</v>
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (-0.6 ATR since signal; stop beyond 560.52) | Bottoming tail, tail 67% of range | Fib 38.2% retrace @ 557.23 | Major pivot zone (4 touches, 1.1x vol) @ 571.91</t>
+          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 467.24) | Bottoming tail, tail 50% of range | Major pivot zone (2 touches, 2.1x vol) @ 465.90 | High-volume node @ 463.40</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -4661,7 +4661,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4678,16 +4678,16 @@
         <v>1</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>44.24</v>
+        <v>97.04000000000001</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>0.36</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I75" s="2" t="n">
         <v>1</v>
@@ -4696,11 +4696,11 @@
         <v>3</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>48.2</v>
+        <v>43.7</v>
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.1 ATR since signal; stop beyond 43.27) | Bottoming tail, tail 66% of range | Major pivot zone (3 touches, 1.1x vol) @ 42.78 | Trendline (rising support) @ 42.98</t>
+          <t>Setup from 1 bar ago, still near entry (+0.0 ATR since signal; stop beyond 94.12) | Bottoming tail, tail 72% of range | Time count: TD setup 11 | Prior pivot (1 touch, 1.2x vol) @ 93.36</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>HUBB</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4725,38 +4725,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C76" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="E76" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F76" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F76" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="G76" s="2" t="n">
-        <v>219.71</v>
+        <v>435.39</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>-3.67</v>
+        <v>-0.44</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>45.7</v>
+        <v>37.3</v>
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (-0.4 ATR since signal; stop beyond 217.90) | Bottoming tail, tail 59% of range | Major pivot zone (1 touch, 1.9x vol) @ 216.04 | High-volume node @ 216.25</t>
+          <t>Setup from 1 bar ago, still near entry (-0.1 ATR since signal; stop beyond 426.91) | Bottoming tail (new low rejected), tail 58% of range | Prior pivot (1 touch, 1.1x vol) @ 420.97 | Tagged lower Bollinger band | Volume 1.9x average</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>FIX</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4781,38 +4781,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D77" s="4" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F77" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>159.93</v>
+        <v>1330.65</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>0.99</v>
+        <v>-1.12</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>3</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>35.4</v>
+        <v>39.4</v>
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.4 ATR since signal; stop beyond 156.20) | Bottoming tail, tail 50% of range | Fib 78.6% retrace @ 157.06 | Major pivot zone (3 touches, 2.4x vol) @ 156.30</t>
+          <t>Setup from 1 bar ago, still near entry (-0.2 ATR since signal; stop beyond 1290.57) | Bottoming tail, tail 68% of range | Time count: TD setup 12 | Volume 1.6x average</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>IVZ</t>
+          <t>GNRC</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4837,38 +4837,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C78" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D78" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>29</v>
+        <v>205</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>1.12</v>
+        <v>1.82</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>43</v>
+        <v>50.3</v>
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.4 ATR since signal; stop beyond 28.20) | Bottoming tail, tail 68% of range | Fib 61.8% retrace @ 28.57 | Major pivot zone (3 touches, 1.5x vol) @ 28.54</t>
+          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 181.00) | Bottoming tail (new low rejected), tail 66% of range | Major pivot zone (7 touches, 7.7x vol) @ 179.18 | Volume 2.3x average</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -4883,168 +4883,168 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>SNPS</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" s="2" t="n">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>HII</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E79" s="7" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="F79" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G79" s="7" t="n">
+        <v>317.43</v>
+      </c>
+      <c r="H79" s="7" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="I79" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="J79" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" s="7" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="L79" s="10" t="inlineStr">
+        <is>
+          <t>Time count: 11 up bars since the last down bar | Fib 78.6% retrace @ 319.32 | Prior pivot (1 touch, 1.2x vol) @ 322.62 | High-volume node @ 317.53 | RSI overbought (76) | Tagged upper Bollinger band | Extended 5.1 ATR from 20 EMA | Volume 2.7x average</t>
+        </is>
+      </c>
+      <c r="M79" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N79" s="11" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>NCLH</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E80" s="7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F80" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G80" s="7" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="H80" s="7" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="I80" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J80" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F79" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>487.51</v>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J79" s="2" t="n">
+      <c r="K80" s="7" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="L80" s="10" t="inlineStr">
+        <is>
+          <t>Time count: 8 up bars since the last down bar | Fib 61.8% retrace @ 18.77 | High-volume node @ 18.57 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 2.8x average</t>
+        </is>
+      </c>
+      <c r="M80" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N80" s="11" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>TXT</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C81" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="E81" s="7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F81" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G81" s="7" t="n">
+        <v>87.45999999999999</v>
+      </c>
+      <c r="H81" s="7" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="I81" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="J81" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="K79" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="L79" s="5" t="inlineStr">
-        <is>
-          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 467.24) | Bottoming tail, tail 50% of range | Major pivot zone (2 touches, 2.1x vol) @ 465.90 | High-volume node @ 463.40</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N79" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>NRG</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C80" s="11" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>0.999</v>
-      </c>
-      <c r="E80" s="2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>96.72</v>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K80" s="2" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="L80" s="5" t="inlineStr">
-        <is>
-          <t>Setup from 1 bar ago, still near entry (-0.1 ATR since signal; stop beyond 94.12) | Bottoming tail, tail 72% of range | Time count: TD setup 11 | Prior pivot (1 touch, 1.2x vol) @ 93.36</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N80" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>FIX</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>0.931</v>
-      </c>
-      <c r="E81" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F81" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>1316.26</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="I81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K81" s="2" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="L81" s="5" t="inlineStr">
-        <is>
-          <t>Setup from 1 bar ago, still near entry (-0.3 ATR since signal; stop beyond 1290.57) | Bottoming tail, tail 68% of range | Time count: TD setup 12 | Volume 1.6x average</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N81" s="6" t="inlineStr">
+      <c r="K81" s="7" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="L81" s="10" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 13 | Fib 61.8% retrace @ 87.58 | Volume POC @ 88.76 | RSI overbought (76) | Tagged upper Bollinger band | Extended 5.2 ATR from 20 EMA | Volume 1.9x average</t>
+        </is>
+      </c>
+      <c r="M81" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N81" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5053,7 +5053,7 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>TDY</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -5066,33 +5066,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D82" s="8" t="n">
-        <v>0.041</v>
+      <c r="D82" s="9" t="n">
+        <v>0.109</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>7.25</v>
+        <v>6.5</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>315.62</v>
+        <v>676.1</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>13.02</v>
+        <v>1.58</v>
       </c>
       <c r="I82" s="7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J82" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K82" s="7" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="L82" s="9" t="inlineStr">
-        <is>
-          <t>Time count: 11 up bars since the last down bar | Fib 78.6% retrace @ 319.32 | Prior pivot (1 touch, 1.2x vol) @ 322.62 | High-volume node @ 317.53 | RSI overbought (76) | Tagged upper Bollinger band | Extended 5.1 ATR from 20 EMA | Volume 2.7x average</t>
+        <v>75.5</v>
+      </c>
+      <c r="L82" s="10" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 12 | Fib 78.6% retrace @ 674.65 | Major pivot zone (2 touches, 3.2x vol) @ 672.68 | RSI overbought (75) | Tagged upper Bollinger band | Extended 3.2 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M82" s="7" t="inlineStr">
@@ -5100,7 +5100,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N82" s="10" t="inlineStr">
+      <c r="N82" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5109,7 +5109,7 @@
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>NCLH</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
@@ -5122,33 +5122,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D83" s="8" t="n">
-        <v>0.008999999999999999</v>
+      <c r="D83" s="9" t="n">
+        <v>0.052</v>
       </c>
       <c r="E83" s="7" t="n">
         <v>6.5</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>18.3</v>
+        <v>106.74</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>13.95</v>
+        <v>1.06</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="J83" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="L83" s="9" t="inlineStr">
-        <is>
-          <t>Time count: 8 up bars since the last down bar | Fib 61.8% retrace @ 18.77 | High-volume node @ 18.57 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 2.8x average</t>
+        <v>72.59999999999999</v>
+      </c>
+      <c r="L83" s="10" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 15 | Fib 61.8% retrace @ 107.01 | Major pivot zone (3 touches, 3.0x vol) @ 107.05 | RSI overbought (73) | Tagged upper Bollinger band | Extended 3.0 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
@@ -5156,7 +5156,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N83" s="10" t="inlineStr">
+      <c r="N83" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5165,7 +5165,7 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>LHX</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -5178,33 +5178,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D84" s="8" t="n">
-        <v>0.449</v>
+      <c r="D84" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>87.06</v>
+        <v>278.03</v>
       </c>
       <c r="H84" s="7" t="n">
-        <v>11.16</v>
+        <v>6.68</v>
       </c>
       <c r="I84" s="7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J84" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K84" s="7" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="L84" s="9" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 13 | Fib 61.8% retrace @ 87.58 | Volume POC @ 88.76 | RSI overbought (76) | Tagged upper Bollinger band | Extended 5.2 ATR from 20 EMA | Volume 1.9x average</t>
+        <v>77.40000000000001</v>
+      </c>
+      <c r="L84" s="10" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 15 | Major pivot zone (1 touch, 2.0x vol) @ 281.06 | RSI overbought (77) | Tagged upper Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 1.5x average</t>
         </is>
       </c>
       <c r="M84" s="7" t="inlineStr">
@@ -5212,7 +5212,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N84" s="10" t="inlineStr">
+      <c r="N84" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5234,20 +5234,20 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D85" s="8" t="n">
+      <c r="D85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="F85" s="7" t="n">
         <v>7</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>280.64</v>
+        <v>281.07</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>5.9</v>
+        <v>6.06</v>
       </c>
       <c r="I85" s="7" t="n">
         <v>1</v>
@@ -5256,11 +5256,11 @@
         <v>3</v>
       </c>
       <c r="K85" s="7" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="L85" s="9" t="inlineStr">
-        <is>
-          <t>Fib 61.8% retrace @ 288.65 | Major pivot zone (6 touches, 1.7x vol) @ 280.70 | Volume POC @ 289.56 | RSI overbought (73) | Tagged upper Bollinger band | Extended 3.8 ATR from 20 EMA | Volume 1.7x average</t>
+        <v>72.8</v>
+      </c>
+      <c r="L85" s="10" t="inlineStr">
+        <is>
+          <t>Fib 61.8% retrace @ 288.65 | Prior pivot (1 touch, 1.3x vol) @ 288.44 | Volume POC @ 289.56 | RSI overbought (73) | Tagged upper Bollinger band | Extended 3.8 ATR from 20 EMA | Volume 1.7x average</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
@@ -5268,7 +5268,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N85" s="10" t="inlineStr">
+      <c r="N85" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5277,7 +5277,7 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>TDY</t>
+          <t>AON</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -5290,33 +5290,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D86" s="8" t="n">
-        <v>0.299</v>
+      <c r="D86" s="9" t="n">
+        <v>0.18</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="F86" s="7" t="n">
         <v>6</v>
       </c>
       <c r="G86" s="7" t="n">
-        <v>674.58</v>
+        <v>319.99</v>
       </c>
       <c r="H86" s="7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="I86" s="7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J86" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K86" s="7" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="L86" s="9" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 12 | Fib 78.6% retrace @ 674.65 | Major pivot zone (2 touches, 3.2x vol) @ 672.68 | RSI overbought (75) | Tagged upper Bollinger band | Extended 3.2 ATR from 20 EMA</t>
+        <v>68.7</v>
+      </c>
+      <c r="L86" s="10" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 10 | Fib 50.0% retrace @ 323.90 | Prior pivot (1 touch, 1.3x vol) @ 324.30 | Volume POC @ 320.45 | Tagged upper Bollinger band | Extended 3.4 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M86" s="7" t="inlineStr">
@@ -5324,7 +5324,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N86" s="10" t="inlineStr">
+      <c r="N86" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5333,7 +5333,7 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -5346,33 +5346,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D87" s="8" t="n">
-        <v>0.1</v>
+      <c r="D87" s="9" t="n">
+        <v>0.048</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="F87" s="7" t="n">
         <v>6</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>106.69</v>
+        <v>367.03</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>1.02</v>
+        <v>3.58</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J87" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="L87" s="9" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 15 | Fib 61.8% retrace @ 107.01 | Major pivot zone (3 touches, 3.0x vol) @ 107.05 | RSI overbought (73) | Tagged upper Bollinger band | Extended 3.0 ATR from 20 EMA</t>
+        <v>70.90000000000001</v>
+      </c>
+      <c r="L87" s="10" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 14 | Fib 61.8% retrace @ 368.42 | Prior pivot (1 touch, 1.6x vol) @ 372.24 | RSI overbought (71) | Tagged upper Bollinger band | Extended 3.6 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
@@ -5380,7 +5380,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N87" s="10" t="inlineStr">
+      <c r="N87" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5389,7 +5389,7 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>LHX</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -5402,97 +5402,97 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D88" s="8" t="n">
-        <v>0</v>
+      <c r="D88" s="9" t="n">
+        <v>0.08699999999999999</v>
       </c>
       <c r="E88" s="7" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="F88" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G88" s="7" t="n">
+        <v>44.78</v>
+      </c>
+      <c r="H88" s="7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I88" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="J88" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K88" s="7" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="L88" s="10" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 20 | Fib 61.8% retrace @ 44.89 | Major pivot zone (3 touches, 1.9x vol) @ 44.71 | RSI overbought (74) | Extended 3.2 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M88" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N88" s="11" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C89" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="F89" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F88" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G88" s="7" t="n">
-        <v>277.99</v>
-      </c>
-      <c r="H88" s="7" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="I88" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="J88" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K88" s="7" t="n">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="L88" s="9" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 15 | Major pivot zone (1 touch, 2.0x vol) @ 281.06 | RSI overbought (77) | Tagged upper Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 1.6x average</t>
-        </is>
-      </c>
-      <c r="M88" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N88" s="10" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="7" t="inlineStr">
-        <is>
-          <t>AON</t>
-        </is>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C89" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D89" s="8" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="E89" s="7" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="F89" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G89" s="7" t="n">
-        <v>320.57</v>
-      </c>
-      <c r="H89" s="7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="I89" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="J89" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K89" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="L89" s="9" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 10 | Fib 50.0% retrace @ 323.90 | Prior pivot (1 touch, 1.3x vol) @ 324.30 | Volume POC @ 320.45 | Tagged upper Bollinger band | Extended 3.4 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M89" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N89" s="10" t="inlineStr">
+      <c r="G89" s="2" t="n">
+        <v>127.35</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>-5.46</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="L89" s="5" t="inlineStr">
+        <is>
+          <t>Time count: 9 down bars since the last up bar | Prior pivot (2 touches, 1.7x vol) @ 128.64 | RSI oversold (30) | Tagged lower Bollinger band | Extended 2.7 ATR from 20 EMA | Volume 2.4x average</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N89" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5501,7 +5501,7 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -5514,33 +5514,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D90" s="8" t="n">
-        <v>0.103</v>
+      <c r="D90" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>366.85</v>
+        <v>265.39</v>
       </c>
       <c r="H90" s="7" t="n">
-        <v>3.53</v>
+        <v>5.44</v>
       </c>
       <c r="I90" s="7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J90" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K90" s="7" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="L90" s="9" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 14 | Fib 61.8% retrace @ 368.42 | Prior pivot (1 touch, 1.6x vol) @ 372.24 | RSI overbought (71) | Tagged upper Bollinger band | Extended 3.6 ATR from 20 EMA</t>
+        <v>69.5</v>
+      </c>
+      <c r="L90" s="10" t="inlineStr">
+        <is>
+          <t>Time count: 13 up bars since the last down bar | Fib 38.2% retrace @ 262.53 | Prior pivot (1 touch, 1.0x vol) @ 265.83 | Trendline (rising resistance) @ 263.21 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M90" s="7" t="inlineStr">
@@ -5548,7 +5548,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N90" s="10" t="inlineStr">
+      <c r="N90" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5557,7 +5557,7 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>NI</t>
+          <t>URI</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -5570,33 +5570,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D91" s="8" t="n">
-        <v>0.083</v>
+      <c r="D91" s="9" t="n">
+        <v>0.022</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="F91" s="7" t="n">
         <v>5</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>44.8</v>
+        <v>1196.38</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J91" s="7" t="n">
         <v>4</v>
       </c>
       <c r="K91" s="7" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="L91" s="9" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 20 | Fib 61.8% retrace @ 44.89 | Major pivot zone (3 touches, 1.9x vol) @ 44.71 | RSI overbought (74) | Extended 3.2 ATR from 20 EMA</t>
+        <v>73</v>
+      </c>
+      <c r="L91" s="10" t="inlineStr">
+        <is>
+          <t>Time count: 7 up bars since the last down bar | Trendline (rising resistance) @ 1185.31 | RSI overbought (73) | Tagged upper Bollinger band | Extended 2.7 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M91" s="7" t="inlineStr">
@@ -5604,21 +5604,21 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N91" s="10" t="inlineStr">
+      <c r="N91" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="7" t="inlineStr">
-        <is>
-          <t>NXPI</t>
-        </is>
-      </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>TPR</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
         </is>
       </c>
       <c r="C92" s="13" t="inlineStr">
@@ -5626,41 +5626,41 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D92" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" s="7" t="n">
+      <c r="D92" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F92" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G92" s="7" t="n">
-        <v>263.09</v>
-      </c>
-      <c r="H92" s="7" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="I92" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="J92" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K92" s="7" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="L92" s="9" t="inlineStr">
-        <is>
-          <t>Time count: 13 up bars since the last down bar | Fib 38.2% retrace @ 262.53 | Prior pivot (1 touch, 1.0x vol) @ 265.83 | Trendline (rising resistance) @ 263.21 | Tagged upper Bollinger band</t>
-        </is>
-      </c>
-      <c r="M92" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N92" s="10" t="inlineStr">
+      <c r="F92" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="L92" s="5" t="inlineStr">
+        <is>
+          <t>Time count: 9 down bars since the last up bar | Major pivot zone (2 touches, 1.9x vol) @ 112.16 | High-volume node @ 115.70 | Trendline (rising support) @ 115.23</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N92" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5669,7 +5669,7 @@
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
@@ -5682,33 +5682,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D93" s="8" t="n">
-        <v>0.274</v>
+      <c r="D93" s="9" t="n">
+        <v>0.04</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="F93" s="7" t="n">
         <v>5</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>309.8</v>
+        <v>120.12</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>-0.01</v>
+        <v>1.42</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J93" s="7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="K93" s="7" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="L93" s="9" t="inlineStr">
-        <is>
-          <t>Time count: 7 bars without a lower low | Fib 78.6% retrace @ 314.31 | Prior pivot (1 touch, 0.7x vol) @ 313.73 | RSI overbought (70) | Tagged upper Bollinger band</t>
+        <v>74.3</v>
+      </c>
+      <c r="L93" s="10" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 10 | Prior pivot (2 touches, 0.9x vol) @ 119.91 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.2 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M93" s="7" t="inlineStr">
@@ -5716,7 +5716,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N93" s="10" t="inlineStr">
+      <c r="N93" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5725,7 +5725,7 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>URI</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -5738,209 +5738,209 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D94" s="8" t="n">
-        <v>0.116</v>
+      <c r="D94" s="9" t="n">
+        <v>0.001</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="F94" s="7" t="n">
         <v>5</v>
       </c>
       <c r="G94" s="7" t="n">
-        <v>1192.44</v>
+        <v>103.55</v>
       </c>
       <c r="H94" s="7" t="n">
-        <v>1.52</v>
+        <v>3.17</v>
       </c>
       <c r="I94" s="7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J94" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K94" s="7" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="L94" s="10" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 12 | Prior pivot (1 touch, 1.0x vol) @ 103.78 | RSI overbought (76) | Tagged upper Bollinger band | Extended 3.0 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M94" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N94" s="11" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>MSI</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C95" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E95" s="7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F95" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="K94" s="7" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="L94" s="9" t="inlineStr">
-        <is>
-          <t>Time count: 7 up bars since the last down bar | Trendline (rising resistance) @ 1185.31 | RSI overbought (73) | Tagged upper Bollinger band | Extended 2.7 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M94" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N94" s="10" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>TPR</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="G95" s="7" t="n">
+        <v>492.26</v>
+      </c>
+      <c r="H95" s="7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I95" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="J95" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" s="7" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="L95" s="10" t="inlineStr">
+        <is>
+          <t>Time count: 13 up bars since the last down bar | Major pivot zone (2 touches, 1.8x vol) @ 492.74 | RSI overbought (73) | Extended 2.8 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M95" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N95" s="11" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="C95" s="13" t="inlineStr">
+      <c r="C96" s="13" t="inlineStr">
         <is>
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D95" s="4" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="E95" s="2" t="n">
+      <c r="D96" s="4" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>135.7</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>-22.05</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="L96" s="5" t="inlineStr">
+        <is>
+          <t>Fib 78.6% retrace @ 126.03 | Prior pivot (1 touch, 1.3x vol) @ 133.05 | RSI oversold (27) | Tagged lower Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 3.8x average</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N96" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C97" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F97" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F95" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>117.49</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>5.61</v>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K95" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="L95" s="5" t="inlineStr">
-        <is>
-          <t>Time count: 9 down bars since the last up bar | Major pivot zone (2 touches, 1.9x vol) @ 112.16 | High-volume node @ 115.70 | Trendline (rising support) @ 115.23</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N95" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="7" t="inlineStr">
-        <is>
-          <t>PPG</t>
-        </is>
-      </c>
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C96" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D96" s="8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E96" s="7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="F96" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G96" s="7" t="n">
-        <v>119.94</v>
-      </c>
-      <c r="H96" s="7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="I96" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="J96" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K96" s="7" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="L96" s="9" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 10 | Prior pivot (2 touches, 0.9x vol) @ 119.91 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.2 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M96" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N96" s="10" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="7" t="inlineStr">
-        <is>
-          <t>SWK</t>
-        </is>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C97" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D97" s="8" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E97" s="7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="F97" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G97" s="7" t="n">
-        <v>103.32</v>
-      </c>
-      <c r="H97" s="7" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I97" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="J97" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K97" s="7" t="n">
-        <v>76</v>
-      </c>
-      <c r="L97" s="9" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 12 | Prior pivot (1 touch, 1.0x vol) @ 103.78 | RSI overbought (76) | Tagged upper Bollinger band | Extended 3.0 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M97" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N97" s="10" t="inlineStr">
+      <c r="G97" s="2" t="n">
+        <v>647.36</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>-9.25</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="L97" s="5" t="inlineStr">
+        <is>
+          <t>Major pivot zone (2 touches, 1.8x vol) @ 619.81 | RSI oversold (27) | Tagged lower Bollinger band | Extended 3.5 ATR from 20 EMA | Volume 2.6x average</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N97" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5949,7 +5949,7 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -5962,33 +5962,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D98" s="8" t="n">
-        <v>0.053</v>
+      <c r="D98" s="9" t="n">
+        <v>0.044</v>
       </c>
       <c r="E98" s="7" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="F98" s="7" t="n">
         <v>4</v>
       </c>
       <c r="G98" s="7" t="n">
-        <v>490.71</v>
+        <v>311.42</v>
       </c>
       <c r="H98" s="7" t="n">
-        <v>1.51</v>
+        <v>0.51</v>
       </c>
       <c r="I98" s="7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J98" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K98" s="7" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="L98" s="9" t="inlineStr">
-        <is>
-          <t>Time count: 13 up bars since the last down bar | Major pivot zone (2 touches, 1.8x vol) @ 492.74 | RSI overbought (72) | Extended 2.8 ATR from 20 EMA</t>
+        <v>71.2</v>
+      </c>
+      <c r="L98" s="10" t="inlineStr">
+        <is>
+          <t>Time count: 7 bars without a lower low | Fib 78.6% retrace @ 314.31 | Prior pivot (1 touch, 0.7x vol) @ 313.73 | RSI overbought (71)</t>
         </is>
       </c>
       <c r="M98" s="7" t="inlineStr">
@@ -5996,7 +5996,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N98" s="10" t="inlineStr">
+      <c r="N98" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -6005,7 +6005,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -6019,32 +6019,32 @@
         </is>
       </c>
       <c r="D99" s="4" t="n">
-        <v>0.839</v>
+        <v>0.994</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>135.43</v>
+        <v>346.67</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>-22.2</v>
+        <v>4.22</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>26.5</v>
+        <v>42.2</v>
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>Fib 78.6% retrace @ 126.03 | Prior pivot (1 touch, 1.3x vol) @ 133.05 | RSI oversold (27) | Tagged lower Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 3.8x average</t>
+          <t>Prior pivot (1 touch, 1.4x vol) @ 340.32 | Trendline (falling support) @ 319.68 | Bullish RSI divergence (42) | Tagged lower Bollinger band | Extended 2.6 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -6059,14 +6059,14 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>CAT</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>CRL</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
         </is>
       </c>
       <c r="C100" s="13" t="inlineStr">
@@ -6074,41 +6074,41 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D100" s="4" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F100" s="2" t="n">
+      <c r="D100" s="9" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="E100" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F100" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G100" s="7" t="n">
+        <v>376.52</v>
+      </c>
+      <c r="H100" s="7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I100" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J100" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G100" s="2" t="n">
-        <v>644.36</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>-9.68</v>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K100" s="2" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="L100" s="5" t="inlineStr">
-        <is>
-          <t>Major pivot zone (2 touches, 1.8x vol) @ 619.81 | RSI oversold (26) | Tagged lower Bollinger band | Extended 3.5 ATR from 20 EMA | Volume 2.6x average</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N100" s="6" t="inlineStr">
+      <c r="K100" s="7" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="L100" s="10" t="inlineStr">
+        <is>
+          <t>Time count: 8 up bars since the last down bar | RSI overbought (81) | Tagged upper Bollinger band | Extended 3.8 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M100" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N100" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -6117,7 +6117,7 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>TFC</t>
+          <t>LYB</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
@@ -6130,33 +6130,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D101" s="8" t="n">
-        <v>0.542</v>
+      <c r="D101" s="9" t="n">
+        <v>0.755</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>49.18</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>1.57</v>
+        <v>-3.16</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J101" s="7" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="K101" s="7" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="L101" s="9" t="inlineStr">
-        <is>
-          <t>Fib 50.0% retrace @ 49.37 | Major pivot zone (7 touches, 1.4x vol) @ 49.39 | High-volume node @ 49.73 | Tagged upper Bollinger band</t>
+        <v>57.5</v>
+      </c>
+      <c r="L101" s="10" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 19 | Fib 61.8% retrace @ 65.23 | Major pivot zone (3 touches, 1.6x vol) @ 67.19</t>
         </is>
       </c>
       <c r="M101" s="7" t="inlineStr">
@@ -6164,7 +6164,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N101" s="10" t="inlineStr">
+      <c r="N101" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -6173,7 +6173,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>LII</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -6187,32 +6187,32 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>0.9379999999999999</v>
+        <v>0</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>344.93</v>
+        <v>97.79000000000001</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>3.7</v>
+        <v>-2.98</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>41.3</v>
+        <v>29.4</v>
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>Prior pivot (1 touch, 1.4x vol) @ 340.32 | Trendline (falling support) @ 319.68 | Bullish RSI divergence (41) | Tagged lower Bollinger band | Extended 2.6 ATR from 20 EMA</t>
+          <t>Time count: 11 down bars since the last up bar | Prior pivot (2 touches, 1.0x vol) @ 95.80 | RSI oversold (29) | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
@@ -6229,7 +6229,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -6243,32 +6243,32 @@
         </is>
       </c>
       <c r="D103" s="4" t="n">
-        <v>0.225</v>
+        <v>0.006</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>128.29</v>
+        <v>76.25</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>-4.76</v>
+        <v>-1.28</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>30.2</v>
+        <v>32.8</v>
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>Time count: 9 down bars since the last up bar | Prior pivot (2 touches, 1.7x vol) @ 128.64 | Tagged lower Bollinger band | Extended 2.6 ATR from 20 EMA | Volume 2.3x average</t>
+          <t>Time count: 11 down bars since the last up bar | Major pivot zone (3 touches, 1.5x vol) @ 75.85 | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -6285,7 +6285,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -6299,32 +6299,32 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>0.467</v>
+        <v>0.245</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>256.4</v>
+        <v>330.5</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>-1.37</v>
+        <v>-1.49</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>-7</v>
+        <v>2</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>-2</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>34.7</v>
+        <v>43.7</v>
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>Time count: 9 down bars since the last up bar | Trendline (falling support) @ 253.65 | Bullish RSI divergence (35) | Tagged lower Bollinger band</t>
+          <t>Fib 61.8% retrace @ 330.37 | Major pivot zone (6 touches, 3.1x vol) @ 327.50 | Volume POC @ 334.25</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -6339,14 +6339,14 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="7" t="inlineStr">
-        <is>
-          <t>LYB</t>
-        </is>
-      </c>
-      <c r="B105" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
         </is>
       </c>
       <c r="C105" s="13" t="inlineStr">
@@ -6354,41 +6354,41 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D105" s="8" t="n">
-        <v>0.501</v>
-      </c>
-      <c r="E105" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F105" s="7" t="n">
+      <c r="D105" s="4" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F105" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G105" s="7" t="n">
-        <v>65.23</v>
-      </c>
-      <c r="H105" s="7" t="n">
-        <v>-2.83</v>
-      </c>
-      <c r="I105" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J105" s="7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="K105" s="7" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="L105" s="9" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 19 | Fib 61.8% retrace @ 65.23 | Major pivot zone (3 touches, 1.6x vol) @ 67.19</t>
-        </is>
-      </c>
-      <c r="M105" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N105" s="10" t="inlineStr">
+      <c r="G105" s="2" t="n">
+        <v>628.77</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="L105" s="5" t="inlineStr">
+        <is>
+          <t>Time count: 11 down bars since the last up bar | Fib 61.8% retrace @ 621.77 | High-volume node @ 620.94</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N105" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -6397,7 +6397,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -6411,96 +6411,96 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>0</v>
+        <v>0.997</v>
       </c>
       <c r="E106" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>77.26000000000001</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="L106" s="5" t="inlineStr">
+        <is>
+          <t>Fib 50.0% retrace @ 76.19 | Major pivot zone (3 touches, 1.0x vol) @ 75.26 | High-volume node @ 75.69</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N106" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>COF</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C107" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="E107" s="7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F107" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G107" s="7" t="n">
+        <v>208.69</v>
+      </c>
+      <c r="H107" s="7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I107" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J107" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F106" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G106" s="2" t="n">
-        <v>97.78</v>
-      </c>
-      <c r="H106" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I106" s="2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J106" s="2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="K106" s="2" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="L106" s="5" t="inlineStr">
-        <is>
-          <t>Time count: 11 down bars since the last up bar | Prior pivot (2 touches, 1.0x vol) @ 95.80 | RSI oversold (29) | Tagged lower Bollinger band</t>
-        </is>
-      </c>
-      <c r="M106" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N106" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>ADM</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C107" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="E107" s="2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="F107" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G107" s="2" t="n">
-        <v>76.11</v>
-      </c>
-      <c r="H107" s="2" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="I107" s="2" t="n">
-        <v>-9</v>
-      </c>
-      <c r="J107" s="2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="K107" s="2" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="L107" s="5" t="inlineStr">
-        <is>
-          <t>Time count: 11 down bars since the last up bar | Major pivot zone (3 touches, 1.5x vol) @ 75.85 | Tagged lower Bollinger band</t>
-        </is>
-      </c>
-      <c r="M107" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N107" s="6" t="inlineStr">
+      <c r="K107" s="7" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="L107" s="10" t="inlineStr">
+        <is>
+          <t>Major pivot zone (8 touches, 1.8x vol) @ 210.88 | Trendline (falling resistance) @ 209.74 | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M107" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N107" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -6509,7 +6509,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -6523,32 +6523,32 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>0.108</v>
+        <v>0.053</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="F108" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>328.83</v>
+        <v>380.21</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>-1.99</v>
+        <v>-2.13</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>43</v>
+        <v>36.8</v>
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>Fib 61.8% retrace @ 330.37 | Major pivot zone (6 touches, 3.1x vol) @ 327.50 | Volume POC @ 334.25</t>
+          <t>Time count: TD setup 8 | Fib 38.2% retrace @ 373.38 | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
@@ -6563,14 +6563,14 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>ARES</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
         </is>
       </c>
       <c r="C109" s="13" t="inlineStr">
@@ -6578,41 +6578,41 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D109" s="4" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E109" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F109" s="2" t="n">
+      <c r="D109" s="9" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="E109" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G109" s="2" t="n">
-        <v>627.22</v>
-      </c>
-      <c r="H109" s="2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I109" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J109" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K109" s="2" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="L109" s="5" t="inlineStr">
-        <is>
-          <t>Time count: 11 down bars since the last up bar | Fib 61.8% retrace @ 621.77 | High-volume node @ 620.94</t>
-        </is>
-      </c>
-      <c r="M109" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N109" s="6" t="inlineStr">
+      <c r="F109" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G109" s="7" t="n">
+        <v>126.78</v>
+      </c>
+      <c r="H109" s="7" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I109" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J109" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K109" s="7" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="L109" s="10" t="inlineStr">
+        <is>
+          <t>Time count: 8 up bars since the last down bar | Prior pivot (2 touches, 1.3x vol) @ 129.72 | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M109" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N109" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -6621,7 +6621,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -6635,32 +6635,32 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.713</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>76.91</v>
+        <v>363.2</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>2.26</v>
+        <v>-0.64</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>50.2</v>
+        <v>26.6</v>
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>Fib 50.0% retrace @ 76.19 | Major pivot zone (3 touches, 1.0x vol) @ 75.26 | High-volume node @ 75.69</t>
+          <t>RSI oversold (27) | Tagged lower Bollinger band | Extended 4.2 ATR from 20 EMA | Volume 2.0x average</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -6691,32 +6691,32 @@
         </is>
       </c>
       <c r="D111" s="4" t="n">
-        <v>0.341</v>
+        <v>0.24</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>238.7</v>
+        <v>281.1</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>-5.94</v>
+        <v>-12.67</v>
       </c>
       <c r="I111" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>39.4</v>
+        <v>21.8</v>
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>Fib 61.8% retrace @ 228.55 | Major pivot zone (3 touches, 1.4x vol) @ 238.69 | Tagged lower Bollinger band</t>
+          <t>RSI oversold (22) | Tagged lower Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 5.0x average</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -6747,32 +6747,32 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>0.061</v>
+        <v>0.237</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>379.52</v>
+        <v>283.04</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>-2.31</v>
+        <v>-12.88</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>36.6</v>
+        <v>22.1</v>
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>Time count: TD setup 8 | Fib 38.2% retrace @ 373.38 | Tagged lower Bollinger band</t>
+          <t>RSI oversold (22) | Tagged lower Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 4.7x average</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
@@ -6787,112 +6787,112 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="7" t="inlineStr">
-        <is>
-          <t>ARES</t>
-        </is>
-      </c>
-      <c r="B113" s="7" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>MGM</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C113" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="L113" s="5" t="inlineStr">
+        <is>
+          <t>Bullish RSI divergence (35) | Tagged lower Bollinger band | Extended 2.7 ATR from 20 EMA | Volume 1.9x average</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N113" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>
       </c>
-      <c r="C113" s="13" t="inlineStr">
+      <c r="C114" s="13" t="inlineStr">
         <is>
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D113" s="8" t="n">
-        <v>0.378</v>
-      </c>
-      <c r="E113" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F113" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G113" s="7" t="n">
-        <v>126.2</v>
-      </c>
-      <c r="H113" s="7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="I113" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="J113" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K113" s="7" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="L113" s="9" t="inlineStr">
-        <is>
-          <t>Time count: 8 up bars since the last down bar | Prior pivot (2 touches, 1.3x vol) @ 129.72 | Tagged upper Bollinger band</t>
-        </is>
-      </c>
-      <c r="M113" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N113" s="10" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C114" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D114" s="4" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="E114" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F114" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G114" s="2" t="n">
-        <v>280.63</v>
-      </c>
-      <c r="H114" s="2" t="n">
-        <v>-12.82</v>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J114" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K114" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="L114" s="5" t="inlineStr">
-        <is>
-          <t>RSI oversold (22) | Tagged lower Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 5.1x average</t>
-        </is>
-      </c>
-      <c r="M114" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N114" s="6" t="inlineStr">
+      <c r="D114" s="9" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="E114" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F114" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G114" s="7" t="n">
+        <v>407.33</v>
+      </c>
+      <c r="H114" s="7" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I114" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J114" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K114" s="7" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="L114" s="10" t="inlineStr">
+        <is>
+          <t>Fib 50.0% retrace @ 410.70 | Major pivot zone (2 touches, 2.0x vol) @ 411.73</t>
+        </is>
+      </c>
+      <c r="M114" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N114" s="11" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -6901,7 +6901,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -6915,152 +6915,148 @@
         </is>
       </c>
       <c r="D115" s="4" t="n">
-        <v>0.222</v>
+        <v>0.985</v>
       </c>
       <c r="E115" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>85.20999999999999</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I115" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F115" s="2" t="n">
+      <c r="J115" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G115" s="2" t="n">
-        <v>282.68</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>-12.99</v>
-      </c>
-      <c r="I115" s="2" t="n">
+      <c r="K115" s="2" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="L115" s="5" t="inlineStr">
+        <is>
+          <t>Fib 38.2% retrace @ 83.44 | High-volume node @ 82.23</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N115" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>CMI</t>
+        </is>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C116" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="E116" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="7" t="n">
+        <v>517.64</v>
+      </c>
+      <c r="H116" s="7" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="I116" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J116" s="7" t="n">
         <v>-1</v>
       </c>
-      <c r="J115" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K115" s="2" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="L115" s="5" t="inlineStr">
-        <is>
-          <t>RSI oversold (22) | Tagged lower Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 4.8x average</t>
-        </is>
-      </c>
-      <c r="M115" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N115" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>MGM</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="K116" s="7" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="L116" s="10" t="inlineStr">
+        <is>
+          <t>Volume POC @ 524.39</t>
+        </is>
+      </c>
+      <c r="M116" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N116" s="11" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>PWR</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="C116" s="13" t="inlineStr">
+      <c r="C117" s="13" t="inlineStr">
         <is>
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D116" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F116" s="2" t="n">
+      <c r="D117" s="4" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>637.17</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J117" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G116" s="2" t="n">
-        <v>28.47</v>
-      </c>
-      <c r="H116" s="2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I116" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J116" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K116" s="2" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="L116" s="5" t="inlineStr">
-        <is>
-          <t>Bullish RSI divergence (35) | Tagged lower Bollinger band | Extended 2.7 ATR from 20 EMA | Volume 1.8x average</t>
-        </is>
-      </c>
-      <c r="M116" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N116" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="7" t="inlineStr">
-        <is>
-          <t>AZO</t>
-        </is>
-      </c>
-      <c r="B117" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C117" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D117" s="8" t="n">
-        <v>0.841</v>
-      </c>
-      <c r="E117" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F117" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G117" s="7" t="n">
-        <v>3137.4</v>
-      </c>
-      <c r="H117" s="7" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="I117" s="7" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J117" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K117" s="7" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="L117" s="9" t="inlineStr">
-        <is>
-          <t>Fib 61.8% retrace @ 3243.91 | Major pivot zone (6 touches, 2.2x vol) @ 3190.97</t>
-        </is>
-      </c>
-      <c r="M117" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N117" s="10" t="inlineStr">
+      <c r="K117" s="2" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="L117" s="5" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N117" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>

--- a/site/reversal_signals.xlsx
+++ b/site/reversal_signals.xlsx
@@ -69,12 +69,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F59E0B"/>
+        <fgColor rgb="00DC2626"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DC2626"/>
+        <fgColor rgb="00F59E0B"/>
       </patternFill>
     </fill>
     <fill>
@@ -106,12 +106,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.997</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>7.75</v>
@@ -596,10 +596,10 @@
         <v>7</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>496.9</v>
+        <v>497.64</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
@@ -608,7 +608,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>46.9</v>
+        <v>47.4</v>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
@@ -637,13 +637,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>0.756</v>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0.986</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>7.5</v>
@@ -652,10 +652,10 @@
         <v>6</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>54.62</v>
+        <v>54.4</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-2.85</v>
+        <v>-3.24</v>
       </c>
       <c r="I3" s="7" t="n">
         <v>-1</v>
@@ -664,11 +664,11 @@
         <v>-2</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="L3" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail, tail 54% of range | Time count: TD setup 7 | Fib 78.6% retrace @ 57.08 | Major pivot zone (9 touches, 2.4x vol) @ 55.40 | High-volume node @ 54.81 | Trendline (rising resistance) @ 56.84</t>
+        <v>53.4</v>
+      </c>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail, tail 52% of range | Time count: TD setup 7 | Fib 78.6% retrace @ 57.08 | Major pivot zone (9 touches, 2.4x vol) @ 55.40 | High-volume node @ 54.81 | Trendline (rising resistance) @ 56.84</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
@@ -676,7 +676,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N3" s="11" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -693,13 +693,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>0.987</v>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.995</v>
       </c>
       <c r="E4" s="7" t="n">
         <v>7.25</v>
@@ -708,10 +708,10 @@
         <v>6</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>33.39</v>
+        <v>33.47</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>-2.17</v>
+        <v>-1.92</v>
       </c>
       <c r="I4" s="7" t="n">
         <v>13</v>
@@ -720,11 +720,11 @@
         <v>-1</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="L4" s="10" t="inlineStr">
-        <is>
-          <t>Bearish engulfing | Time count: 12 up bars since the last down bar | Fib 61.8% retrace @ 34.41 | Major pivot zone (2 touches, 1.9x vol) @ 33.92 | Bearish RSI divergence (70) | Extended 3.4 ATR from 20 EMA</t>
+        <v>70.40000000000001</v>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>Bearish engulfing | Time count: 12 up bars since the last down bar | Fib 61.8% retrace @ 34.41 | Major pivot zone (2 touches, 1.9x vol) @ 33.92 | RSI overbought (70) | Extended 3.4 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
@@ -732,7 +732,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -741,7 +741,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>WEC</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -749,13 +749,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>0.629</v>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>7</v>
@@ -764,23 +764,23 @@
         <v>7</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>114.38</v>
+        <v>417.43</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>3.51</v>
+        <v>3.42</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="L5" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 54% of range | Fib 78.6% retrace @ 114.79 | Major pivot zone (5 touches, 1.7x vol) @ 116.28 | RSI overbought (71) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 2.2x average</t>
+        <v>81</v>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 77% of range | Time count: 15 up bars since the last down bar | Fib 1.27 extension @ 434.72 | RSI overbought (81) | Tagged upper Bollinger band | Extended 5.1 ATR from 20 EMA | Volume 2.7x average</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
@@ -788,7 +788,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -797,7 +797,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -805,38 +805,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>1</v>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>At risk</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>0.585</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>419.61</v>
+        <v>42.19</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>3.96</v>
+        <v>1.44</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="L6" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 77% of range | Time count: 15 up bars since the last down bar | Fib 1.27 extension @ 434.72 | RSI overbought (82) | Tagged upper Bollinger band | Extended 5.1 ATR from 20 EMA | Volume 2.6x average</t>
+        <v>70.8</v>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 53% of range | Time count: TD setup 20 | Prior pivot (2 touches, 1.1x vol) @ 42.24 | High-volume node @ 42.32 | RSI overbought (71) | Extended 3.2 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -844,7 +844,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N6" s="11" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -853,7 +853,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -861,38 +861,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>0.571</v>
+      <c r="D7" s="8" t="n">
+        <v>0.97</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="F7" s="7" t="n">
         <v>6</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>1027.25</v>
+        <v>561.5700000000001</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1.94</v>
+        <v>1.59</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="L7" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 65% of range | Fib 78.6% retrace @ 1078.54 | Major pivot zone (8 touches, 1.8x vol) @ 1043.32 | High-volume node @ 1073.68 | Trendline (falling resistance) @ 1028.20 | Tagged upper Bollinger band</t>
+        <v>66.59999999999999</v>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 65% of range | Time count: TD setup 15 | Fib 78.6% retrace @ 565.76 | Prior pivot (2 touches, 1.2x vol) @ 575.43 | Bearish RSI divergence (67) | Extended 2.9 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
@@ -900,7 +900,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N7" s="11" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -909,7 +909,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -917,13 +917,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>0.59</v>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>6.5</v>
@@ -932,23 +932,23 @@
         <v>6</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>42.18</v>
+        <v>88.52</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>1.42</v>
+        <v>-2.12</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>21</v>
+        <v>-2</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="L8" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 55% of range | Time count: TD setup 20 | Prior pivot (2 touches, 1.1x vol) @ 42.24 | High-volume node @ 42.32 | RSI overbought (71) | Extended 3.2 ATR from 20 EMA</t>
+        <v>51.1</v>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>Bearish engulfing | Fib 78.6% retrace @ 92.43 | Major pivot zone (14 touches, 2.7x vol) @ 92.79 | Volume POC @ 91.53 | Bearish RSI divergence (51) | Volume 1.8x average</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
@@ -956,7 +956,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N8" s="11" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -965,7 +965,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -973,102 +973,102 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>0.633</v>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>At risk</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>0.911</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="F9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>504.36</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>Bearish engulfing | Fib 61.8% retrace @ 511.18 | Major pivot zone (3 touches, 1.4x vol) @ 505.57 | High-volume node @ 505.80 | Bearish RSI divergence (63)</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>306.34</v>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="J9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 53% of range | Time count: TD setup 10 | Fib 50.0% retrace @ 310.98 | Prior pivot (1 touch, 1.4x vol) @ 312.88 | High-volume node @ 311.94 | Tagged upper Bollinger band</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N9" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>NOC</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>561.58</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="J10" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="L10" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 65% of range | Time count: TD setup 15 | Fib 78.6% retrace @ 565.76 | Prior pivot (2 touches, 1.2x vol) @ 575.43 | Bearish RSI divergence (67) | Extended 2.9 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M10" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="G10" s="2" t="n">
+        <v>430</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>-4.12</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Bottoming tail (new low rejected), tail 53% of range | Major pivot zone (3 touches, 1.5x vol) @ 414.52 | High-volume node @ 423.56 | Tagged lower Bollinger band | Extended 2.9 ATR from 20 EMA | Volume 1.6x average</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1077,7 +1077,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -1085,102 +1085,102 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>1036.7</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 65% of range | Fib 78.6% retrace @ 1078.54 | Major pivot zone (8 touches, 1.8x vol) @ 1043.32 | High-volume node @ 1073.68 | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>UHS</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Likely to confirm</t>
         </is>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>88.43000000000001</v>
-      </c>
-      <c r="H11" s="7" t="n">
-        <v>-2.22</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J11" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="L11" s="10" t="inlineStr">
-        <is>
-          <t>Bearish engulfing | Fib 78.6% retrace @ 92.43 | Major pivot zone (14 touches, 2.7x vol) @ 92.79 | Volume POC @ 91.53 | Bearish RSI divergence (51) | Volume 1.7x average</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N11" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>DOV</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>209.34</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I12" s="7" t="n">
+      <c r="D12" s="4" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="F12" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="L12" s="10" t="inlineStr">
-        <is>
-          <t>Doji (indecision at extreme) | Fib 50.0% retrace @ 208.52 | Major pivot zone (3 touches, 1.6x vol) @ 209.50 | RSI overbought (73) | Tagged upper Bollinger band | Extended 3.0 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="G12" s="2" t="n">
+        <v>176.32</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Bottoming tail, tail 59% of range | Fib 38.2% retrace @ 171.84 | Major pivot zone (4 touches, 1.5x vol) @ 174.58 | High-volume node @ 168.36 | Tagged lower Bollinger band</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1189,7 +1189,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>ALGN</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -1197,38 +1197,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>0.997</v>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>At risk</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>0.027</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="F13" s="7" t="n">
         <v>5</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>501.81</v>
+        <v>153.22</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-1.25</v>
+        <v>-0.26</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>-2</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="L13" s="10" t="inlineStr">
-        <is>
-          <t>Bearish engulfing | Fib 61.8% retrace @ 511.18 | Major pivot zone (3 touches, 1.4x vol) @ 505.57 | High-volume node @ 505.80 | Bearish RSI divergence (60)</t>
+        <v>56.7</v>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | Time count: 8 up bars since the last down bar | Fib 38.2% retrace @ 158.27 | Major pivot zone (3 touches, 2.4x vol) @ 154.53 | Volume 1.7x average</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -1236,175 +1236,175 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>CINF</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>At risk</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>181.99</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 54% of range | Time count: TD setup 15 | Prior pivot (1 touch, 1.7x vol) @ 185.27 | RSI overbought (71) | Extended 3.4 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>LDOS</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Likely to confirm</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
-        <v>0.997</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>430.77</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>-3.95</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>Bottoming tail (new low rejected), tail 56% of range | Major pivot zone (3 touches, 1.5x vol) @ 414.52 | High-volume node @ 423.56 | Tagged lower Bollinger band | Extended 2.9 ATR from 20 EMA | Volume 1.6x average</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N14" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>APP</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>0.504</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="F15" s="2" t="n">
+      <c r="D15" s="8" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F15" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G15" s="2" t="n">
-        <v>256.61</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>-7</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>Bottoming tail (new low rejected), tail 50% of range | Time count: 9 down bars since the last up bar | Trendline (falling support) @ 253.65 | Bullish RSI divergence (35) | Tagged lower Bollinger band</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="inlineStr">
+      <c r="G15" s="7" t="n">
+        <v>140.66</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 58% of range | Time count: TD setup 15 | Prior pivot (1 touch, 0.9x vol) @ 142.02 | RSI overbought (73) | Extended 3.4 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>UHS</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="F16" s="2" t="n">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>NDAQ</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F16" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="2" t="n">
-        <v>176.52</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>Bottoming tail, tail 59% of range | Fib 38.2% retrace @ 171.84 | Major pivot zone (4 touches, 1.5x vol) @ 174.58 | High-volume node @ 168.36 | Tagged lower Bollinger band</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N16" s="6" t="inlineStr">
+      <c r="G16" s="7" t="n">
+        <v>105.36</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 47% of range | Time count: 10 bars without a lower low | RSI overbought (74) | Tagged upper Bollinger band | Extended 4.1 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1413,7 +1413,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>NSC</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -1421,38 +1421,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>0.5570000000000001</v>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>At risk</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>0.522</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>5.5</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>1368.15</v>
+        <v>341.93</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>6.2</v>
+        <v>1.14</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>74</v>
-      </c>
-      <c r="L17" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 51% of range | Fib 1.27 extension @ 1424.82 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 1.6x average</t>
+        <v>66.59999999999999</v>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 51% of range | Major pivot zone (1 touch, 2.1x vol) @ 343.63 | Bearish RSI divergence (67) | Tagged upper Bollinger band | Extended 2.8 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
@@ -1460,63 +1460,63 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N17" s="11" t="inlineStr">
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>ALGN</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="E18" s="7" t="n">
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E18" s="2" t="n">
         <v>5.5</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>153.94</v>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I18" s="7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J18" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="L18" s="10" t="inlineStr">
-        <is>
-          <t>Doji (indecision at extreme) | Time count: 8 up bars since the last down bar | Fib 38.2% retrace @ 158.27 | Major pivot zone (3 touches, 2.4x vol) @ 154.53 | Volume 1.7x average</t>
-        </is>
-      </c>
-      <c r="M18" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N18" s="11" t="inlineStr">
+      <c r="G18" s="2" t="n">
+        <v>65.44</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>-12</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>Bottoming tail (new low rejected), tail 74% of range | Time count: TD setup 11 | Prior pivot (1 touch, 1.4x vol) @ 65.41 | Trendline (falling support) @ 64.82 | Tagged lower Bollinger band</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1525,7 +1525,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -1533,38 +1533,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>0.844</v>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>At risk</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>0.769</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="F19" s="7" t="n">
         <v>5</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>181.66</v>
+        <v>1171.82</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="L19" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 54% of range | Time count: TD setup 15 | Prior pivot (1 touch, 1.7x vol) @ 185.27 | RSI overbought (71) | Extended 3.4 ATR from 20 EMA</t>
+        <v>66.7</v>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 62% of range | Time count: 7 up bars since the last down bar | Prior pivot (2 touches, 1.0x vol) @ 1180.97 | Tagged upper Bollinger band | Extended 2.5 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
@@ -1572,7 +1572,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N19" s="11" t="inlineStr">
+      <c r="N19" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1581,7 +1581,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>LDOS</t>
+          <t>TFC</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -1589,38 +1589,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>0.9350000000000001</v>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>At risk</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>0.27</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>5</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>140.84</v>
+        <v>49.26</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>0.89</v>
+        <v>1.75</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="L20" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 58% of range | Time count: TD setup 15 | Prior pivot (1 touch, 0.9x vol) @ 142.02 | RSI overbought (73) | Extended 3.4 ATR from 20 EMA</t>
+        <v>61.4</v>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | Fib 50.0% retrace @ 49.37 | Major pivot zone (7 touches, 1.4x vol) @ 49.39 | High-volume node @ 49.73 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
@@ -1628,7 +1628,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N20" s="11" t="inlineStr">
+      <c r="N20" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1637,7 +1637,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -1645,25 +1645,25 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>0.996</v>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>At risk</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>0.421</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>5</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>105.37</v>
+        <v>165.3</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>-0.17</v>
+        <v>-0.02</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>8</v>
@@ -1672,11 +1672,11 @@
         <v>-1</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="L21" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 47% of range | Time count: 10 bars without a lower low | RSI overbought (74) | Tagged upper Bollinger band | Extended 4.1 ATR from 20 EMA</t>
+        <v>72.7</v>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | Time count: 7 up bars since the last down bar | Prior pivot (1 touch, 1.4x vol) @ 166.18 | RSI overbought (73) | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
@@ -1684,7 +1684,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N21" s="11" t="inlineStr">
+      <c r="N21" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1693,7 +1693,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>NSC</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -1701,38 +1701,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>0.6870000000000001</v>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>0.999</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>341.47</v>
+        <v>62.39</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>1</v>
+        <v>-5.98</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="L22" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 57% of range | Major pivot zone (1 touch, 2.1x vol) @ 343.63 | Bearish RSI divergence (66) | Tagged upper Bollinger band | Extended 2.8 ATR from 20 EMA</t>
+        <v>46.6</v>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail, tail 71% of range | Major pivot zone (4 touches, 1.8x vol) @ 65.08 | High-volume node @ 63.60 | Trendline (rising resistance) @ 64.96</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -1740,7 +1740,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N22" s="11" t="inlineStr">
+      <c r="N22" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1749,7 +1749,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>KEY</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -1757,38 +1757,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D23" s="9" t="n">
-        <v>0.531</v>
+      <c r="D23" s="8" t="n">
+        <v>0.66</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>165.1</v>
+        <v>21.43</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>-0.14</v>
+        <v>1.11</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="L23" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail, tail 47% of range | Time count: 7 up bars since the last down bar | Prior pivot (1 touch, 1.4x vol) @ 166.18 | RSI overbought (72) | Tagged upper Bollinger band</t>
+        <v>64.3</v>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 52% of range | Fib 50.0% retrace @ 21.65 | Major pivot zone (3 touches, 1.3x vol) @ 21.45 | High-volume node @ 21.64</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
@@ -1796,7 +1796,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N23" s="11" t="inlineStr">
+      <c r="N23" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1805,7 +1805,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>BF-B</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1819,152 +1819,152 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.772</v>
+        <v>0.71</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="F24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>Bottoming tail (new low rejected), tail 56% of range | Fib 50.0% retrace @ 27.22 | Major pivot zone (4 touches, 4.9x vol) @ 27.85 | High-volume node @ 27.83</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="E25" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G24" s="2" t="n">
-        <v>65.63</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>-12</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>Bottoming tail (new low rejected), tail 74% of range | Time count: TD setup 11 | Prior pivot (1 touch, 1.4x vol) @ 65.41 | Trendline (falling support) @ 64.82 | Tagged lower Bollinger band</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N24" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>BLK</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E25" s="7" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="F25" s="7" t="n">
+      <c r="F25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>93.19</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>Bottoming tail, tail 93% of range | Fib 38.2% retrace @ 92.09 | Major pivot zone (4 touches, 1.2x vol) @ 91.65 | High-volume node @ 91.89</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G25" s="7" t="n">
-        <v>1171.11</v>
-      </c>
-      <c r="H25" s="7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="I25" s="7" t="n">
+      <c r="F26" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>239.71</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I26" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J25" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="L25" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 66% of range | Time count: 7 up bars since the last down bar | Prior pivot (2 touches, 1.0x vol) @ 1180.97 | Tagged upper Bollinger band | Extended 2.5 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M25" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N25" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>TFC</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="n">
-        <v>0.318</v>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="F26" s="7" t="n">
+      <c r="J26" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G26" s="7" t="n">
-        <v>49.28</v>
-      </c>
-      <c r="H26" s="7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="I26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="L26" s="10" t="inlineStr">
-        <is>
-          <t>Doji (indecision at extreme) | Fib 50.0% retrace @ 49.37 | Major pivot zone (7 touches, 1.4x vol) @ 49.39 | High-volume node @ 49.73 | Tagged upper Bollinger band</t>
-        </is>
-      </c>
-      <c r="M26" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N26" s="11" t="inlineStr">
+      <c r="K26" s="2" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>Bottoming tail, tail 72% of range | Major pivot zone (2 touches, 2.1x vol) @ 229.88 | High-volume node @ 233.72 | Trendline (rising support) @ 236.19</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1973,7 +1973,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -1981,38 +1981,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>0.879</v>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>0.837</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="F27" s="7" t="n">
         <v>4</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>62.83</v>
+        <v>207.93</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>-5.31</v>
+        <v>1.49</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="L27" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail, tail 65% of range | Major pivot zone (4 touches, 1.8x vol) @ 65.08 | High-volume node @ 63.60 | Trendline (rising resistance) @ 64.96</t>
+        <v>59.6</v>
+      </c>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 67% of range | Major pivot zone (8 touches, 1.8x vol) @ 210.88 | Trendline (falling resistance) @ 209.74 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -2020,7 +2020,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N27" s="11" t="inlineStr">
+      <c r="N27" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2029,7 +2029,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>KEY</t>
+          <t>HBAN</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -2037,38 +2037,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D28" s="9" t="n">
-        <v>0.572</v>
+      <c r="D28" s="8" t="n">
+        <v>0.9360000000000001</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="F28" s="7" t="n">
         <v>4</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>21.47</v>
+        <v>15.91</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>64.7</v>
-      </c>
-      <c r="L28" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 52% of range | Fib 50.0% retrace @ 21.65 | Major pivot zone (3 touches, 1.3x vol) @ 21.45 | High-volume node @ 21.64</t>
+        <v>58.1</v>
+      </c>
+      <c r="L28" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 59% of range | Time count: 8 up bars since the last down bar | Fib 38.2% retrace @ 16.19 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -2076,175 +2076,175 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N28" s="11" t="inlineStr">
+      <c r="N28" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>BF-B</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>PFG</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>113.26</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="7" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | Time count: 7 up bars since the last down bar | Major pivot zone (3 touches, 1.0x vol) @ 114.93 | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>WMB</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>75.02</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 71% of range | Fib 78.6% retrace @ 76.45 | Major pivot zone (10 touches, 1.5x vol) @ 75.24 | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N30" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>BAX</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Likely to confirm</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n">
-        <v>0.776</v>
-      </c>
-      <c r="E29" s="2" t="n">
+      <c r="D31" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F31" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F29" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>28.01</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="I29" s="2" t="n">
+      <c r="G31" s="7" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>-7.19</v>
+      </c>
+      <c r="I31" s="7" t="n">
         <v>-2</v>
       </c>
-      <c r="J29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>Bottoming tail (new low rejected), tail 62% of range | Fib 50.0% retrace @ 27.22 | Major pivot zone (4 touches, 4.9x vol) @ 27.85 | High-volume node @ 27.83</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N29" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>93.08</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>Bottoming tail, tail 98% of range | Fib 38.2% retrace @ 92.09 | Major pivot zone (4 touches, 1.2x vol) @ 91.65 | High-volume node @ 91.89</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N30" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>IEX</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>0.998</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>238.93</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>Bottoming tail, tail 77% of range | Major pivot zone (2 touches, 2.1x vol) @ 229.88 | High-volume node @ 233.72 | Trendline (rising support) @ 236.19</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N31" s="6" t="inlineStr">
+      <c r="J31" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>Bearish engulfing | Prior pivot (2 touches, 0.9x vol) @ 25.84 | Bearish RSI divergence (42) | Tagged upper Bollinger band | Volume 2.1x average</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N31" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2253,7 +2253,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>HBAN</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -2261,38 +2261,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D32" s="9" t="n">
-        <v>0.771</v>
+      <c r="D32" s="8" t="n">
+        <v>0.799</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="F32" s="7" t="n">
         <v>4</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>15.93</v>
+        <v>60.5</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="L32" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 59% of range | Time count: 8 up bars since the last down bar | Fib 38.2% retrace @ 16.19 | Tagged upper Bollinger band</t>
+        <v>60.5</v>
+      </c>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 64% of range | Time count: 7 up bars since the last down bar | Prior pivot (1 touch, 0.8x vol) @ 60.89 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -2300,63 +2300,63 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N32" s="11" t="inlineStr">
+      <c r="N32" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>IRM</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="n">
-        <v>0.573</v>
-      </c>
-      <c r="E33" s="7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="F33" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G33" s="7" t="n">
-        <v>118.33</v>
-      </c>
-      <c r="H33" s="7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I33" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J33" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="L33" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 55% of range | Fib 50.0% retrace @ 120.42 | Major pivot zone (7 touches, 1.6x vol) @ 118.99 | Tagged upper Bollinger band</t>
-        </is>
-      </c>
-      <c r="M33" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N33" s="11" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>MGM</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>28.69</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>Bullish engulfing | Bullish RSI divergence (37) | Tagged lower Bollinger band | Extended 2.7 ATR from 20 EMA | Volume 1.9x average</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N33" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2365,7 +2365,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -2373,38 +2373,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D34" s="9" t="n">
-        <v>0.604</v>
+      <c r="D34" s="8" t="n">
+        <v>0.911</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="F34" s="7" t="n">
         <v>4</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>113.24</v>
+        <v>65.13</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="J34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="L34" s="10" t="inlineStr">
-        <is>
-          <t>Doji (indecision at extreme) | Time count: 7 up bars since the last down bar | Major pivot zone (3 touches, 1.0x vol) @ 114.93 | Tagged upper Bollinger band</t>
+        <v>59.4</v>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail, tail 62% of range | Fib 50.0% retrace @ 65.85 | Prior pivot (2 touches, 1.4x vol) @ 65.45 | High-volume node @ 65.93</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
@@ -2412,7 +2412,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N34" s="11" t="inlineStr">
+      <c r="N34" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2421,7 +2421,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>WMB</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -2429,38 +2429,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>At risk</t>
         </is>
       </c>
-      <c r="D35" s="9" t="n">
-        <v>0.701</v>
+      <c r="D35" s="8" t="n">
+        <v>0.067</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="F35" s="7" t="n">
         <v>4</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>75.06</v>
+        <v>119.59</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>1.06</v>
+        <v>0.77</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="L35" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 68% of range | Fib 78.6% retrace @ 76.45 | Major pivot zone (10 touches, 1.5x vol) @ 75.24 | Tagged upper Bollinger band</t>
+        <v>88.7</v>
+      </c>
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | Time count: TD setup 24 | RSI overbought (89) | Extended 4.5 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
@@ -2468,63 +2468,63 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N35" s="11" t="inlineStr">
+      <c r="N35" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>0.626</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="F36" s="2" t="n">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>At risk</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F36" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G36" s="2" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>Bottoming tail (new low rejected), tail 59% of range | Time count: TD setup 9 | Trendline (falling support) @ 60.70 | Extended 3.0 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N36" s="6" t="inlineStr">
+      <c r="G36" s="7" t="n">
+        <v>222.24</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" s="7" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="L36" s="9" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | Time count: TD setup 11 | Fib 50.0% retrace @ 224.11 | Prior pivot (2 touches, 1.5x vol) @ 221.25</t>
+        </is>
+      </c>
+      <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N36" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2533,7 +2533,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>SHW</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2541,38 +2541,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>0.5659999999999999</v>
+        <v>1</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>240.37</v>
+        <v>330.02</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>-5.28</v>
+        <v>2.87</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>40</v>
+        <v>50.4</v>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>Bottoming tail (new low rejected), tail 53% of range | Fib 61.8% retrace @ 228.55 | Major pivot zone (3 touches, 1.4x vol) @ 238.69 | Tagged lower Bollinger band</t>
+          <t>Bottoming tail, tail 81% of range | Fib 61.8% retrace @ 320.56 | Prior pivot (2 touches, 1.5x vol) @ 326.09 | Volume POC @ 320.98</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>BAX</t>
+          <t>CASY</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -2602,33 +2602,33 @@
           <t>Likely to confirm</t>
         </is>
       </c>
-      <c r="D38" s="9" t="n">
-        <v>1</v>
+      <c r="D38" s="8" t="n">
+        <v>0.992</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>23.73</v>
+        <v>674.52</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>-6.79</v>
+        <v>0.67</v>
       </c>
       <c r="I38" s="7" t="n">
         <v>-2</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="L38" s="10" t="inlineStr">
-        <is>
-          <t>Bearish engulfing | Prior pivot (2 touches, 0.9x vol) @ 25.84 | Bearish RSI divergence (42) | Tagged upper Bollinger band | Volume 2.0x average</t>
+        <v>50.9</v>
+      </c>
+      <c r="L38" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail, tail 47% of range | Major pivot zone (2 touches, 6.6x vol) @ 690.37 | High-volume node @ 681.51</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
@@ -2636,7 +2636,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N38" s="11" t="inlineStr">
+      <c r="N38" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2645,7 +2645,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>CIEN</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -2653,38 +2653,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="n">
-        <v>0.122</v>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>0.9330000000000001</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>51.32</v>
+        <v>346.7</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>0.41</v>
+        <v>-4.55</v>
       </c>
       <c r="I39" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" s="7" t="n">
         <v>-1</v>
       </c>
-      <c r="J39" s="7" t="n">
-        <v>2</v>
-      </c>
       <c r="K39" s="7" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="L39" s="10" t="inlineStr">
-        <is>
-          <t>Doji (indecision at extreme) | Time count: TD setup 20 | Trendline (rising resistance) @ 51.68 | RSI overbought (70)</t>
+        <v>46.3</v>
+      </c>
+      <c r="L39" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail, tail 61% of range | Major pivot zone (6 touches, 1.4x vol) @ 366.58 | Volume POC @ 351.24</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
@@ -2692,7 +2692,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N39" s="11" t="inlineStr">
+      <c r="N39" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2701,7 +2701,7 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>GNRC</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -2709,38 +2709,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="n">
-        <v>0.731</v>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>0.791</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>275.11</v>
+        <v>203.3</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>1.5</v>
+        <v>0.97</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J40" s="7" t="n">
         <v>4</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="L40" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 61% of range | Time count: TD setup 8 | Prior pivot (1 touch, 1.0x vol) @ 281.07 | Tagged upper Bollinger band</t>
+        <v>51.7</v>
+      </c>
+      <c r="L40" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 86% of range | Major pivot zone (2 touches, 3.0x vol) @ 211.79 | Volume POC @ 204.31</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
@@ -2748,7 +2748,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N40" s="11" t="inlineStr">
+      <c r="N40" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2757,7 +2757,7 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -2765,214 +2765,214 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D41" s="9" t="n">
-        <v>0.73</v>
+      <c r="D41" s="8" t="n">
+        <v>0.9389999999999999</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="F41" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" s="7" t="n">
+        <v>82.04000000000001</v>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I41" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J41" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="7" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="L41" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 75% of range | Major pivot zone (3 touches, 2.4x vol) @ 82.62 | Volume POC @ 82.88</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N41" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>FFIV</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>At risk</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="E42" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G41" s="7" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="H41" s="7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="I41" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="L41" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 65% of range | Time count: 7 up bars since the last down bar | Prior pivot (1 touch, 0.8x vol) @ 60.89 | Tagged upper Bollinger band</t>
-        </is>
-      </c>
-      <c r="M41" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N41" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="F42" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>360.78</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | RSI oversold (26) | Tagged lower Bollinger band | Extended 4.2 ATR from 20 EMA | Volume 2.1x average</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N42" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D42" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E42" s="7" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="F42" s="7" t="n">
+      <c r="D43" s="4" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="E43" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G42" s="7" t="n">
-        <v>65.18000000000001</v>
-      </c>
-      <c r="H42" s="7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I42" s="7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J42" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="L42" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail, tail 62% of range | Fib 50.0% retrace @ 65.85 | Prior pivot (2 touches, 1.4x vol) @ 65.45 | High-volume node @ 65.93</t>
-        </is>
-      </c>
-      <c r="M42" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N42" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>HAS</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E43" s="7" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="F43" s="7" t="n">
+      <c r="F43" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G43" s="7" t="n">
-        <v>119.41</v>
-      </c>
-      <c r="H43" s="7" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I43" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="J43" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="L43" s="10" t="inlineStr">
-        <is>
-          <t>Doji (indecision at extreme) | Time count: TD setup 24 | RSI overbought (89) | Extended 4.5 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M43" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N43" s="11" t="inlineStr">
+      <c r="G43" s="2" t="n">
+        <v>180.21</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>Bottoming tail, tail 67% of range | High-volume node @ 173.84 | Trendline (rising support) @ 179.82 | Volume 2.2x average</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N43" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>HON</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="E44" s="7" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="F44" s="7" t="n">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G44" s="7" t="n">
-        <v>222.73</v>
-      </c>
-      <c r="H44" s="7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="I44" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="J44" s="7" t="n">
+      <c r="F44" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>659.8099999999999</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K44" s="7" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="L44" s="10" t="inlineStr">
-        <is>
-          <t>Doji (indecision at extreme) | Time count: TD setup 11 | Fib 50.0% retrace @ 224.11 | Prior pivot (2 touches, 1.5x vol) @ 221.25</t>
-        </is>
-      </c>
-      <c r="M44" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N44" s="11" t="inlineStr">
+      <c r="K44" s="2" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>Bullish engulfing | Fib 50.0% retrace @ 616.05 | Major pivot zone (3 touches, 1.5x vol) @ 619.72</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N44" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2981,7 +2981,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>SHW</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2989,270 +2989,270 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C45" s="12" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
       <c r="D45" s="4" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.865</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="F45" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>150.34</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>Bottoming tail, tail 65% of range | Major pivot zone (2 touches, 2.4x vol) @ 149.50 | Tagged lower Bollinger band</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N45" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>At risk</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>183.07</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | Fib 38.2% retrace @ 185.98 | Major pivot zone (10 touches, 2.3x vol) @ 180.72</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N46" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>At risk</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>220.54</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | Major pivot zone (1 touch, 1.9x vol) @ 216.04 | High-volume node @ 216.25</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N47" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>GLW</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>At risk</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>128.55</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | Major pivot zone (2 touches, 2.0x vol) @ 125.03 | Volume POC @ 129.44</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N48" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>WAB</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>284.46</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J49" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G45" s="2" t="n">
-        <v>328.52</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" s="2" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>Bottoming tail, tail 88% of range | Fib 61.8% retrace @ 320.56 | Prior pivot (2 touches, 1.5x vol) @ 326.09 | Volume POC @ 320.98</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N45" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>AZO</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="E46" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F46" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G46" s="7" t="n">
-        <v>3132.97</v>
-      </c>
-      <c r="H46" s="7" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="I46" s="7" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J46" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K46" s="7" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="L46" s="10" t="inlineStr">
-        <is>
-          <t>Bearish engulfing | Fib 61.8% retrace @ 3243.91 | Major pivot zone (6 touches, 2.2x vol) @ 3190.97</t>
-        </is>
-      </c>
-      <c r="M46" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N46" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>CASY</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E47" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F47" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G47" s="7" t="n">
-        <v>676.05</v>
-      </c>
-      <c r="H47" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I47" s="7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J47" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="L47" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail, tail 47% of range | Major pivot zone (2 touches, 6.6x vol) @ 690.37 | High-volume node @ 681.51</t>
-        </is>
-      </c>
-      <c r="M47" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N47" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>CIEN</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="n">
-        <v>0.512</v>
-      </c>
-      <c r="E48" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F48" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G48" s="7" t="n">
-        <v>350.85</v>
-      </c>
-      <c r="H48" s="7" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="I48" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="L48" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail, tail 51% of range | Major pivot zone (6 touches, 1.4x vol) @ 366.58 | Volume POC @ 351.24</t>
-        </is>
-      </c>
-      <c r="M48" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N48" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>NEE</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="n">
-        <v>0.752</v>
-      </c>
-      <c r="E49" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F49" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G49" s="7" t="n">
-        <v>82.14</v>
-      </c>
-      <c r="H49" s="7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="I49" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="L49" s="10" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 66% of range | Major pivot zone (3 touches, 2.4x vol) @ 82.62 | Volume POC @ 82.88</t>
-        </is>
-      </c>
-      <c r="M49" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N49" s="11" t="inlineStr">
+      <c r="K49" s="2" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>Bullish engulfing | Fib 50.0% retrace @ 278.61 | Trendline (rising support) @ 277.12</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N49" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -3261,7 +3261,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>HUBB</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3269,38 +3269,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>At risk</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.271</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>181.15</v>
+        <v>434.52</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>6.88</v>
+        <v>-0.64</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>45.5</v>
+        <v>36.2</v>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>Bottoming tail, tail 67% of range | High-volume node @ 173.84 | Trendline (rising support) @ 179.82 | Volume 2.2x average</t>
+          <t>Doji (indecision at extreme) | Major pivot zone (3 touches, 1.1x vol) @ 438.28 | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3331,32 +3331,32 @@
         </is>
       </c>
       <c r="D51" s="4" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>657.05</v>
+        <v>151.7</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>2.56</v>
+        <v>1.84</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>2</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>52.8</v>
+        <v>46.7</v>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>Bullish engulfing | Fib 50.0% retrace @ 616.05 | Major pivot zone (3 touches, 1.5x vol) @ 619.72</t>
+          <t>Bottoming tail, tail 50% of range | Fib 38.2% retrace @ 149.71 | Prior pivot (1 touch, 1.1x vol) @ 150.46</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -3373,7 +3373,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3387,32 +3387,32 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>3.75</v>
+        <v>7</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>150.99</v>
+        <v>40.48</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>2.06</v>
+        <v>1.43</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>36.1</v>
+        <v>31.5</v>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>Bottoming tail, tail 72% of range | Major pivot zone (2 touches, 2.4x vol) @ 149.50 | Tagged lower Bollinger band</t>
+          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 38.34) | Bottoming tail (new low rejected), tail 59% of range | Major pivot zone (1 touch, 2.5x vol) @ 38.32 | Trendline (falling support) @ 37.65 | Bullish RSI divergence (31) | Tagged lower Bollinger band | Extended 3.0 ATR from 20 EMA | Volume 2.3x average</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -3429,7 +3429,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>GPC</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3437,38 +3437,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C53" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D53" s="4" t="n">
-        <v>0.159</v>
+        <v>1</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>183.74</v>
+        <v>121.87</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>-1.59</v>
+        <v>0.4</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>44.2</v>
+        <v>38.7</v>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>Doji (indecision at extreme) | Fib 38.2% retrace @ 185.98 | Major pivot zone (10 touches, 2.3x vol) @ 180.72</t>
+          <t>Setup from 2 bars ago, still near entry (+0.0 ATR since signal; stop beyond 120.18) | Bottoming tail (new low rejected), tail 59% of range | Fib 38.2% retrace @ 119.82 | Major pivot zone (4 touches, 1.8x vol) @ 121.77 | Trendline (falling support) @ 121.46 | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -3485,7 +3485,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3495,36 +3495,36 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>At risk</t>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>0.134</v>
+        <v>1</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>128.89</v>
+        <v>177.83</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>-1.76</v>
+        <v>2.27</v>
       </c>
       <c r="I54" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J54" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J54" s="2" t="n">
-        <v>-1</v>
-      </c>
       <c r="K54" s="2" t="n">
-        <v>39.5</v>
+        <v>43.1</v>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>Doji (indecision at extreme) | Major pivot zone (2 touches, 2.0x vol) @ 125.03 | Volume POC @ 129.44</t>
+          <t>Setup from 1 bar ago, still near entry (+0.8 ATR since signal; stop beyond 170.14) | Bullish engulfing | Major pivot zone (5 touches, 1.3x vol) @ 172.11 | Trendline (falling support) @ 170.53 | Bullish RSI divergence (43) | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>WAB</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3555,32 +3555,32 @@
         </is>
       </c>
       <c r="D55" s="4" t="n">
-        <v>0.951</v>
+        <v>1</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>284.61</v>
+        <v>252.91</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>0.86</v>
+        <v>-0.36</v>
       </c>
       <c r="I55" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="J55" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J55" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="K55" s="2" t="n">
-        <v>50.9</v>
+        <v>31.1</v>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>Bullish engulfing | Fib 50.0% retrace @ 278.61 | Trendline (rising support) @ 277.12</t>
+          <t>Setup from 2 bars ago, still near entry (+0.9 ATR since signal; stop beyond 235.21) | Bottoming tail, tail 87% of range | Time count: TD setup 14 | Prior pivot (2 touches, 1.1x vol) @ 241.07 | High-volume node @ 234.92 | Extended 2.8 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -3597,7 +3597,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>FDXF</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3605,38 +3605,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>0.714</v>
+        <v>1</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>102.47</v>
+        <v>107.48</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0.05</v>
+        <v>-0.78</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>26.2</v>
+        <v>38.5</v>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>Bottoming tail, tail 64% of range | RSI oversold (26) | Tagged lower Bollinger band</t>
+          <t>Setup from 1 bar ago, still near entry (-0.2 ATR since signal; stop beyond 103.48) | Bottoming tail (new low rejected), tail 90% of range | Prior pivot (2 touches, 1.8x vol) @ 106.96 | Trendline (falling support) @ 103.62 | Bullish RSI divergence (38) | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3661,38 +3661,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>At risk</t>
         </is>
       </c>
       <c r="D57" s="4" t="n">
-        <v>0.908</v>
+        <v>1</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>151.41</v>
+        <v>887.6</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>1.64</v>
+        <v>1.09</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>46.2</v>
+        <v>43</v>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>Bottoming tail, tail 50% of range | Fib 38.2% retrace @ 149.71 | Prior pivot (1 touch, 1.1x vol) @ 150.46</t>
+          <t>Setup from 1 bar ago, still near entry (+0.2 ATR since signal; stop beyond 836.24) | Bottoming tail, tail 72% of range | Time count: TD setup 10 | Major pivot zone (6 touches, 2.1x vol) @ 870.38 | Volume 2.3x average</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -3709,7 +3709,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>HSIC</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3717,38 +3717,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C58" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>40.5</v>
+        <v>86.19</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>31.5</v>
+        <v>48.1</v>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 38.34) | Bottoming tail (new low rejected), tail 59% of range | Major pivot zone (1 touch, 2.5x vol) @ 38.32 | Trendline (falling support) @ 37.65 | Bullish RSI divergence (31) | Tagged lower Bollinger band | Extended 3.0 ATR from 20 EMA | Volume 2.3x average</t>
+          <t>Setup from 1 bar ago, still near entry (+0.7 ATR since signal; stop beyond 83.97) | Bullish engulfing | Fib 38.2% retrace @ 83.21 | Major pivot zone (1 touch, 1.9x vol) @ 84.15 | High-volume node @ 84.67</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GPC</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3775,36 +3775,36 @@
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>At risk</t>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D59" s="4" t="n">
-        <v>0.989</v>
+        <v>1</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>121.57</v>
+        <v>634.17</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>0.14</v>
+        <v>4.5</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>38.7</v>
+        <v>45.8</v>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>Setup from 2 bars ago, still near entry (-0.1 ATR since signal; stop beyond 120.18) | Bottoming tail (new low rejected), tail 59% of range | Fib 38.2% retrace @ 119.82 | Major pivot zone (4 touches, 1.8x vol) @ 121.77 | Trendline (falling support) @ 121.46 | Tagged lower Bollinger band</t>
+          <t>Setup from 1 bar ago, still near entry (+1.0 ATR since signal; stop beyond 581.78) | Bottoming tail, tail 66% of range | Time count: TD setup 12 | Major pivot zone (5 touches, 1.5x vol) @ 594.79 | Volume 1.8x average</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3829,38 +3829,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>At risk</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>177.94</v>
+        <v>245.89</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>2.33</v>
+        <v>1.21</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>43.1</v>
+        <v>57</v>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.8 ATR since signal; stop beyond 170.14) | Bullish engulfing | Major pivot zone (5 touches, 1.3x vol) @ 172.11 | Trendline (falling support) @ 170.53 | Bullish RSI divergence (43) | Tagged lower Bollinger band</t>
+          <t>Setup from 1 bar ago, still near entry (+0.2 ATR since signal; stop beyond 228.81) | Bottoming tail, tail 86% of range | Time count: TD setup 14 | Major pivot zone (5 touches, 3.3x vol) @ 226.83 | Volume 3.3x average</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3885,38 +3885,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C61" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D61" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>254.14</v>
+        <v>102.17</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>0.13</v>
+        <v>-0.24</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>-15</v>
+        <v>-6</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>31.1</v>
+        <v>26</v>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>Setup from 2 bars ago, still near entry (+0.9 ATR since signal; stop beyond 235.21) | Bottoming tail, tail 87% of range | Time count: TD setup 14 | Prior pivot (2 touches, 1.1x vol) @ 241.07 | High-volume node @ 234.92 | Extended 2.8 ATR from 20 EMA</t>
+          <t>Setup from 1 bar ago, still near entry (-0.1 ATR since signal; stop beyond 100.50) | Bottoming tail, tail 62% of range | Prior pivot (1 touch, 1.6x vol) @ 99.18 | RSI oversold (26) | Tagged lower Bollinger band | Extended 2.8 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>FDXF</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3941,38 +3941,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>At risk</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>107.9</v>
+        <v>56.99</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>-0.4</v>
+        <v>0.77</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>38.5</v>
+        <v>52.4</v>
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (-0.1 ATR since signal; stop beyond 103.48) | Bottoming tail (new low rejected), tail 90% of range | Prior pivot (2 touches, 1.8x vol) @ 106.96 | Trendline (falling support) @ 103.62 | Bullish RSI divergence (38) | Tagged lower Bollinger band</t>
+          <t>Setup from 2 bars ago, still near entry (+0.6 ATR since signal; stop beyond 54.34) | Bottoming tail (new low rejected), tail 47% of range | Fib 38.2% retrace @ 53.99 | Prior pivot (2 touches, 1.3x vol) @ 54.64 | Trendline (rising support) @ 54.50 | Volume 1.8x average</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>EME</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
+      <c r="C63" s="12" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
@@ -4006,29 +4006,29 @@
         <v>1</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>892.8200000000001</v>
+        <v>687.36</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="I63" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 836.24) | Bottoming tail, tail 72% of range | Time count: TD setup 10 | Major pivot zone (6 touches, 2.1x vol) @ 870.38 | Volume 2.3x average</t>
+          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 665.55) | Bottoming tail, tail 68% of range | Time count: TD setup 12 | Major pivot zone (1 touch, 2.0x vol) @ 668.46</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -4045,7 +4045,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>HSIC</t>
+          <t>GPN</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4053,38 +4053,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D64" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>86.19</v>
+        <v>85.53</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>1.45</v>
+        <v>2.37</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>48.1</v>
+        <v>49.7</v>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.7 ATR since signal; stop beyond 83.97) | Bullish engulfing | Fib 38.2% retrace @ 83.21 | Major pivot zone (1 touch, 1.9x vol) @ 84.15 | High-volume node @ 84.67</t>
+          <t>Setup from 1 bar ago, still near entry (+0.8 ATR since signal; stop beyond 80.85) | Bullish engulfing | Fib 38.2% retrace @ 82.29 | Prior pivot (2 touches, 1.7x vol) @ 82.12 | Trendline (rising support) @ 81.14</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -4099,56 +4099,56 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>VRT</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F65" s="2" t="n">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G65" s="2" t="n">
-        <v>247.56</v>
-      </c>
-      <c r="H65" s="2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="2" t="n">
+      <c r="F65" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="K65" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="L65" s="5" t="inlineStr">
-        <is>
-          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 228.81) | Bottoming tail, tail 86% of range | Time count: TD setup 14 | Major pivot zone (5 touches, 3.3x vol) @ 226.83 | Volume 3.3x average</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N65" s="6" t="inlineStr">
+      <c r="G65" s="7" t="n">
+        <v>51.22</v>
+      </c>
+      <c r="H65" s="7" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I65" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="J65" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" s="7" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="L65" s="9" t="inlineStr">
+        <is>
+          <t>Setup from 1 bar ago, still near entry (-0.1 ATR since signal; stop beyond 52.07) | Topping tail, tail 73% of range | Time count: TD setup 19 | Trendline (rising resistance) @ 51.54</t>
+        </is>
+      </c>
+      <c r="M65" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N65" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -4157,7 +4157,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4165,38 +4165,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>1</v>
+        <v>0.839</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>57.24</v>
+        <v>563.47</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>1.23</v>
+        <v>-2.59</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>52.4</v>
+        <v>53.6</v>
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>Setup from 2 bars ago, still near entry (+0.8 ATR since signal; stop beyond 54.34) | Bottoming tail (new low rejected), tail 47% of range | Fib 38.2% retrace @ 53.99 | Prior pivot (2 touches, 1.3x vol) @ 54.64 | Trendline (rising support) @ 54.50 | Volume 1.8x average</t>
+          <t>Setup from 1 bar ago, still near entry (-0.6 ATR since signal; stop beyond 560.52) | Bottoming tail, tail 67% of range | Fib 38.2% retrace @ 557.23 | Major pivot zone (4 touches, 1.1x vol) @ 571.91</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>EME</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4221,25 +4221,25 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C67" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D67" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>687.39</v>
+        <v>44.32</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>1.3</v>
+        <v>0.54</v>
       </c>
       <c r="I67" s="2" t="n">
         <v>1</v>
@@ -4248,11 +4248,11 @@
         <v>3</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>37</v>
+        <v>48.2</v>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 665.55) | Bottoming tail, tail 68% of range | Time count: TD setup 12 | Major pivot zone (1 touch, 2.0x vol) @ 668.46</t>
+          <t>Setup from 1 bar ago, still near entry (+0.2 ATR since signal; stop beyond 43.27) | Bottoming tail, tail 66% of range | Major pivot zone (3 touches, 1.1x vol) @ 42.78 | Trendline (rising support) @ 42.98</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GPN</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4277,38 +4277,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>At risk</t>
         </is>
       </c>
       <c r="D68" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>85.69</v>
+        <v>159.67</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>2.56</v>
+        <v>0.82</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>49.7</v>
+        <v>35.4</v>
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.9 ATR since signal; stop beyond 80.85) | Bullish engulfing | Fib 38.2% retrace @ 82.29 | Prior pivot (2 touches, 1.7x vol) @ 82.12 | Trendline (rising support) @ 81.14</t>
+          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 156.20) | Bottoming tail, tail 50% of range | Fib 78.6% retrace @ 157.06 | Major pivot zone (3 touches, 2.4x vol) @ 156.30</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>IVZ</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4333,13 +4333,13 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>At risk</t>
         </is>
       </c>
       <c r="D69" s="4" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="E69" s="2" t="n">
         <v>4</v>
@@ -4348,23 +4348,23 @@
         <v>3</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>564.6</v>
+        <v>28.93</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>-2.39</v>
+        <v>0.89</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>53.6</v>
+        <v>43</v>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (-0.5 ATR since signal; stop beyond 560.52) | Bottoming tail, tail 67% of range | Fib 38.2% retrace @ 557.23 | Major pivot zone (4 touches, 1.1x vol) @ 571.91</t>
+          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 28.20) | Bottoming tail, tail 68% of range | Fib 61.8% retrace @ 28.57 | Major pivot zone (3 touches, 1.5x vol) @ 28.54</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -4381,7 +4381,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4389,9 +4389,9 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>At risk</t>
         </is>
       </c>
       <c r="D70" s="4" t="n">
@@ -4404,23 +4404,23 @@
         <v>3</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>44.43</v>
+        <v>486.96</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>0.79</v>
+        <v>1.05</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>48.2</v>
+        <v>59</v>
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 43.27) | Bottoming tail, tail 66% of range | Major pivot zone (3 touches, 1.1x vol) @ 42.78 | Trendline (rising support) @ 42.98</t>
+          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 467.24) | Bottoming tail, tail 50% of range | Major pivot zone (2 touches, 2.1x vol) @ 465.90 | High-volume node @ 463.40</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4445,25 +4445,25 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C71" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D71" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>222.08</v>
+        <v>97.04000000000001</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>-2.63</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I71" s="2" t="n">
         <v>1</v>
@@ -4472,11 +4472,11 @@
         <v>3</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>45.7</v>
+        <v>43.7</v>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (-0.3 ATR since signal; stop beyond 217.90) | Bottoming tail, tail 59% of range | Major pivot zone (1 touch, 1.9x vol) @ 216.04 | High-volume node @ 216.25</t>
+          <t>Setup from 1 bar ago, still near entry (+0.0 ATR since signal; stop beyond 94.12) | Bottoming tail, tail 72% of range | Time count: TD setup 11 | Prior pivot (1 touch, 1.2x vol) @ 93.36</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -4493,7 +4493,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>FIX</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4501,38 +4501,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C72" s="12" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Likely to confirm</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>159.79</v>
+        <v>1321.74</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>0.9</v>
+        <v>-1.79</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>3</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>35.4</v>
+        <v>39.4</v>
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.4 ATR since signal; stop beyond 156.20) | Bottoming tail, tail 50% of range | Fib 78.6% retrace @ 157.06 | Major pivot zone (3 touches, 2.4x vol) @ 156.30</t>
+          <t>Setup from 1 bar ago, still near entry (-0.3 ATR since signal; stop beyond 1290.57) | Bottoming tail, tail 68% of range | Time count: TD setup 12 | Volume 1.6x average</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -4547,336 +4547,336 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>IVZ</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" s="2" t="n">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>HII</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="F73" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>317.25</v>
+      </c>
+      <c r="H73" s="7" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="I73" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="J73" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" s="7" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="L73" s="9" t="inlineStr">
+        <is>
+          <t>Time count: 11 up bars since the last down bar | Fib 78.6% retrace @ 319.32 | Prior pivot (1 touch, 1.2x vol) @ 322.62 | High-volume node @ 317.53 | RSI overbought (76) | Tagged upper Bollinger band | Extended 5.1 ATR from 20 EMA | Volume 2.7x average</t>
+        </is>
+      </c>
+      <c r="M73" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N73" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>NCLH</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C74" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F74" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="H74" s="7" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="I74" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J74" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F73" s="2" t="n">
+      <c r="K74" s="7" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="L74" s="9" t="inlineStr">
+        <is>
+          <t>Time count: 8 up bars since the last down bar | Fib 61.8% retrace @ 18.77 | High-volume node @ 18.57 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 2.9x average</t>
+        </is>
+      </c>
+      <c r="M74" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N74" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>TDY</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C75" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F75" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>673.7</v>
+      </c>
+      <c r="H75" s="7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I75" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="J75" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K75" s="7" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="L75" s="9" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 12 | Fib 78.6% retrace @ 674.65 | Major pivot zone (2 touches, 3.2x vol) @ 672.68 | RSI overbought (75) | Tagged upper Bollinger band | Extended 3.2 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M75" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N75" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F76" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>106.82</v>
+      </c>
+      <c r="H76" s="7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I76" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="J76" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" s="7" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="L76" s="9" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 15 | Fib 61.8% retrace @ 107.01 | Major pivot zone (3 touches, 3.0x vol) @ 107.05 | RSI overbought (73) | Tagged upper Bollinger band | Extended 3.0 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M76" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N76" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>LHX</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C77" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F77" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>278.09</v>
+      </c>
+      <c r="H77" s="7" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="I77" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="J77" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K77" s="7" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="L77" s="9" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 15 | Major pivot zone (1 touch, 2.0x vol) @ 281.06 | RSI overbought (77) | Tagged upper Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 1.5x average</t>
+        </is>
+      </c>
+      <c r="M77" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N77" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>VMC</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="F78" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>281.11</v>
+      </c>
+      <c r="H78" s="7" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="I78" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G73" s="2" t="n">
-        <v>29.07</v>
-      </c>
-      <c r="H73" s="2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J73" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K73" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="L73" s="5" t="inlineStr">
-        <is>
-          <t>Setup from 1 bar ago, still near entry (+0.4 ATR since signal; stop beyond 28.20) | Bottoming tail, tail 68% of range | Fib 61.8% retrace @ 28.57 | Major pivot zone (3 touches, 1.5x vol) @ 28.54</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N73" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>SNPS</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>488.37</v>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J74" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K74" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="L74" s="5" t="inlineStr">
-        <is>
-          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 467.24) | Bottoming tail, tail 50% of range | Major pivot zone (2 touches, 2.1x vol) @ 465.90 | High-volume node @ 463.40</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N74" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>NRG</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E75" s="2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>97.04000000000001</v>
-      </c>
-      <c r="H75" s="2" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K75" s="2" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="L75" s="5" t="inlineStr">
-        <is>
-          <t>Setup from 1 bar ago, still near entry (+0.0 ATR since signal; stop beyond 94.12) | Bottoming tail, tail 72% of range | Time count: TD setup 11 | Prior pivot (1 touch, 1.2x vol) @ 93.36</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N75" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>HUBB</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>435.39</v>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K76" s="2" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="L76" s="5" t="inlineStr">
-        <is>
-          <t>Setup from 1 bar ago, still near entry (-0.1 ATR since signal; stop beyond 426.91) | Bottoming tail (new low rejected), tail 58% of range | Prior pivot (1 touch, 1.1x vol) @ 420.97 | Tagged lower Bollinger band | Volume 1.9x average</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N76" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>FIX</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>0.997</v>
-      </c>
-      <c r="E77" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F77" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>1330.65</v>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>-1.12</v>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K77" s="2" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="L77" s="5" t="inlineStr">
-        <is>
-          <t>Setup from 1 bar ago, still near entry (-0.2 ATR since signal; stop beyond 1290.57) | Bottoming tail, tail 68% of range | Time count: TD setup 12 | Volume 1.6x average</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N77" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>GNRC</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K78" s="2" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="L78" s="5" t="inlineStr">
-        <is>
-          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 181.00) | Bottoming tail (new low rejected), tail 66% of range | Major pivot zone (7 touches, 7.7x vol) @ 179.18 | Volume 2.3x average</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N78" s="6" t="inlineStr">
+      <c r="K78" s="7" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="L78" s="9" t="inlineStr">
+        <is>
+          <t>Fib 61.8% retrace @ 288.65 | Prior pivot (1 touch, 1.3x vol) @ 288.44 | Volume POC @ 289.56 | RSI overbought (73) | Tagged upper Bollinger band | Extended 3.8 ATR from 20 EMA | Volume 1.7x average</t>
+        </is>
+      </c>
+      <c r="M78" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N78" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -4885,7 +4885,7 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>AON</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
@@ -4898,33 +4898,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D79" s="9" t="n">
-        <v>0.001</v>
+      <c r="D79" s="8" t="n">
+        <v>0.016</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>7.25</v>
+        <v>5.75</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>317.43</v>
+        <v>320.68</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>13.67</v>
+        <v>1.57</v>
       </c>
       <c r="I79" s="7" t="n">
         <v>11</v>
       </c>
       <c r="J79" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K79" s="7" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="L79" s="10" t="inlineStr">
-        <is>
-          <t>Time count: 11 up bars since the last down bar | Fib 78.6% retrace @ 319.32 | Prior pivot (1 touch, 1.2x vol) @ 322.62 | High-volume node @ 317.53 | RSI overbought (76) | Tagged upper Bollinger band | Extended 5.1 ATR from 20 EMA | Volume 2.7x average</t>
+        <v>69</v>
+      </c>
+      <c r="L79" s="9" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 10 | Fib 50.0% retrace @ 323.90 | Prior pivot (1 touch, 1.3x vol) @ 324.30 | Volume POC @ 320.45 | Tagged upper Bollinger band | Extended 3.4 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M79" s="7" t="inlineStr">
@@ -4932,7 +4932,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N79" s="11" t="inlineStr">
+      <c r="N79" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -4941,7 +4941,7 @@
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>NCLH</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -4954,33 +4954,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D80" s="9" t="n">
-        <v>0.001</v>
+      <c r="D80" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G80" s="7" t="n">
-        <v>18.35</v>
+        <v>367.7</v>
       </c>
       <c r="H80" s="7" t="n">
-        <v>14.26</v>
+        <v>3.77</v>
       </c>
       <c r="I80" s="7" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J80" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K80" s="7" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="L80" s="10" t="inlineStr">
-        <is>
-          <t>Time count: 8 up bars since the last down bar | Fib 61.8% retrace @ 18.77 | High-volume node @ 18.57 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 2.8x average</t>
+        <v>71.2</v>
+      </c>
+      <c r="L80" s="9" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 14 | Fib 61.8% retrace @ 368.42 | Prior pivot (1 touch, 1.6x vol) @ 372.24 | RSI overbought (71) | Tagged upper Bollinger band | Extended 3.6 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M80" s="7" t="inlineStr">
@@ -4988,7 +4988,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N80" s="11" t="inlineStr">
+      <c r="N80" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -4997,7 +4997,7 @@
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
@@ -5010,33 +5010,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D81" s="9" t="n">
-        <v>0.123</v>
+      <c r="D81" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>87.45999999999999</v>
+        <v>265.15</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>11.67</v>
+        <v>5.35</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J81" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K81" s="7" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="L81" s="10" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 13 | Fib 61.8% retrace @ 87.58 | Volume POC @ 88.76 | RSI overbought (76) | Tagged upper Bollinger band | Extended 5.2 ATR from 20 EMA | Volume 1.9x average</t>
+        <v>69.40000000000001</v>
+      </c>
+      <c r="L81" s="9" t="inlineStr">
+        <is>
+          <t>Time count: 13 up bars since the last down bar | Fib 38.2% retrace @ 262.53 | Prior pivot (1 touch, 1.0x vol) @ 265.83 | Trendline (rising resistance) @ 263.21 | Tagged upper Bollinger band | Extended 2.5 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr">
@@ -5044,7 +5044,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N81" s="11" t="inlineStr">
+      <c r="N81" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5053,7 +5053,7 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>TDY</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -5066,33 +5066,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D82" s="9" t="n">
-        <v>0.109</v>
+      <c r="D82" s="8" t="n">
+        <v>0.008999999999999999</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>676.1</v>
+        <v>44.81</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>1.58</v>
+        <v>2.13</v>
       </c>
       <c r="I82" s="7" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J82" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K82" s="7" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="L82" s="10" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 12 | Fib 78.6% retrace @ 674.65 | Major pivot zone (2 touches, 3.2x vol) @ 672.68 | RSI overbought (75) | Tagged upper Bollinger band | Extended 3.2 ATR from 20 EMA</t>
+        <v>74.3</v>
+      </c>
+      <c r="L82" s="9" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 20 | Fib 61.8% retrace @ 44.89 | Major pivot zone (3 touches, 1.9x vol) @ 44.71 | RSI overbought (74) | Extended 3.2 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M82" s="7" t="inlineStr">
@@ -5100,7 +5100,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N82" s="11" t="inlineStr">
+      <c r="N82" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5109,7 +5109,7 @@
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
@@ -5122,33 +5122,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D83" s="9" t="n">
-        <v>0.052</v>
+      <c r="D83" s="8" t="n">
+        <v>0.002</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="F83" s="7" t="n">
         <v>6</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>106.74</v>
+        <v>87.75</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>1.06</v>
+        <v>12.04</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J83" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="L83" s="10" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 15 | Fib 61.8% retrace @ 107.01 | Major pivot zone (3 touches, 3.0x vol) @ 107.05 | RSI overbought (73) | Tagged upper Bollinger band | Extended 3.0 ATR from 20 EMA</t>
+        <v>76.5</v>
+      </c>
+      <c r="L83" s="9" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 13 | Volume POC @ 88.76 | RSI overbought (77) | Tagged upper Bollinger band | Extended 5.1 ATR from 20 EMA | Volume 2.0x average</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
@@ -5156,7 +5156,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N83" s="11" t="inlineStr">
+      <c r="N83" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5165,7 +5165,7 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>LHX</t>
+          <t>WEC</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -5178,33 +5178,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D84" s="9" t="n">
-        <v>0</v>
+      <c r="D84" s="8" t="n">
+        <v>0.254</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="F84" s="7" t="n">
         <v>6</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>278.03</v>
+        <v>114.65</v>
       </c>
       <c r="H84" s="7" t="n">
-        <v>6.68</v>
+        <v>3.76</v>
       </c>
       <c r="I84" s="7" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J84" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K84" s="7" t="n">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="L84" s="10" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 15 | Major pivot zone (1 touch, 2.0x vol) @ 281.06 | RSI overbought (77) | Tagged upper Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 1.5x average</t>
+        <v>71.8</v>
+      </c>
+      <c r="L84" s="9" t="inlineStr">
+        <is>
+          <t>Fib 78.6% retrace @ 114.79 | Major pivot zone (5 touches, 1.7x vol) @ 116.28 | RSI overbought (72) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 2.2x average</t>
         </is>
       </c>
       <c r="M84" s="7" t="inlineStr">
@@ -5212,7 +5212,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N84" s="11" t="inlineStr">
+      <c r="N84" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5221,7 +5221,7 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>DOV</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
@@ -5234,33 +5234,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D85" s="9" t="n">
-        <v>0</v>
+      <c r="D85" s="8" t="n">
+        <v>0.003</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>281.07</v>
+        <v>209.85</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>6.06</v>
+        <v>0.89</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J85" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K85" s="7" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="L85" s="10" t="inlineStr">
-        <is>
-          <t>Fib 61.8% retrace @ 288.65 | Prior pivot (1 touch, 1.3x vol) @ 288.44 | Volume POC @ 289.56 | RSI overbought (73) | Tagged upper Bollinger band | Extended 3.8 ATR from 20 EMA | Volume 1.7x average</t>
+        <v>73.5</v>
+      </c>
+      <c r="L85" s="9" t="inlineStr">
+        <is>
+          <t>Fib 50.0% retrace @ 208.52 | Major pivot zone (3 touches, 1.6x vol) @ 209.50 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.0 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
@@ -5268,7 +5268,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N85" s="11" t="inlineStr">
+      <c r="N85" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5277,7 +5277,7 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>AON</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -5290,33 +5290,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D86" s="9" t="n">
-        <v>0.18</v>
+      <c r="D86" s="8" t="n">
+        <v>0.266</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G86" s="7" t="n">
-        <v>319.99</v>
+        <v>307.26</v>
       </c>
       <c r="H86" s="7" t="n">
-        <v>1.35</v>
+        <v>0.88</v>
       </c>
       <c r="I86" s="7" t="n">
         <v>11</v>
       </c>
       <c r="J86" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K86" s="7" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="L86" s="10" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 10 | Fib 50.0% retrace @ 323.90 | Prior pivot (1 touch, 1.3x vol) @ 324.30 | Volume POC @ 320.45 | Tagged upper Bollinger band | Extended 3.4 ATR from 20 EMA</t>
+        <v>60.2</v>
+      </c>
+      <c r="L86" s="9" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 10 | Fib 50.0% retrace @ 310.98 | Prior pivot (1 touch, 1.4x vol) @ 312.88 | High-volume node @ 311.94 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M86" s="7" t="inlineStr">
@@ -5324,7 +5324,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N86" s="11" t="inlineStr">
+      <c r="N86" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5333,7 +5333,7 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -5346,33 +5346,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D87" s="9" t="n">
-        <v>0.048</v>
+      <c r="D87" s="8" t="n">
+        <v>0.01</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>367.03</v>
+        <v>311.55</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>3.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J87" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="L87" s="10" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 14 | Fib 61.8% retrace @ 368.42 | Prior pivot (1 touch, 1.6x vol) @ 372.24 | RSI overbought (71) | Tagged upper Bollinger band | Extended 3.6 ATR from 20 EMA</t>
+        <v>71.2</v>
+      </c>
+      <c r="L87" s="9" t="inlineStr">
+        <is>
+          <t>Time count: 7 bars without a lower low | Fib 78.6% retrace @ 314.31 | Prior pivot (1 touch, 0.7x vol) @ 313.73 | RSI overbought (71) | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
@@ -5380,7 +5380,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N87" s="11" t="inlineStr">
+      <c r="N87" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5389,7 +5389,7 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>NI</t>
+          <t>URI</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -5402,33 +5402,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D88" s="9" t="n">
-        <v>0.08699999999999999</v>
+      <c r="D88" s="8" t="n">
+        <v>0.03</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="F88" s="7" t="n">
         <v>5</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>44.78</v>
+        <v>1191.74</v>
       </c>
       <c r="H88" s="7" t="n">
-        <v>2.06</v>
+        <v>1.46</v>
       </c>
       <c r="I88" s="7" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J88" s="7" t="n">
         <v>4</v>
       </c>
       <c r="K88" s="7" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="L88" s="10" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 20 | Fib 61.8% retrace @ 44.89 | Major pivot zone (3 touches, 1.9x vol) @ 44.71 | RSI overbought (74) | Extended 3.2 ATR from 20 EMA</t>
+        <v>72.5</v>
+      </c>
+      <c r="L88" s="9" t="inlineStr">
+        <is>
+          <t>Time count: 7 up bars since the last down bar | Trendline (rising resistance) @ 1185.31 | RSI overbought (73) | Tagged upper Bollinger band | Extended 2.8 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M88" s="7" t="inlineStr">
@@ -5436,7 +5436,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N88" s="11" t="inlineStr">
+      <c r="N88" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5445,7 +5445,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>TPR</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5459,32 +5459,32 @@
         </is>
       </c>
       <c r="D89" s="4" t="n">
-        <v>0.08500000000000001</v>
+        <v>1</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>127.35</v>
+        <v>117.76</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>-5.46</v>
+        <v>5.86</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>29.6</v>
+        <v>53.5</v>
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>Time count: 9 down bars since the last up bar | Prior pivot (2 touches, 1.7x vol) @ 128.64 | RSI oversold (30) | Tagged lower Bollinger band | Extended 2.7 ATR from 20 EMA | Volume 2.4x average</t>
+          <t>Time count: 9 down bars since the last up bar | Major pivot zone (2 touches, 1.9x vol) @ 112.16 | High-volume node @ 115.70 | Trendline (rising support) @ 115.23</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -5501,7 +5501,7 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -5514,33 +5514,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D90" s="9" t="n">
-        <v>0</v>
+      <c r="D90" s="8" t="n">
+        <v>0.016</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="F90" s="7" t="n">
         <v>5</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>265.39</v>
+        <v>119.98</v>
       </c>
       <c r="H90" s="7" t="n">
-        <v>5.44</v>
+        <v>1.3</v>
       </c>
       <c r="I90" s="7" t="n">
         <v>11</v>
       </c>
       <c r="J90" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K90" s="7" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="L90" s="10" t="inlineStr">
-        <is>
-          <t>Time count: 13 up bars since the last down bar | Fib 38.2% retrace @ 262.53 | Prior pivot (1 touch, 1.0x vol) @ 265.83 | Trendline (rising resistance) @ 263.21 | Tagged upper Bollinger band</t>
+        <v>74.2</v>
+      </c>
+      <c r="L90" s="9" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 10 | Prior pivot (2 touches, 0.9x vol) @ 119.91 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.2 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M90" s="7" t="inlineStr">
@@ -5548,7 +5548,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N90" s="11" t="inlineStr">
+      <c r="N90" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5557,7 +5557,7 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>URI</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -5570,265 +5570,265 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D91" s="9" t="n">
-        <v>0.022</v>
+      <c r="D91" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="F91" s="7" t="n">
         <v>5</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>1196.38</v>
+        <v>103.31</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>1.85</v>
+        <v>2.92</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J91" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K91" s="7" t="n">
+        <v>76</v>
+      </c>
+      <c r="L91" s="9" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 12 | Prior pivot (1 touch, 1.0x vol) @ 103.78 | RSI overbought (76) | Tagged upper Bollinger band | Extended 3.1 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M91" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N91" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>MSI</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C92" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F92" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="K91" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="L91" s="10" t="inlineStr">
-        <is>
-          <t>Time count: 7 up bars since the last down bar | Trendline (rising resistance) @ 1185.31 | RSI overbought (73) | Tagged upper Bollinger band | Extended 2.7 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M91" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N91" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>TPR</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="G92" s="7" t="n">
+        <v>491.92</v>
+      </c>
+      <c r="H92" s="7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I92" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="J92" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" s="7" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="L92" s="9" t="inlineStr">
+        <is>
+          <t>Time count: 13 up bars since the last down bar | Major pivot zone (2 touches, 1.8x vol) @ 492.74 | RSI overbought (73) | Extended 2.8 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M92" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N92" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="C92" s="13" t="inlineStr">
+      <c r="C93" s="13" t="inlineStr">
         <is>
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D92" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" s="2" t="n">
+      <c r="D93" s="4" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>135.83</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>-21.97</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="L93" s="5" t="inlineStr">
+        <is>
+          <t>Fib 78.6% retrace @ 126.03 | Prior pivot (1 touch, 1.3x vol) @ 133.05 | RSI oversold (27) | Tagged lower Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 3.7x average</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N93" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C94" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F94" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F92" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>117.92</v>
-      </c>
-      <c r="H92" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K92" s="2" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="L92" s="5" t="inlineStr">
-        <is>
-          <t>Time count: 9 down bars since the last up bar | Major pivot zone (2 touches, 1.9x vol) @ 112.16 | High-volume node @ 115.70 | Trendline (rising support) @ 115.23</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N92" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="7" t="inlineStr">
-        <is>
-          <t>PPG</t>
-        </is>
-      </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C93" s="13" t="inlineStr">
+      <c r="G94" s="2" t="n">
+        <v>643.77</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>-9.76</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="L94" s="5" t="inlineStr">
+        <is>
+          <t>Major pivot zone (2 touches, 1.8x vol) @ 619.81 | RSI oversold (26) | Tagged lower Bollinger band | Extended 3.5 ATR from 20 EMA | Volume 2.6x average</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N94" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>LII</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C95" s="13" t="inlineStr">
         <is>
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D93" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E93" s="7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="F93" s="7" t="n">
+      <c r="D95" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F95" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G93" s="7" t="n">
-        <v>120.12</v>
-      </c>
-      <c r="H93" s="7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="I93" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="J93" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K93" s="7" t="n">
-        <v>74.3</v>
-      </c>
-      <c r="L93" s="10" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 10 | Prior pivot (2 touches, 0.9x vol) @ 119.91 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.2 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M93" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N93" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="7" t="inlineStr">
-        <is>
-          <t>SWK</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C94" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D94" s="9" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="E94" s="7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="F94" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G94" s="7" t="n">
-        <v>103.55</v>
-      </c>
-      <c r="H94" s="7" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="I94" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="J94" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K94" s="7" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="L94" s="10" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 12 | Prior pivot (1 touch, 1.0x vol) @ 103.78 | RSI overbought (76) | Tagged upper Bollinger band | Extended 3.0 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M94" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N94" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="7" t="inlineStr">
-        <is>
-          <t>MSI</t>
-        </is>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C95" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D95" s="9" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="E95" s="7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="F95" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G95" s="7" t="n">
-        <v>492.26</v>
-      </c>
-      <c r="H95" s="7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="I95" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="J95" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K95" s="7" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="L95" s="10" t="inlineStr">
-        <is>
-          <t>Time count: 13 up bars since the last down bar | Major pivot zone (2 touches, 1.8x vol) @ 492.74 | RSI overbought (73) | Extended 2.8 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M95" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N95" s="11" t="inlineStr">
+      <c r="G95" s="2" t="n">
+        <v>346.54</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="L95" s="5" t="inlineStr">
+        <is>
+          <t>Prior pivot (1 touch, 1.4x vol) @ 340.32 | Trendline (falling support) @ 319.68 | Bullish RSI divergence (42) | Tagged lower Bollinger band | Extended 2.6 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N95" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5837,7 +5837,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5851,32 +5851,32 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>0.909</v>
+        <v>0.25</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>135.7</v>
+        <v>128.54</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>-22.05</v>
+        <v>-4.57</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>26.6</v>
+        <v>30.3</v>
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>Fib 78.6% retrace @ 126.03 | Prior pivot (1 touch, 1.3x vol) @ 133.05 | RSI oversold (27) | Tagged lower Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 3.8x average</t>
+          <t>Time count: 9 down bars since the last up bar | Prior pivot (2 touches, 1.7x vol) @ 128.64 | Tagged lower Bollinger band | Extended 2.7 ATR from 20 EMA | Volume 2.5x average</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5907,32 +5907,32 @@
         </is>
       </c>
       <c r="D97" s="4" t="n">
-        <v>0.471</v>
+        <v>0.096</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>647.36</v>
+        <v>254.93</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>-9.25</v>
+        <v>-1.94</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>26.6</v>
+        <v>34</v>
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>Major pivot zone (2 touches, 1.8x vol) @ 619.81 | RSI oversold (27) | Tagged lower Bollinger band | Extended 3.5 ATR from 20 EMA | Volume 2.6x average</t>
+          <t>Time count: 9 down bars since the last up bar | Trendline (falling support) @ 253.65 | Bullish RSI divergence (34) | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -5949,7 +5949,7 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
@@ -5962,97 +5962,97 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D98" s="9" t="n">
-        <v>0.044</v>
+      <c r="D98" s="8" t="n">
+        <v>0.227</v>
       </c>
       <c r="E98" s="7" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="F98" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G98" s="7" t="n">
+        <v>1372.84</v>
+      </c>
+      <c r="H98" s="7" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="I98" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G98" s="7" t="n">
-        <v>311.42</v>
-      </c>
-      <c r="H98" s="7" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="I98" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="J98" s="7" t="n">
+      <c r="K98" s="7" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="L98" s="9" t="inlineStr">
+        <is>
+          <t>Fib 1.27 extension @ 1424.82 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 1.6x average</t>
+        </is>
+      </c>
+      <c r="M98" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N98" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>CRL</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C99" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="E99" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F99" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G99" s="7" t="n">
+        <v>377.76</v>
+      </c>
+      <c r="H99" s="7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I99" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J99" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K98" s="7" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="L98" s="10" t="inlineStr">
-        <is>
-          <t>Time count: 7 bars without a lower low | Fib 78.6% retrace @ 314.31 | Prior pivot (1 touch, 0.7x vol) @ 313.73 | RSI overbought (71)</t>
-        </is>
-      </c>
-      <c r="M98" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N98" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>LII</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C99" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="n">
-        <v>0.994</v>
-      </c>
-      <c r="E99" s="2" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="F99" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>346.67</v>
-      </c>
-      <c r="H99" s="2" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J99" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K99" s="2" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="L99" s="5" t="inlineStr">
-        <is>
-          <t>Prior pivot (1 touch, 1.4x vol) @ 340.32 | Trendline (falling support) @ 319.68 | Bullish RSI divergence (42) | Tagged lower Bollinger band | Extended 2.6 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N99" s="6" t="inlineStr">
+      <c r="K99" s="7" t="n">
+        <v>81</v>
+      </c>
+      <c r="L99" s="9" t="inlineStr">
+        <is>
+          <t>Time count: 8 up bars since the last down bar | RSI overbought (81) | Tagged upper Bollinger band | Extended 3.8 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M99" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N99" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -6061,7 +6061,7 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>CRL</t>
+          <t>LYB</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -6074,97 +6074,97 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D100" s="9" t="n">
-        <v>0.148</v>
+      <c r="D100" s="8" t="n">
+        <v>0.78</v>
       </c>
       <c r="E100" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F100" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G100" s="7" t="n">
+        <v>65.06999999999999</v>
+      </c>
+      <c r="H100" s="7" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="I100" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J100" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K100" s="7" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="L100" s="9" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 19 | Fib 61.8% retrace @ 65.23 | Major pivot zone (3 touches, 1.6x vol) @ 67.19</t>
+        </is>
+      </c>
+      <c r="M100" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N100" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C101" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G100" s="7" t="n">
-        <v>376.52</v>
-      </c>
-      <c r="H100" s="7" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I100" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="J100" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K100" s="7" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="L100" s="10" t="inlineStr">
-        <is>
-          <t>Time count: 8 up bars since the last down bar | RSI overbought (81) | Tagged upper Bollinger band | Extended 3.8 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M100" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N100" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="7" t="inlineStr">
-        <is>
-          <t>LYB</t>
-        </is>
-      </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C101" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D101" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E101" s="7" t="n">
+      <c r="F101" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F101" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G101" s="7" t="n">
-        <v>65.01000000000001</v>
-      </c>
-      <c r="H101" s="7" t="n">
-        <v>-3.16</v>
-      </c>
-      <c r="I101" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J101" s="7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="K101" s="7" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="L101" s="10" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 19 | Fib 61.8% retrace @ 65.23 | Major pivot zone (3 touches, 1.6x vol) @ 67.19</t>
-        </is>
-      </c>
-      <c r="M101" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N101" s="11" t="inlineStr">
+      <c r="G101" s="2" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="L101" s="5" t="inlineStr">
+        <is>
+          <t>Time count: 11 down bars since the last up bar | Prior pivot (2 touches, 1.0x vol) @ 95.80 | RSI oversold (29) | Tagged lower Bollinger band</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N101" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -6173,7 +6173,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -6190,29 +6190,29 @@
         <v>0</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>97.79000000000001</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>-2.98</v>
+        <v>-1.26</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>-4</v>
+        <v>-9</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>-4</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>29.4</v>
+        <v>32.8</v>
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>Time count: 11 down bars since the last up bar | Prior pivot (2 touches, 1.0x vol) @ 95.80 | RSI oversold (29) | Tagged lower Bollinger band</t>
+          <t>Time count: 11 down bars since the last up bar | Major pivot zone (3 touches, 1.5x vol) @ 75.85 | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
@@ -6229,7 +6229,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -6243,32 +6243,32 @@
         </is>
       </c>
       <c r="D103" s="4" t="n">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="F103" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>76.25</v>
+        <v>328.68</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>-1.28</v>
+        <v>-2.03</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>-9</v>
+        <v>2</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>32.8</v>
+        <v>43</v>
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>Time count: 11 down bars since the last up bar | Major pivot zone (3 touches, 1.5x vol) @ 75.85 | Tagged lower Bollinger band</t>
+          <t>Fib 61.8% retrace @ 330.37 | Major pivot zone (6 touches, 3.1x vol) @ 327.50 | Volume POC @ 334.25</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -6285,7 +6285,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -6299,7 +6299,7 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>0.245</v>
+        <v>0.721</v>
       </c>
       <c r="E104" s="2" t="n">
         <v>3.5</v>
@@ -6308,23 +6308,23 @@
         <v>3</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>330.5</v>
+        <v>627.34</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>-1.49</v>
+        <v>2.42</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>43.7</v>
+        <v>35.9</v>
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>Fib 61.8% retrace @ 330.37 | Major pivot zone (6 touches, 3.1x vol) @ 327.50 | Volume POC @ 334.25</t>
+          <t>Time count: 11 down bars since the last up bar | Fib 61.8% retrace @ 621.77 | High-volume node @ 620.94</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -6341,7 +6341,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="D105" s="4" t="n">
-        <v>0.771</v>
+        <v>1</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>3.5</v>
@@ -6364,143 +6364,143 @@
         <v>3</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>628.77</v>
+        <v>77.09</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="I105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="L105" s="5" t="inlineStr">
+        <is>
+          <t>Fib 50.0% retrace @ 76.19 | Major pivot zone (3 touches, 1.0x vol) @ 75.26 | High-volume node @ 75.69</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N105" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>IRM</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C106" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E106" s="7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F106" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G106" s="7" t="n">
+        <v>118.48</v>
+      </c>
+      <c r="H106" s="7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="I106" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J106" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K106" s="7" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="L106" s="9" t="inlineStr">
+        <is>
+          <t>Fib 50.0% retrace @ 120.42 | Major pivot zone (7 touches, 1.6x vol) @ 118.99 | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M106" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N106" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C107" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>61.92</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="I107" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J105" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K105" s="2" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="L105" s="5" t="inlineStr">
-        <is>
-          <t>Time count: 11 down bars since the last up bar | Fib 61.8% retrace @ 621.77 | High-volume node @ 620.94</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N105" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C106" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D106" s="4" t="n">
-        <v>0.997</v>
-      </c>
-      <c r="E106" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F106" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G106" s="2" t="n">
-        <v>77.26000000000001</v>
-      </c>
-      <c r="H106" s="2" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="I106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J106" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K106" s="2" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="L106" s="5" t="inlineStr">
-        <is>
-          <t>Fib 50.0% retrace @ 76.19 | Major pivot zone (3 touches, 1.0x vol) @ 75.26 | High-volume node @ 75.69</t>
-        </is>
-      </c>
-      <c r="M106" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N106" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="7" t="inlineStr">
-        <is>
-          <t>COF</t>
-        </is>
-      </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C107" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D107" s="9" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="E107" s="7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="F107" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G107" s="7" t="n">
-        <v>208.69</v>
-      </c>
-      <c r="H107" s="7" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="I107" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J107" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K107" s="7" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="L107" s="10" t="inlineStr">
-        <is>
-          <t>Major pivot zone (8 touches, 1.8x vol) @ 210.88 | Trendline (falling resistance) @ 209.74 | Tagged upper Bollinger band</t>
-        </is>
-      </c>
-      <c r="M107" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N107" s="11" t="inlineStr">
+      <c r="J107" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="L107" s="5" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 9 | Trendline (falling support) @ 60.70 | Extended 3.0 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N107" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -6509,7 +6509,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>0.053</v>
+        <v>0.144</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>3.25</v>
@@ -6532,199 +6532,199 @@
         <v>3</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>380.21</v>
+        <v>238.13</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>-2.13</v>
+        <v>-6.16</v>
       </c>
       <c r="I108" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="L108" s="5" t="inlineStr">
+        <is>
+          <t>Fib 61.8% retrace @ 228.55 | Major pivot zone (3 touches, 1.4x vol) @ 238.69 | Tagged lower Bollinger band</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N108" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>VLO</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C109" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>379.92</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="I109" s="2" t="n">
         <v>-9</v>
       </c>
-      <c r="J108" s="2" t="n">
+      <c r="J109" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="K108" s="2" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="L108" s="5" t="inlineStr">
+      <c r="K109" s="2" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="L109" s="5" t="inlineStr">
         <is>
           <t>Time count: TD setup 8 | Fib 38.2% retrace @ 373.38 | Tagged lower Bollinger band</t>
         </is>
       </c>
-      <c r="M108" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N108" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="7" t="inlineStr">
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N109" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
         <is>
           <t>ARES</t>
         </is>
       </c>
-      <c r="B109" s="7" t="inlineStr">
+      <c r="B110" s="7" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>
       </c>
-      <c r="C109" s="13" t="inlineStr">
+      <c r="C110" s="13" t="inlineStr">
         <is>
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D109" s="9" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="E109" s="7" t="n">
+      <c r="D110" s="8" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="E110" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F109" s="7" t="n">
+      <c r="F110" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G109" s="7" t="n">
-        <v>126.78</v>
-      </c>
-      <c r="H109" s="7" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="I109" s="7" t="n">
+      <c r="G110" s="7" t="n">
+        <v>126.85</v>
+      </c>
+      <c r="H110" s="7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I110" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="J109" s="7" t="n">
+      <c r="J110" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="K109" s="7" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="L109" s="10" t="inlineStr">
+      <c r="K110" s="7" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="L110" s="9" t="inlineStr">
         <is>
           <t>Time count: 8 up bars since the last down bar | Prior pivot (2 touches, 1.3x vol) @ 129.72 | Tagged upper Bollinger band</t>
         </is>
       </c>
-      <c r="M109" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N109" s="11" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>FFIV</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C110" s="13" t="inlineStr">
+      <c r="M110" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N110" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C111" s="13" t="inlineStr">
         <is>
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D110" s="4" t="n">
-        <v>0.713</v>
-      </c>
-      <c r="E110" s="2" t="n">
+      <c r="D111" s="8" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="E111" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F110" s="2" t="n">
+      <c r="F111" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G111" s="7" t="n">
+        <v>276.02</v>
+      </c>
+      <c r="H111" s="7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I111" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J111" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G110" s="2" t="n">
-        <v>363.2</v>
-      </c>
-      <c r="H110" s="2" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="I110" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J110" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="K110" s="2" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="L110" s="5" t="inlineStr">
-        <is>
-          <t>RSI oversold (27) | Tagged lower Bollinger band | Extended 4.2 ATR from 20 EMA | Volume 2.0x average</t>
-        </is>
-      </c>
-      <c r="M110" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N110" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C111" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E111" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F111" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G111" s="2" t="n">
-        <v>281.1</v>
-      </c>
-      <c r="H111" s="2" t="n">
-        <v>-12.67</v>
-      </c>
-      <c r="I111" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J111" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K111" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="L111" s="5" t="inlineStr">
-        <is>
-          <t>RSI oversold (22) | Tagged lower Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 5.0x average</t>
-        </is>
-      </c>
-      <c r="M111" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N111" s="6" t="inlineStr">
+      <c r="K111" s="7" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="L111" s="9" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 8 | Prior pivot (1 touch, 1.0x vol) @ 281.07 | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M111" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N111" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -6733,7 +6733,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -6747,7 +6747,7 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>0.237</v>
+        <v>0.079</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>3</v>
@@ -6756,10 +6756,10 @@
         <v>4</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>283.04</v>
+        <v>280.67</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>-12.88</v>
+        <v>-12.81</v>
       </c>
       <c r="I112" s="2" t="n">
         <v>-1</v>
@@ -6768,11 +6768,11 @@
         <v>-1</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>22.1</v>
+        <v>21.7</v>
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>RSI oversold (22) | Tagged lower Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 4.7x average</t>
+          <t>RSI oversold (22) | Tagged lower Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 4.9x average</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
@@ -6789,7 +6789,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>MGM</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="D113" s="4" t="n">
-        <v>1</v>
+        <v>0.068</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>3</v>
@@ -6812,23 +6812,23 @@
         <v>4</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>28.47</v>
+        <v>282.52</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>4.4</v>
+        <v>-13.04</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>35.1</v>
+        <v>22</v>
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>Bullish RSI divergence (35) | Tagged lower Bollinger band | Extended 2.7 ATR from 20 EMA | Volume 1.9x average</t>
+          <t>RSI oversold (22) | Tagged lower Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 4.6x average</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>AZO</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
@@ -6858,8 +6858,8 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D114" s="9" t="n">
-        <v>0.848</v>
+      <c r="D114" s="8" t="n">
+        <v>0.833</v>
       </c>
       <c r="E114" s="7" t="n">
         <v>2.5</v>
@@ -6868,23 +6868,23 @@
         <v>2</v>
       </c>
       <c r="G114" s="7" t="n">
-        <v>407.33</v>
+        <v>3145.11</v>
       </c>
       <c r="H114" s="7" t="n">
-        <v>0.06</v>
+        <v>-0.37</v>
       </c>
       <c r="I114" s="7" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="J114" s="7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K114" s="7" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="L114" s="10" t="inlineStr">
-        <is>
-          <t>Fib 50.0% retrace @ 410.70 | Major pivot zone (2 touches, 2.0x vol) @ 411.73</t>
+        <v>59.6</v>
+      </c>
+      <c r="L114" s="9" t="inlineStr">
+        <is>
+          <t>Fib 61.8% retrace @ 3243.91 | Major pivot zone (6 touches, 2.2x vol) @ 3190.97</t>
         </is>
       </c>
       <c r="M114" s="7" t="inlineStr">
@@ -6892,21 +6892,21 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N114" s="11" t="inlineStr">
+      <c r="N114" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>CMI</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
         </is>
       </c>
       <c r="C115" s="13" t="inlineStr">
@@ -6914,41 +6914,41 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D115" s="4" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="E115" s="2" t="n">
+      <c r="D115" s="8" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="E115" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F115" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F115" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G115" s="2" t="n">
-        <v>85.20999999999999</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J115" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K115" s="2" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="L115" s="5" t="inlineStr">
-        <is>
-          <t>Fib 38.2% retrace @ 83.44 | High-volume node @ 82.23</t>
-        </is>
-      </c>
-      <c r="M115" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N115" s="6" t="inlineStr">
+      <c r="G115" s="7" t="n">
+        <v>515.16</v>
+      </c>
+      <c r="H115" s="7" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="I115" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J115" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K115" s="7" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="L115" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail, tail 67% of range | Volume POC @ 524.39</t>
+        </is>
+      </c>
+      <c r="M115" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N115" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -6957,7 +6957,7 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>CMI</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
@@ -6970,33 +6970,33 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D116" s="9" t="n">
-        <v>0.491</v>
+      <c r="D116" s="8" t="n">
+        <v>0.498</v>
       </c>
       <c r="E116" s="7" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="F116" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G116" s="7" t="n">
-        <v>517.64</v>
+        <v>409.27</v>
       </c>
       <c r="H116" s="7" t="n">
-        <v>-2.59</v>
+        <v>0.53</v>
       </c>
       <c r="I116" s="7" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="J116" s="7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K116" s="7" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="L116" s="10" t="inlineStr">
-        <is>
-          <t>Volume POC @ 524.39</t>
+        <v>58.5</v>
+      </c>
+      <c r="L116" s="9" t="inlineStr">
+        <is>
+          <t>Fib 50.0% retrace @ 410.70 | Major pivot zone (2 touches, 2.0x vol) @ 411.73</t>
         </is>
       </c>
       <c r="M116" s="7" t="inlineStr">
@@ -7004,7 +7004,7 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="N116" s="11" t="inlineStr">
+      <c r="N116" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -7013,7 +7013,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -7027,30 +7027,34 @@
         </is>
       </c>
       <c r="D117" s="4" t="n">
-        <v>0.647</v>
+        <v>0.999</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>637.17</v>
+        <v>85.22</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>4.99</v>
+        <v>3.32</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="L117" s="5" t="inlineStr"/>
+        <v>58.9</v>
+      </c>
+      <c r="L117" s="5" t="inlineStr">
+        <is>
+          <t>Fib 38.2% retrace @ 83.44 | High-volume node @ 82.23</t>
+        </is>
+      </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
           <t>2026-10-29</t>

--- a/site/reversal_signals.xlsx
+++ b/site/reversal_signals.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily'!$A$1:$N$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily'!$A$1:$N$130</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Weekly'!$A$1:$N$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Monthly'!$A$1:$N$1</definedName>
   </definedNames>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N117"/>
+  <dimension ref="A1:N130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -583,7 +583,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Likely to confirm</t>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
@@ -596,10 +596,10 @@
         <v>7</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>497.64</v>
+        <v>497.41</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
@@ -608,11 +608,11 @@
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>Bullish engulfing | Fib 61.8% retrace @ 485.63 | Major pivot zone (11 touches, 2.0x vol) @ 480.89 | High-volume node @ 491.45 | Trendline (falling support) @ 475.07 | Bullish RSI divergence (47) | Tagged lower Bollinger band</t>
+          <t>Bullish engulfing | Fib 61.8% retrace @ 485.63 | Major pivot zone (13 touches, 2.0x vol) @ 479.63 | High-volume node @ 491.45 | Trendline (falling support) @ 475.07 | Bullish RSI divergence (47) | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -639,11 +639,11 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Likely to confirm</t>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D3" s="8" t="n">
-        <v>0.986</v>
+        <v>1</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>7.5</v>
@@ -652,10 +652,10 @@
         <v>6</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>54.4</v>
+        <v>54.55</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-3.24</v>
+        <v>-2.97</v>
       </c>
       <c r="I3" s="7" t="n">
         <v>-1</v>
@@ -664,11 +664,11 @@
         <v>-2</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>53.4</v>
+        <v>54.1</v>
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t>Topping tail, tail 52% of range | Time count: TD setup 7 | Fib 78.6% retrace @ 57.08 | Major pivot zone (9 touches, 2.4x vol) @ 55.40 | High-volume node @ 54.81 | Trendline (rising resistance) @ 56.84</t>
+          <t>Topping tail, tail 50% of range | Time count: TD setup 7 | Fib 78.6% retrace @ 57.08 | Major pivot zone (9 touches, 2.4x vol) @ 55.40 | High-volume node @ 54.81 | Trendline (rising resistance) @ 56.84</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
@@ -693,13 +693,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Failed at close</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
       <c r="E4" s="7" t="n">
         <v>7.25</v>
@@ -708,10 +708,10 @@
         <v>6</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>33.47</v>
+        <v>33.62</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>-1.92</v>
+        <v>-1.49</v>
       </c>
       <c r="I4" s="7" t="n">
         <v>13</v>
@@ -720,11 +720,11 @@
         <v>-1</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>70.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="L4" s="9" t="inlineStr">
         <is>
-          <t>Bearish engulfing | Time count: 12 up bars since the last down bar | Fib 61.8% retrace @ 34.41 | Major pivot zone (2 touches, 1.9x vol) @ 33.92 | RSI overbought (70) | Extended 3.4 ATR from 20 EMA</t>
+          <t>Bearish engulfing | Time count: 12 up bars since the last down bar | Fib 61.8% retrace @ 34.41 | Major pivot zone (2 touches, 1.9x vol) @ 33.92 | RSI overbought (72) | Extended 3.3 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Likely to confirm</t>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D5" s="8" t="n">
@@ -764,10 +764,10 @@
         <v>7</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>417.43</v>
+        <v>415.75</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="I5" s="7" t="n">
         <v>13</v>
@@ -776,11 +776,11 @@
         <v>4</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>81</v>
+        <v>80.5</v>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 77% of range | Time count: 15 up bars since the last down bar | Fib 1.27 extension @ 434.72 | RSI overbought (81) | Tagged upper Bollinger band | Extended 5.1 ATR from 20 EMA | Volume 2.7x average</t>
+          <t>Topping tail (new high rejected), tail 77% of range | Time count: 15 up bars since the last down bar | Fib 1.27 extension @ 434.72 | RSI overbought (80) | Tagged upper Bollinger band | Extended 5.2 ATR from 20 EMA | Volume 3.1x average</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
@@ -797,7 +797,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -805,13 +805,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>0.585</v>
+        <v>1</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>6.5</v>
@@ -820,23 +820,23 @@
         <v>6</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>42.19</v>
+        <v>562.52</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>70.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 53% of range | Time count: TD setup 20 | Prior pivot (2 touches, 1.1x vol) @ 42.24 | High-volume node @ 42.32 | RSI overbought (71) | Extended 3.2 ATR from 20 EMA</t>
+          <t>Topping tail (new high rejected), tail 65% of range | Time count: TD setup 15 | Fib 78.6% retrace @ 565.76 | Prior pivot (2 touches, 1.2x vol) @ 575.43 | Bearish RSI divergence (67) | Extended 2.9 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -861,13 +861,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>6.5</v>
@@ -876,23 +876,23 @@
         <v>6</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>561.5700000000001</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1.59</v>
+        <v>-2.62</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>16</v>
+        <v>-2</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>66.59999999999999</v>
+        <v>49.6</v>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 65% of range | Time count: TD setup 15 | Fib 78.6% retrace @ 565.76 | Prior pivot (2 touches, 1.2x vol) @ 575.43 | Bearish RSI divergence (67) | Extended 2.9 ATR from 20 EMA</t>
+          <t>Bearish engulfing | Fib 78.6% retrace @ 92.43 | Major pivot zone (14 touches, 2.7x vol) @ 92.79 | Volume POC @ 91.53 | Bearish RSI divergence (50) | Volume 2.2x average</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
@@ -909,7 +909,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -917,38 +917,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Failed at close</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>88.52</v>
+        <v>503.15</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>-2.12</v>
+        <v>-0.99</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>-2</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>51.1</v>
+        <v>61.4</v>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>Bearish engulfing | Fib 78.6% retrace @ 92.43 | Major pivot zone (14 touches, 2.7x vol) @ 92.79 | Volume POC @ 91.53 | Bearish RSI divergence (51) | Volume 1.8x average</t>
+          <t>Bearish engulfing | Fib 61.8% retrace @ 511.18 | Major pivot zone (3 touches, 1.4x vol) @ 505.57 | High-volume node @ 505.80 | Bearish RSI divergence (61)</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
@@ -963,168 +963,168 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>LIN</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>430.85</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>-3.93</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Bottoming tail (new low rejected), tail 52% of range | Major pivot zone (3 touches, 1.5x vol) @ 414.52 | High-volume node @ 423.56 | Tagged lower Bollinger band | Extended 2.9 ATR from 20 EMA | Volume 1.7x average</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>EQIX</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>0.911</v>
-      </c>
-      <c r="E9" s="7" t="n">
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>1036.67</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 65% of range | Fib 78.6% retrace @ 1078.54 | Major pivot zone (8 touches, 1.8x vol) @ 1043.32 | High-volume node @ 1073.68 | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="F11" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>504.36</v>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J9" s="7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>Bearish engulfing | Fib 61.8% retrace @ 511.18 | Major pivot zone (3 touches, 1.4x vol) @ 505.57 | High-volume node @ 505.80 | Bearish RSI divergence (63)</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N9" s="10" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>430</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>-4.12</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>Bottoming tail (new low rejected), tail 53% of range | Major pivot zone (3 touches, 1.5x vol) @ 414.52 | High-volume node @ 423.56 | Tagged lower Bollinger band | Extended 2.9 ATR from 20 EMA | Volume 1.6x average</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>EQIX</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>0.969</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>1036.7</v>
-      </c>
-      <c r="H11" s="7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 65% of range | Fib 78.6% retrace @ 1078.54 | Major pivot zone (8 touches, 1.8x vol) @ 1043.32 | High-volume node @ 1073.68 | Tagged upper Bollinger band</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N11" s="10" t="inlineStr">
+      <c r="G11" s="2" t="n">
+        <v>129.87</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>-3.59</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Bottoming tail (new low rejected), tail 63% of range | Time count: 9 down bars since the last up bar | Prior pivot (2 touches, 1.7x vol) @ 128.64 | Tagged lower Bollinger band | Extended 2.7 ATR from 20 EMA | Volume 2.7x average</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1133,7 +1133,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1143,11 +1143,11 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Likely to confirm</t>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.992</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>5.75</v>
@@ -1156,87 +1156,87 @@
         <v>5</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>176.32</v>
+        <v>241.84</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>2.4</v>
+        <v>-4.7</v>
       </c>
       <c r="I12" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J12" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="J12" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K12" s="2" t="n">
-        <v>45.9</v>
+        <v>40.5</v>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
+          <t>Bottoming tail (new low rejected), tail 63% of range | Fib 61.8% retrace @ 228.55 | Major pivot zone (3 touches, 1.4x vol) @ 238.69 | Trendline (rising support) @ 241.66 | Tagged lower Bollinger band</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>UHS</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>176.63</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
           <t>Bottoming tail, tail 59% of range | Fib 38.2% retrace @ 171.84 | Major pivot zone (4 touches, 1.5x vol) @ 174.58 | High-volume node @ 168.36 | Tagged lower Bollinger band</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>ALGN</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>153.22</v>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J13" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="L13" s="9" t="inlineStr">
-        <is>
-          <t>Doji (indecision at extreme) | Time count: 8 up bars since the last down bar | Fib 38.2% retrace @ 158.27 | Major pivot zone (3 touches, 2.4x vol) @ 154.53 | Volume 1.7x average</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N13" s="10" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -1245,7 +1245,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>ALGN</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -1255,11 +1255,11 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>At risk</t>
+          <t>Failed at close</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>5.5</v>
@@ -1268,23 +1268,23 @@
         <v>5</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>181.99</v>
+        <v>153.71</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>1.45</v>
+        <v>0.06</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>16</v>
+        <v>-2</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>70.90000000000001</v>
+        <v>57.7</v>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 54% of range | Time count: TD setup 15 | Prior pivot (1 touch, 1.7x vol) @ 185.27 | RSI overbought (71) | Extended 3.4 ATR from 20 EMA</t>
+          <t>Doji (indecision at extreme) | Time count: 8 up bars since the last down bar | Fib 38.2% retrace @ 158.27 | Major pivot zone (3 touches, 2.4x vol) @ 154.53 | Volume 2.1x average</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
@@ -1301,7 +1301,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>LDOS</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -1309,13 +1309,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Failed at close</t>
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>0.996</v>
+        <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>5.5</v>
@@ -1324,10 +1324,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>140.66</v>
+        <v>181.87</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>0.76</v>
+        <v>1.38</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>16</v>
@@ -1336,11 +1336,11 @@
         <v>1</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>72.7</v>
+        <v>70.7</v>
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 58% of range | Time count: TD setup 15 | Prior pivot (1 touch, 0.9x vol) @ 142.02 | RSI overbought (73) | Extended 3.4 ATR from 20 EMA</t>
+          <t>Topping tail (new high rejected), tail 54% of range | Time count: TD setup 15 | Prior pivot (1 touch, 1.7x vol) @ 185.27 | RSI overbought (71) | Extended 3.4 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
@@ -1357,7 +1357,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>LDOS</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -1380,23 +1380,23 @@
         <v>5</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>105.36</v>
+        <v>141.02</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>-0.18</v>
+        <v>1.02</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>73.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 47% of range | Time count: 10 bars without a lower low | RSI overbought (74) | Tagged upper Bollinger band | Extended 4.1 ATR from 20 EMA</t>
+          <t>Topping tail (new high rejected), tail 58% of range | Time count: TD setup 15 | Prior pivot (1 touch, 0.9x vol) @ 142.02 | RSI overbought (73) | Extended 3.4 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
@@ -1413,7 +1413,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>NSC</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -1421,13 +1421,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>0.522</v>
+        <v>1</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>5.5</v>
@@ -1436,23 +1436,23 @@
         <v>5</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>341.93</v>
+        <v>105.6</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>1.14</v>
+        <v>0.05</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>66.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 51% of range | Major pivot zone (1 touch, 2.1x vol) @ 343.63 | Bearish RSI divergence (67) | Tagged upper Bollinger band | Extended 2.8 ATR from 20 EMA</t>
+          <t>Topping tail (new high rejected), tail 47% of range | Time count: 10 bars without a lower low | RSI overbought (75) | Tagged upper Bollinger band | Extended 4.1 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
@@ -1477,13 +1477,13 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>5.5</v>
@@ -1492,10 +1492,10 @@
         <v>5</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>65.44</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.26</v>
+        <v>0.71</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>-12</v>
@@ -1504,11 +1504,11 @@
         <v>1</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>35.7</v>
+        <v>37.2</v>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>Bottoming tail (new low rejected), tail 74% of range | Time count: TD setup 11 | Prior pivot (1 touch, 1.4x vol) @ 65.41 | Trendline (falling support) @ 64.82 | Tagged lower Bollinger band</t>
+          <t>Bottoming tail (new low rejected), tail 70% of range | Time count: TD setup 11 | Prior pivot (1 touch, 1.4x vol) @ 65.41 | Trendline (falling support) @ 64.82 | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>BAX</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -1533,13 +1533,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>0.769</v>
+        <v>1</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>5.25</v>
@@ -1548,23 +1548,23 @@
         <v>5</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>1171.82</v>
+        <v>23.49</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>1.2</v>
+        <v>-7.76</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>66.7</v>
+        <v>40.7</v>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 62% of range | Time count: 7 up bars since the last down bar | Prior pivot (2 touches, 1.0x vol) @ 1180.97 | Tagged upper Bollinger band | Extended 2.5 ATR from 20 EMA</t>
+          <t>Bearish engulfing | Major pivot zone (3 touches, 2.0x vol) @ 23.62 | Bearish RSI divergence (41) | Tagged upper Bollinger band | Volume 2.3x average</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
@@ -1591,11 +1591,11 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>At risk</t>
+          <t>Failed at close</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>5.25</v>
@@ -1604,10 +1604,10 @@
         <v>5</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>49.26</v>
+        <v>49.31</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>1</v>
@@ -1616,7 +1616,7 @@
         <v>1</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>61.4</v>
+        <v>61.6</v>
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>CRL</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -1647,11 +1647,11 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>At risk</t>
+          <t>Failed at close</t>
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>0.421</v>
+        <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>5</v>
@@ -1660,23 +1660,23 @@
         <v>5</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>165.3</v>
+        <v>375.83</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>-0.02</v>
+        <v>0.49</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>72.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>Doji (indecision at extreme) | Time count: 7 up bars since the last down bar | Prior pivot (1 touch, 1.4x vol) @ 166.18 | RSI overbought (73) | Tagged upper Bollinger band</t>
+          <t>Doji (indecision at extreme) | Time count: 8 up bars since the last down bar | RSI overbought (81) | Tagged upper Bollinger band | Extended 3.8 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
@@ -1703,11 +1703,11 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Likely to confirm</t>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>5</v>
@@ -1716,10 +1716,10 @@
         <v>4</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>62.39</v>
+        <v>62.52</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>-5.98</v>
+        <v>-5.79</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>-3</v>
@@ -1728,7 +1728,7 @@
         <v>-1</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>46.6</v>
+        <v>46.8</v>
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
@@ -1757,13 +1757,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Failed at close</t>
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>5</v>
@@ -1772,10 +1772,10 @@
         <v>4</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>21.43</v>
+        <v>21.48</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="I23" s="7" t="n">
         <v>1</v>
@@ -1784,11 +1784,11 @@
         <v>2</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>64.3</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 52% of range | Fib 50.0% retrace @ 21.65 | Major pivot zone (3 touches, 1.3x vol) @ 21.45 | High-volume node @ 21.64</t>
+          <t>Topping tail (new high rejected), tail 51% of range | Fib 50.0% retrace @ 21.65 | Major pivot zone (3 touches, 1.3x vol) @ 21.45 | High-volume node @ 21.64</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>BF-B</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1815,36 +1815,36 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Likely to confirm</t>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>27.96</v>
+        <v>172.35</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.76</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="I24" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J24" s="2" t="n">
         <v>-2</v>
       </c>
-      <c r="J24" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K24" s="2" t="n">
-        <v>52</v>
+        <v>36.3</v>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>Bottoming tail (new low rejected), tail 56% of range | Fib 50.0% retrace @ 27.22 | Major pivot zone (4 touches, 4.9x vol) @ 27.85 | High-volume node @ 27.83</t>
+          <t>Bottoming tail (new low rejected), tail 55% of range | Major pivot zone (3 touches, 2.1x vol) @ 168.52 | Tagged lower Bollinger band | Extended 2.6 ATR from 20 EMA | Volume 1.8x average</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>BF-B</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1871,11 +1871,11 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Likely to confirm</t>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>5</v>
@@ -1884,23 +1884,23 @@
         <v>4</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>93.19</v>
+        <v>28.03</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>57.4</v>
+        <v>52.5</v>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>Bottoming tail, tail 93% of range | Fib 38.2% retrace @ 92.09 | Major pivot zone (4 touches, 1.2x vol) @ 91.65 | High-volume node @ 91.89</t>
+          <t>Bottoming tail (new low rejected), tail 64% of range | Fib 50.0% retrace @ 27.22 | Major pivot zone (4 touches, 4.9x vol) @ 27.85 | High-volume node @ 27.83</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Likely to confirm</t>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
@@ -1940,87 +1940,87 @@
         <v>4</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>239.71</v>
+        <v>93.2</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0.49</v>
+        <v>1.65</v>
       </c>
       <c r="I26" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>Bottoming tail, tail 93% of range | Fib 38.2% retrace @ 92.09 | Major pivot zone (4 touches, 1.2x vol) @ 91.65 | High-volume node @ 91.89</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>239.46</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I27" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J26" s="2" t="n">
+      <c r="J27" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K26" s="2" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>Bottoming tail, tail 72% of range | Major pivot zone (2 touches, 2.1x vol) @ 229.88 | High-volume node @ 233.72 | Trendline (rising support) @ 236.19</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N26" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>COF</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="n">
-        <v>0.837</v>
-      </c>
-      <c r="E27" s="7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G27" s="7" t="n">
-        <v>207.93</v>
-      </c>
-      <c r="H27" s="7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="I27" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="L27" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail (new high rejected), tail 67% of range | Major pivot zone (8 touches, 1.8x vol) @ 210.88 | Trendline (falling resistance) @ 209.74 | Tagged upper Bollinger band</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N27" s="10" t="inlineStr">
+      <c r="K27" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>Bottoming tail, tail 66% of range | Major pivot zone (2 touches, 2.1x vol) @ 229.88 | High-volume node @ 233.72 | Trendline (rising support) @ 236.19</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N27" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2029,7 +2029,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>HBAN</t>
+          <t>IRM</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>0.9360000000000001</v>
+        <v>1</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>4.75</v>
@@ -2052,23 +2052,23 @@
         <v>4</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>15.91</v>
+        <v>118.43</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>1.37</v>
+        <v>2.38</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>58.1</v>
+        <v>59.6</v>
       </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 59% of range | Time count: 8 up bars since the last down bar | Fib 38.2% retrace @ 16.19 | Tagged upper Bollinger band</t>
+          <t>Topping tail (new high rejected), tail 51% of range | Fib 50.0% retrace @ 120.42 | Major pivot zone (7 touches, 1.6x vol) @ 118.99 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -2085,7 +2085,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -2093,13 +2093,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D29" s="8" t="n">
-        <v>0.626</v>
+        <v>1</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>4.75</v>
@@ -2108,23 +2108,23 @@
         <v>4</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>113.26</v>
+        <v>643.6</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>1.27</v>
+        <v>2.2</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>58.7</v>
+        <v>79.2</v>
       </c>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>Doji (indecision at extreme) | Time count: 7 up bars since the last down bar | Major pivot zone (3 touches, 1.0x vol) @ 114.93 | Tagged upper Bollinger band</t>
+          <t>Topping tail (new high rejected), tail 51% of range | Time count: TD setup 15 | RSI overbought (79) | Extended 4.4 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
@@ -2149,13 +2149,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>0.831</v>
+        <v>1</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>4.75</v>
@@ -2164,10 +2164,10 @@
         <v>4</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>75.02</v>
+        <v>74.88</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>1.01</v>
+        <v>0.82</v>
       </c>
       <c r="I30" s="7" t="n">
         <v>5</v>
@@ -2176,11 +2176,11 @@
         <v>5</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>60</v>
+        <v>59.6</v>
       </c>
       <c r="L30" s="9" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 71% of range | Fib 78.6% retrace @ 76.45 | Major pivot zone (10 touches, 1.5x vol) @ 75.24 | Tagged upper Bollinger band</t>
+          <t>Topping tail (new high rejected), tail 72% of range | Fib 78.6% retrace @ 76.45 | Major pivot zone (10 touches, 1.5x vol) @ 75.24 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
@@ -2195,56 +2195,56 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>BAX</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F31" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>23.63</v>
-      </c>
-      <c r="H31" s="7" t="n">
-        <v>-7.19</v>
-      </c>
-      <c r="I31" s="7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J31" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="L31" s="9" t="inlineStr">
-        <is>
-          <t>Bearish engulfing | Prior pivot (2 touches, 0.9x vol) @ 25.84 | Bearish RSI divergence (42) | Tagged upper Bollinger band | Volume 2.1x average</t>
-        </is>
-      </c>
-      <c r="M31" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N31" s="10" t="inlineStr">
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>62.05</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>Bottoming tail (new low rejected), tail 55% of range | Time count: TD setup 9 | Trendline (falling support) @ 60.70 | Extended 3.0 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N31" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2253,7 +2253,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -2261,13 +2261,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Failed at close</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>0.799</v>
+        <v>0</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>4.5</v>
@@ -2276,23 +2276,23 @@
         <v>4</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>60.5</v>
+        <v>51.51</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>1.51</v>
+        <v>0.78</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>60.5</v>
+        <v>71</v>
       </c>
       <c r="L32" s="9" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 64% of range | Time count: 7 up bars since the last down bar | Prior pivot (1 touch, 0.8x vol) @ 60.89 | Tagged upper Bollinger band</t>
+          <t>Doji (indecision at extreme) | Time count: TD setup 20 | Trendline (rising resistance) @ 51.68 | RSI overbought (71)</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -2307,168 +2307,168 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Failed at close</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>275.17</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 61% of range | Time count: TD setup 8 | Prior pivot (1 touch, 1.0x vol) @ 281.07 | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N33" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>MGM</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="2" t="n">
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="F34" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G33" s="2" t="n">
-        <v>28.69</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>Bullish engulfing | Bullish RSI divergence (37) | Tagged lower Bollinger band | Extended 2.7 ATR from 20 EMA | Volume 1.9x average</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N33" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="n">
-        <v>0.911</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>65.13</v>
-      </c>
-      <c r="H34" s="7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="I34" s="7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="L34" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail, tail 62% of range | Fib 50.0% retrace @ 65.85 | Prior pivot (2 touches, 1.4x vol) @ 65.45 | High-volume node @ 65.93</t>
-        </is>
-      </c>
-      <c r="M34" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N34" s="10" t="inlineStr">
+      <c r="G34" s="2" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>Bullish engulfing | Bullish RSI divergence (38) | Tagged lower Bollinger band | Extended 2.7 ATR from 20 EMA | Volume 2.1x average</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N34" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>HAS</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="E35" s="7" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="F35" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G35" s="7" t="n">
-        <v>119.59</v>
-      </c>
-      <c r="H35" s="7" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I35" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="J35" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="L35" s="9" t="inlineStr">
-        <is>
-          <t>Doji (indecision at extreme) | Time count: TD setup 24 | RSI overbought (89) | Extended 4.5 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M35" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N35" s="10" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>330.64</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>Bottoming tail, tail 53% of range | Time count: 10 down bars since the last up bar | Major pivot zone (4 touches, 2.4x vol) @ 326.14</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N35" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2477,7 +2477,7 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -2485,13 +2485,13 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>4.25</v>
@@ -2500,23 +2500,23 @@
         <v>4</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>222.24</v>
+        <v>65.09</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>65.90000000000001</v>
+        <v>59.2</v>
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>Doji (indecision at extreme) | Time count: TD setup 11 | Fib 50.0% retrace @ 224.11 | Prior pivot (2 touches, 1.5x vol) @ 221.25</t>
+          <t>Topping tail, tail 62% of range | Fib 50.0% retrace @ 65.85 | Prior pivot (2 touches, 1.4x vol) @ 65.45 | High-volume node @ 65.93</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -2531,56 +2531,56 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>SHW</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="2" t="n">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>HAS</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Failed at close</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="7" t="n">
         <v>4.25</v>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="F37" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G37" s="2" t="n">
-        <v>330.02</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>Bottoming tail, tail 81% of range | Fib 61.8% retrace @ 320.56 | Prior pivot (2 touches, 1.5x vol) @ 326.09 | Volume POC @ 320.98</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N37" s="6" t="inlineStr">
+      <c r="G37" s="7" t="n">
+        <v>119.57</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J37" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="K37" s="7" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="L37" s="9" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | Time count: TD setup 24 | RSI overbought (89) | Extended 4.5 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N37" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2589,7 +2589,7 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>CASY</t>
+          <t>HBAN</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -2597,38 +2597,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>Failed at close</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>0.992</v>
+        <v>0</v>
       </c>
       <c r="E38" s="7" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F38" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F38" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G38" s="7" t="n">
-        <v>674.52</v>
+        <v>15.97</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>0.67</v>
+        <v>1.72</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="J38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>50.9</v>
+        <v>59.4</v>
       </c>
       <c r="L38" s="9" t="inlineStr">
         <is>
-          <t>Topping tail, tail 47% of range | Major pivot zone (2 touches, 6.6x vol) @ 690.37 | High-volume node @ 681.51</t>
+          <t>Doji (indecision at extreme) | Time count: 8 up bars since the last down bar | Fib 38.2% retrace @ 16.19 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
@@ -2645,7 +2645,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>CIEN</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -2653,38 +2653,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Failed at close</t>
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>0.9330000000000001</v>
+        <v>0</v>
       </c>
       <c r="E39" s="7" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F39" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F39" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G39" s="7" t="n">
-        <v>346.7</v>
+        <v>222.14</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>-4.55</v>
+        <v>1.31</v>
       </c>
       <c r="I39" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J39" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="J39" s="7" t="n">
-        <v>-1</v>
-      </c>
       <c r="K39" s="7" t="n">
-        <v>46.3</v>
+        <v>65.8</v>
       </c>
       <c r="L39" s="9" t="inlineStr">
         <is>
-          <t>Topping tail, tail 61% of range | Major pivot zone (6 touches, 1.4x vol) @ 366.58 | Volume POC @ 351.24</t>
+          <t>Doji (indecision at extreme) | Time count: TD setup 11 | Fib 50.0% retrace @ 224.11 | Prior pivot (2 touches, 1.5x vol) @ 221.25</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>GNRC</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -2709,38 +2709,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>Developing</t>
         </is>
       </c>
       <c r="D40" s="8" t="n">
-        <v>0.791</v>
+        <v>1</v>
       </c>
       <c r="E40" s="7" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F40" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F40" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G40" s="7" t="n">
-        <v>203.3</v>
+        <v>199.46</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>0.97</v>
+        <v>1.85</v>
       </c>
       <c r="I40" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J40" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="J40" s="7" t="n">
-        <v>4</v>
-      </c>
       <c r="K40" s="7" t="n">
-        <v>51.7</v>
+        <v>60.4</v>
       </c>
       <c r="L40" s="9" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 86% of range | Major pivot zone (2 touches, 3.0x vol) @ 211.79 | Volume POC @ 204.31</t>
+          <t>Topping tail (new high rejected), tail 59% of range | Major pivot zone (5 touches, 2.1x vol) @ 203.68 | Tagged upper Bollinger band | Volume 1.7x average</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
@@ -2757,7 +2757,7 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -2765,38 +2765,38 @@
           <t>bearish</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>Failed at close</t>
         </is>
       </c>
       <c r="D41" s="8" t="n">
-        <v>0.9389999999999999</v>
+        <v>0</v>
       </c>
       <c r="E41" s="7" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F41" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F41" s="7" t="n">
+      <c r="G41" s="7" t="n">
+        <v>106.63</v>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="I41" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J41" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G41" s="7" t="n">
-        <v>82.04000000000001</v>
-      </c>
-      <c r="H41" s="7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="I41" s="7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J41" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="K41" s="7" t="n">
-        <v>59.9</v>
+        <v>60.1</v>
       </c>
       <c r="L41" s="9" t="inlineStr">
         <is>
-          <t>Topping tail (new high rejected), tail 75% of range | Major pivot zone (3 touches, 2.4x vol) @ 82.62 | Volume POC @ 82.88</t>
+          <t>Doji (indecision at extreme) | Time count: TD setup 7 | Fib 38.2% retrace @ 106.62 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
@@ -2811,56 +2811,56 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>FFIV</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>WAT</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="E42" s="2" t="n">
+          <t>Failed at close</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F42" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F42" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>360.78</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="L42" s="5" t="inlineStr">
-        <is>
-          <t>Doji (indecision at extreme) | RSI oversold (26) | Tagged lower Bollinger band | Extended 4.2 ATR from 20 EMA | Volume 2.1x average</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N42" s="6" t="inlineStr">
+      <c r="G42" s="7" t="n">
+        <v>480.02</v>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J42" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K42" s="7" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="L42" s="9" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | Time count: TD setup 11 | RSI overbought (74) | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M42" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N42" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -2869,7 +2869,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>SHW</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2877,38 +2877,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>0.652</v>
+        <v>1</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>180.21</v>
+        <v>330.18</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>6.32</v>
+        <v>2.92</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>44.7</v>
+        <v>50.5</v>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>Bottoming tail, tail 67% of range | High-volume node @ 173.84 | Trendline (rising support) @ 179.82 | Volume 2.2x average</t>
+          <t>Bottoming tail, tail 80% of range | Fib 61.8% retrace @ 320.56 | Prior pivot (2 touches, 1.5x vol) @ 326.09 | Volume POC @ 320.98</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -2923,336 +2923,336 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="2" t="n">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>CASY</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>Failed at close</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F44" s="2" t="n">
+      <c r="F44" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G44" s="2" t="n">
-        <v>659.8099999999999</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="2" t="n">
+      <c r="G44" s="7" t="n">
+        <v>677.74</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="L44" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail, tail 47% of range | Major pivot zone (2 touches, 6.6x vol) @ 690.37 | High-volume node @ 681.51</t>
+        </is>
+      </c>
+      <c r="M44" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N44" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>CIEN</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>349.15</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>-3.87</v>
+      </c>
+      <c r="I45" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="K44" s="2" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="L44" s="5" t="inlineStr">
-        <is>
-          <t>Bullish engulfing | Fib 50.0% retrace @ 616.05 | Major pivot zone (3 touches, 1.5x vol) @ 619.72</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N44" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>BKNG</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="J45" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K45" s="7" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="L45" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail, tail 58% of range | Major pivot zone (6 touches, 1.4x vol) @ 366.58 | Volume POC @ 351.24</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N45" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>GNRC</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>203.37</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K46" s="7" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="L46" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 85% of range | Major pivot zone (2 touches, 3.0x vol) @ 211.79 | Volume POC @ 204.31</t>
+        </is>
+      </c>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N46" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D45" s="4" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="F45" s="2" t="n">
+      <c r="D47" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G45" s="2" t="n">
-        <v>150.34</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>-7</v>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" s="2" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>Bottoming tail, tail 65% of range | Major pivot zone (2 touches, 2.4x vol) @ 149.50 | Tagged lower Bollinger band</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N45" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>ANET</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F46" s="2" t="n">
+      <c r="G47" s="7" t="n">
+        <v>82.11</v>
+      </c>
+      <c r="H47" s="7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I47" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" s="7" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="L47" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 69% of range | Major pivot zone (3 touches, 2.4x vol) @ 82.62 | Volume POC @ 82.88</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N47" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>SRE</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G46" s="2" t="n">
-        <v>183.07</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>-1.95</v>
-      </c>
-      <c r="I46" s="2" t="n">
+      <c r="G48" s="7" t="n">
+        <v>85.88</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" s="7" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="L48" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 59% of range | Time count: 7 bars without a lower low | Fib 50.0% retrace @ 85.72</t>
+        </is>
+      </c>
+      <c r="M48" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N48" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>ZBH</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>Failed at close</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="J46" s="2" t="n">
+      <c r="G49" s="7" t="n">
+        <v>97.47</v>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I49" s="7" t="n">
         <v>-2</v>
       </c>
-      <c r="K46" s="2" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="L46" s="5" t="inlineStr">
-        <is>
-          <t>Doji (indecision at extreme) | Fib 38.2% retrace @ 185.98 | Major pivot zone (10 touches, 2.3x vol) @ 180.72</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N46" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C47" s="11" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>220.54</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="I47" s="2" t="n">
+      <c r="J49" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="J47" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K47" s="2" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t>Doji (indecision at extreme) | Major pivot zone (1 touch, 1.9x vol) @ 216.04 | High-volume node @ 216.25</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N47" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>GLW</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>128.55</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>-2.02</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="L48" s="5" t="inlineStr">
-        <is>
-          <t>Doji (indecision at extreme) | Major pivot zone (2 touches, 2.0x vol) @ 125.03 | Volume POC @ 129.44</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N48" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>WAB</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C49" s="12" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>0.989</v>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>284.46</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J49" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K49" s="2" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="L49" s="5" t="inlineStr">
-        <is>
-          <t>Bullish engulfing | Fib 50.0% retrace @ 278.61 | Trendline (rising support) @ 277.12</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N49" s="6" t="inlineStr">
+      <c r="K49" s="7" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="L49" s="9" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | Time count: 11 up bars since the last down bar | Major pivot zone (3 touches, 1.7x vol) @ 97.32</t>
+        </is>
+      </c>
+      <c r="M49" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N49" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -3261,7 +3261,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>HUBB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3269,38 +3269,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C50" s="11" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>0.271</v>
+        <v>1</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>434.52</v>
+        <v>660</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>-0.64</v>
+        <v>3.02</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>36.2</v>
+        <v>54</v>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>Doji (indecision at extreme) | Major pivot zone (3 touches, 1.1x vol) @ 438.28 | Tagged lower Bollinger band</t>
+          <t>Bullish engulfing | Fib 50.0% retrace @ 616.05 | Major pivot zone (3 touches, 1.5x vol) @ 619.72</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3327,156 +3327,156 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Likely to confirm</t>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D51" s="4" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>151.7</v>
+        <v>196.42</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>1.84</v>
+        <v>-0.2</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="J51" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>Bottoming tail (new low rejected), tail 74% of range | Major pivot zone (4 touches, 1.2x vol) @ 188.00 | Trendline (rising support) @ 191.34</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N51" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>Failed at close</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>125.75</v>
+      </c>
+      <c r="H52" s="7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I52" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="K51" s="2" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="L51" s="5" t="inlineStr">
-        <is>
-          <t>Bottoming tail, tail 50% of range | Fib 38.2% retrace @ 149.71 | Prior pivot (1 touch, 1.1x vol) @ 150.46</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N51" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>ARE</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>40.48</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J52" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="K52" s="2" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="L52" s="5" t="inlineStr">
-        <is>
-          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 38.34) | Bottoming tail (new low rejected), tail 59% of range | Major pivot zone (1 touch, 2.5x vol) @ 38.32 | Trendline (falling support) @ 37.65 | Bullish RSI divergence (31) | Tagged lower Bollinger band | Extended 3.0 ATR from 20 EMA | Volume 2.3x average</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N52" s="6" t="inlineStr">
+      <c r="J52" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K52" s="7" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="L52" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 66% of range | Time count: 7 up bars since the last down bar | Prior pivot (2 touches, 1.2x vol) @ 126.30</t>
+        </is>
+      </c>
+      <c r="M52" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N52" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>GPC</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>121.87</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>-7</v>
-      </c>
-      <c r="J53" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K53" s="2" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="L53" s="5" t="inlineStr">
-        <is>
-          <t>Setup from 2 bars ago, still near entry (+0.0 ATR since signal; stop beyond 120.18) | Bottoming tail (new low rejected), tail 59% of range | Fib 38.2% retrace @ 119.82 | Major pivot zone (4 touches, 1.8x vol) @ 121.77 | Trendline (falling support) @ 121.46 | Tagged lower Bollinger band</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N53" s="6" t="inlineStr">
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F53" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" s="7" t="n">
+        <v>53.82</v>
+      </c>
+      <c r="H53" s="7" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J53" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="L53" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail, tail 62% of range | Time count: TD setup 9 | Prior pivot (1 touch, 1.1x vol) @ 54.23</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N53" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -3485,7 +3485,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3502,205 +3502,205 @@
         <v>1</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>5.75</v>
+        <v>3.75</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>177.83</v>
+        <v>150.43</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>2.27</v>
+        <v>1.68</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="J54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>Bottoming tail, tail 67% of range | Major pivot zone (2 touches, 2.4x vol) @ 149.50 | Tagged lower Bollinger band</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N54" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>163.03</v>
+      </c>
+      <c r="H55" s="7" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="I55" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="K54" s="2" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="L54" s="5" t="inlineStr">
-        <is>
-          <t>Setup from 1 bar ago, still near entry (+0.8 ATR since signal; stop beyond 170.14) | Bullish engulfing | Major pivot zone (5 touches, 1.3x vol) @ 172.11 | Trendline (falling support) @ 170.53 | Bullish RSI divergence (43) | Tagged lower Bollinger band</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N54" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>LRCX</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>252.91</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>-15</v>
-      </c>
-      <c r="J55" s="2" t="n">
+      <c r="K55" s="7" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="L55" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 56% of range | Prior pivot (2 touches, 1.2x vol) @ 166.55 | Tagged upper Bollinger band | Volume 1.6x average</t>
+        </is>
+      </c>
+      <c r="M55" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N55" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>AXP</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>323.7</v>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="K55" s="2" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="L55" s="5" t="inlineStr">
-        <is>
-          <t>Setup from 2 bars ago, still near entry (+0.9 ATR since signal; stop beyond 235.21) | Bottoming tail, tail 87% of range | Time count: TD setup 14 | Prior pivot (2 touches, 1.1x vol) @ 241.07 | High-volume node @ 234.92 | Extended 2.8 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N55" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>FDXF</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C56" s="12" t="inlineStr">
-        <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>107.48</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="I56" s="2" t="n">
+      <c r="K56" s="7" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="L56" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 51% of range | Fib 50.0% retrace @ 329.15 | Bearish RSI divergence (60)</t>
+        </is>
+      </c>
+      <c r="M56" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N56" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>NEM</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>Failed at close</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" s="7" t="n">
+        <v>111.81</v>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="I57" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="7" t="n">
         <v>-1</v>
       </c>
-      <c r="J56" s="2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="K56" s="2" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="L56" s="5" t="inlineStr">
-        <is>
-          <t>Setup from 1 bar ago, still near entry (-0.2 ATR since signal; stop beyond 103.48) | Bottoming tail (new low rejected), tail 90% of range | Prior pivot (2 touches, 1.8x vol) @ 106.96 | Trendline (falling support) @ 103.62 | Bullish RSI divergence (38) | Tagged lower Bollinger band</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N56" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>GEV</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C57" s="11" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>887.6</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K57" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="L57" s="5" t="inlineStr">
-        <is>
-          <t>Setup from 1 bar ago, still near entry (+0.2 ATR since signal; stop beyond 836.24) | Bottoming tail, tail 72% of range | Time count: TD setup 10 | Major pivot zone (6 touches, 2.1x vol) @ 870.38 | Volume 2.3x average</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N57" s="6" t="inlineStr">
+      <c r="K57" s="7" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="L57" s="9" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme) | Major pivot zone (3 touches, 2.5x vol) @ 111.41 | High-volume node @ 113.87</t>
+        </is>
+      </c>
+      <c r="M57" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N57" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -3709,7 +3709,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>HSIC</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3717,38 +3717,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>Failed at close</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>86.19</v>
+        <v>128.89</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>1.45</v>
+        <v>-1.76</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>48.1</v>
+        <v>39.5</v>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.7 ATR since signal; stop beyond 83.97) | Bullish engulfing | Fib 38.2% retrace @ 83.21 | Major pivot zone (1 touch, 1.9x vol) @ 84.15 | High-volume node @ 84.67</t>
+          <t>Doji (indecision at extreme) | Major pivot zone (2 touches, 2.0x vol) @ 125.03 | Volume POC @ 129.44</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>WAB</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3773,102 +3773,102 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C59" s="12" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D59" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="F59" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>285.46</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J59" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G59" s="2" t="n">
-        <v>634.17</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="2" t="n">
+      <c r="K59" s="2" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>Bullish engulfing | Fib 50.0% retrace @ 278.61 | Trendline (rising support) @ 277.12</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N59" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F60" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="K59" s="2" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="L59" s="5" t="inlineStr">
-        <is>
-          <t>Setup from 1 bar ago, still near entry (+1.0 ATR since signal; stop beyond 581.78) | Bottoming tail, tail 66% of range | Time count: TD setup 12 | Major pivot zone (5 touches, 1.5x vol) @ 594.79 | Volume 1.8x average</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N59" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>VRT</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C60" s="11" t="inlineStr">
-        <is>
-          <t>At risk</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>245.89</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K60" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="L60" s="5" t="inlineStr">
-        <is>
-          <t>Setup from 1 bar ago, still near entry (+0.2 ATR since signal; stop beyond 228.81) | Bottoming tail, tail 86% of range | Time count: TD setup 14 | Major pivot zone (5 touches, 3.3x vol) @ 226.83 | Volume 3.3x average</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N60" s="6" t="inlineStr">
+      <c r="G60" s="7" t="n">
+        <v>348.91</v>
+      </c>
+      <c r="H60" s="7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" s="7" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>Topping tail (new high rejected), tail 61% of range | Trendline (rising resistance) @ 350.40 | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M60" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N60" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -3887,36 +3887,36 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Likely to confirm</t>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D61" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>102.17</v>
+        <v>102.29</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.13</v>
       </c>
       <c r="I61" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J61" s="2" t="n">
         <v>-6</v>
       </c>
-      <c r="J61" s="2" t="n">
-        <v>-5</v>
-      </c>
       <c r="K61" s="2" t="n">
-        <v>26</v>
+        <v>25.8</v>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (-0.1 ATR since signal; stop beyond 100.50) | Bottoming tail, tail 62% of range | Prior pivot (1 touch, 1.6x vol) @ 99.18 | RSI oversold (26) | Tagged lower Bollinger band | Extended 2.8 ATR from 20 EMA</t>
+          <t>Bottoming tail, tail 55% of range | RSI oversold (26) | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3941,38 +3941,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C62" s="11" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>56.99</v>
+        <v>151.81</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>0.77</v>
+        <v>1.91</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>52.4</v>
+        <v>46.9</v>
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>Setup from 2 bars ago, still near entry (+0.6 ATR since signal; stop beyond 54.34) | Bottoming tail (new low rejected), tail 47% of range | Fib 38.2% retrace @ 53.99 | Prior pivot (2 touches, 1.3x vol) @ 54.64 | Trendline (rising support) @ 54.50 | Volume 1.8x average</t>
+          <t>Bottoming tail, tail 50% of range | Fib 38.2% retrace @ 149.71 | Prior pivot (1 touch, 1.1x vol) @ 150.46</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>EME</t>
+          <t>CHRW</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3997,38 +3997,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C63" s="12" t="inlineStr">
-        <is>
-          <t>Developing</t>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D63" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>687.36</v>
+        <v>127.43</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>1.3</v>
+        <v>-0.13</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>37</v>
+        <v>33.2</v>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 665.55) | Bottoming tail, tail 68% of range | Time count: TD setup 12 | Major pivot zone (1 touch, 2.0x vol) @ 668.46</t>
+          <t>Bottoming tail (new low rejected), tail 64% of range | Tagged lower Bollinger band | Extended 2.8 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -4045,7 +4045,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GPN</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4062,29 +4062,29 @@
         <v>1</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>85.53</v>
+        <v>179</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>2.37</v>
+        <v>5.61</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>49.7</v>
+        <v>43.7</v>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.8 ATR since signal; stop beyond 80.85) | Bullish engulfing | Fib 38.2% retrace @ 82.29 | Prior pivot (2 touches, 1.7x vol) @ 82.12 | Trendline (rising support) @ 81.14</t>
+          <t>Bottoming tail, tail 67% of range | High-volume node @ 173.84 | Volume 2.8x average</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -4099,56 +4099,56 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>APA</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>FDXF</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Likely to confirm</t>
-        </is>
-      </c>
-      <c r="D65" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F65" s="7" t="n">
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G65" s="7" t="n">
-        <v>51.22</v>
-      </c>
-      <c r="H65" s="7" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I65" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="J65" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K65" s="7" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="L65" s="9" t="inlineStr">
-        <is>
-          <t>Setup from 1 bar ago, still near entry (-0.1 ATR since signal; stop beyond 52.07) | Topping tail, tail 73% of range | Time count: TD setup 19 | Trendline (rising resistance) @ 51.54</t>
-        </is>
-      </c>
-      <c r="M65" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N65" s="10" t="inlineStr">
+      <c r="F65" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>109.88</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>Bullish engulfing | Prior pivot (2 touches, 1.8x vol) @ 106.96 | Tagged lower Bollinger band</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N65" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -4157,7 +4157,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4167,36 +4167,36 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Likely to confirm</t>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>0.839</v>
+        <v>1</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>563.47</v>
+        <v>40.6</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>-2.59</v>
+        <v>1.73</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>53.6</v>
+        <v>31.5</v>
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (-0.6 ATR since signal; stop beyond 560.52) | Bottoming tail, tail 67% of range | Fib 38.2% retrace @ 557.23 | Major pivot zone (4 touches, 1.1x vol) @ 571.91</t>
+          <t>Setup from 1 bar ago, still near entry (+0.4 ATR since signal; stop beyond 38.34) | Bottoming tail (new low rejected), tail 59% of range | Major pivot zone (1 touch, 2.5x vol) @ 38.32 | Trendline (falling support) @ 37.65 | Bullish RSI divergence (31) | Tagged lower Bollinger band | Extended 3.0 ATR from 20 EMA | Volume 2.3x average</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>WELL</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4221,38 +4221,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>Failed at close</t>
         </is>
       </c>
       <c r="D67" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>4</v>
+        <v>6.25</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>44.32</v>
+        <v>233.13</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>0.54</v>
+        <v>2.61</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>48.2</v>
+        <v>43.4</v>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.2 ATR since signal; stop beyond 43.27) | Bottoming tail, tail 66% of range | Major pivot zone (3 touches, 1.1x vol) @ 42.78 | Trendline (rising support) @ 42.98</t>
+          <t>Setup from 1 bar ago, still near entry (+1.0 ATR since signal; stop beyond 217.72) | Bottoming tail (new low rejected), tail 46% of range | Fib 61.8% retrace @ 216.97 | Major pivot zone (3 touches, 1.4x vol) @ 219.55 | Bullish RSI divergence (43) | Tagged lower Bollinger band | Volume 2.2x average</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>GPC</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4277,38 +4277,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C68" s="11" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D68" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>159.67</v>
+        <v>122.29</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>35.4</v>
+        <v>38.7</v>
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 156.20) | Bottoming tail, tail 50% of range | Fib 78.6% retrace @ 157.06 | Major pivot zone (3 touches, 2.4x vol) @ 156.30</t>
+          <t>Setup from 2 bars ago, still near entry (+0.1 ATR since signal; stop beyond 120.18) | Bottoming tail (new low rejected), tail 59% of range | Fib 38.2% retrace @ 119.82 | Major pivot zone (4 touches, 1.8x vol) @ 121.77 | Trendline (falling support) @ 121.46 | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>IVZ</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4333,38 +4333,38 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C69" s="11" t="inlineStr">
-        <is>
-          <t>At risk</t>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D69" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>28.93</v>
+        <v>254.39</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>0.89</v>
+        <v>0.22</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>-4</v>
+        <v>-15</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>43</v>
+        <v>31.1</v>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 28.20) | Bottoming tail, tail 68% of range | Fib 61.8% retrace @ 28.57 | Major pivot zone (3 touches, 1.5x vol) @ 28.54</t>
+          <t>Setup from 2 bars ago, still near entry (+1.0 ATR since signal; stop beyond 235.21) | Bottoming tail, tail 87% of range | Time count: TD setup 14 | Prior pivot (2 touches, 1.1x vol) @ 241.07 | High-volume node @ 234.92 | Extended 2.8 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -4381,7 +4381,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4391,36 +4391,36 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>At risk</t>
+          <t>Failed at close</t>
         </is>
       </c>
       <c r="D70" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E70" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F70" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F70" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="G70" s="2" t="n">
-        <v>486.96</v>
+        <v>888.1</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 467.24) | Bottoming tail, tail 50% of range | Major pivot zone (2 touches, 2.1x vol) @ 465.90 | High-volume node @ 463.40</t>
+          <t>Setup from 1 bar ago, still near entry (+0.2 ATR since signal; stop beyond 836.24) | Bottoming tail, tail 72% of range | Time count: TD setup 10 | Major pivot zone (6 touches, 2.1x vol) @ 870.38 | Volume 2.3x average</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>HSIC</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4447,36 +4447,36 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Likely to confirm</t>
+          <t>Confirmed at close</t>
         </is>
       </c>
       <c r="D71" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>97.04000000000001</v>
+        <v>86.44</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.74</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>43.7</v>
+        <v>48.1</v>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (+0.0 ATR since signal; stop beyond 94.12) | Bottoming tail, tail 72% of range | Time count: TD setup 11 | Prior pivot (1 touch, 1.2x vol) @ 93.36</t>
+          <t>Setup from 1 bar ago, still near entry (+0.8 ATR since signal; stop beyond 83.97) | Bullish engulfing | Fib 38.2% retrace @ 83.21 | Major pivot zone (1 touch, 1.9x vol) @ 84.15 | High-volume node @ 84.67</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -4493,7 +4493,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>FIX</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4501,25 +4501,25 @@
           <t>bullish</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>Likely to confirm</t>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>Failed at close</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>1321.74</v>
+        <v>245.95</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>-1.79</v>
+        <v>1.24</v>
       </c>
       <c r="I72" s="2" t="n">
         <v>1</v>
@@ -4528,11 +4528,11 @@
         <v>3</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>39.4</v>
+        <v>57</v>
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>Setup from 1 bar ago, still near entry (-0.3 ATR since signal; stop beyond 1290.57) | Bottoming tail, tail 68% of range | Time count: TD setup 12 | Volume 1.6x average</t>
+          <t>Setup from 1 bar ago, still near entry (+0.2 ATR since signal; stop beyond 228.81) | Bottoming tail, tail 86% of range | Time count: TD setup 14 | Major pivot zone (5 touches, 3.3x vol) @ 226.83 | Volume 3.3x average</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -4547,504 +4547,504 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t>HII</t>
-        </is>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C73" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="7" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="F73" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="G73" s="7" t="n">
-        <v>317.25</v>
-      </c>
-      <c r="H73" s="7" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="I73" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="J73" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K73" s="7" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="L73" s="9" t="inlineStr">
-        <is>
-          <t>Time count: 11 up bars since the last down bar | Fib 78.6% retrace @ 319.32 | Prior pivot (1 touch, 1.2x vol) @ 322.62 | High-volume node @ 317.53 | RSI overbought (76) | Tagged upper Bollinger band | Extended 5.1 ATR from 20 EMA | Volume 2.7x average</t>
-        </is>
-      </c>
-      <c r="M73" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N73" s="10" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>Failed at close</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>Setup from 2 bars ago, still near entry (+0.6 ATR since signal; stop beyond 54.34) | Bottoming tail (new low rejected), tail 47% of range | Fib 38.2% retrace @ 53.99 | Prior pivot (2 touches, 1.3x vol) @ 54.64 | Trendline (rising support) @ 54.50 | Volume 1.8x average</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N73" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t>NCLH</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C74" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="E74" s="7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F74" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G74" s="7" t="n">
-        <v>18.18</v>
-      </c>
-      <c r="H74" s="7" t="n">
-        <v>13.23</v>
-      </c>
-      <c r="I74" s="7" t="n">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>EME</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F74" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J74" s="7" t="n">
+      <c r="G74" s="2" t="n">
+        <v>689.79</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>Setup from 1 bar ago, still near entry (+0.4 ATR since signal; stop beyond 665.55) | Bottoming tail, tail 68% of range | Time count: TD setup 12 | Major pivot zone (1 touch, 2.0x vol) @ 668.46</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N74" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>GPN</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F75" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K74" s="7" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="L74" s="9" t="inlineStr">
-        <is>
-          <t>Time count: 8 up bars since the last down bar | Fib 61.8% retrace @ 18.77 | High-volume node @ 18.57 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 2.9x average</t>
-        </is>
-      </c>
-      <c r="M74" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N74" s="10" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t>TDY</t>
-        </is>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C75" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E75" s="7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F75" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G75" s="7" t="n">
-        <v>673.7</v>
-      </c>
-      <c r="H75" s="7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="I75" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="J75" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K75" s="7" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="L75" s="9" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 12 | Fib 78.6% retrace @ 674.65 | Major pivot zone (2 touches, 3.2x vol) @ 672.68 | RSI overbought (75) | Tagged upper Bollinger band | Extended 3.2 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M75" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N75" s="10" t="inlineStr">
+      <c r="G75" s="2" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>Setup from 1 bar ago, still near entry (+0.9 ATR since signal; stop beyond 80.85) | Bullish engulfing | Fib 38.2% retrace @ 82.29 | Prior pivot (2 touches, 1.7x vol) @ 82.12 | Trendline (rising support) @ 81.14</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N75" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="7" t="inlineStr">
-        <is>
-          <t>UPS</t>
-        </is>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C76" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="E76" s="7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F76" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G76" s="7" t="n">
-        <v>106.82</v>
-      </c>
-      <c r="H76" s="7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="I76" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="J76" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K76" s="7" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="L76" s="9" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 15 | Fib 61.8% retrace @ 107.01 | Major pivot zone (3 touches, 3.0x vol) @ 107.05 | RSI overbought (73) | Tagged upper Bollinger band | Extended 3.0 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M76" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N76" s="10" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>566.42</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>Setup from 1 bar ago, still near entry (-0.5 ATR since signal; stop beyond 560.52) | Bottoming tail, tail 67% of range | Fib 38.2% retrace @ 557.23 | Major pivot zone (4 touches, 1.1x vol) @ 571.91</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N76" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>LHX</t>
-        </is>
-      </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C77" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F77" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G77" s="7" t="n">
-        <v>278.09</v>
-      </c>
-      <c r="H77" s="7" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="I77" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="J77" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K77" s="7" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="L77" s="9" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 15 | Major pivot zone (1 touch, 2.0x vol) @ 281.06 | RSI overbought (77) | Tagged upper Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 1.5x average</t>
-        </is>
-      </c>
-      <c r="M77" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N77" s="10" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>APTV</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>44.42</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>Setup from 1 bar ago, still near entry (+0.3 ATR since signal; stop beyond 43.27) | Bottoming tail, tail 66% of range | Major pivot zone (3 touches, 1.1x vol) @ 42.78 | Trendline (rising support) @ 42.98</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N77" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t>VMC</t>
-        </is>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C78" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D78" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="7" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="F78" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G78" s="7" t="n">
-        <v>281.11</v>
-      </c>
-      <c r="H78" s="7" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="I78" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="7" t="n">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F78" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K78" s="7" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="L78" s="9" t="inlineStr">
-        <is>
-          <t>Fib 61.8% retrace @ 288.65 | Prior pivot (1 touch, 1.3x vol) @ 288.44 | Volume POC @ 289.56 | RSI overbought (73) | Tagged upper Bollinger band | Extended 3.8 ATR from 20 EMA | Volume 1.7x average</t>
-        </is>
-      </c>
-      <c r="M78" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N78" s="10" t="inlineStr">
+      <c r="G78" s="2" t="n">
+        <v>222.21</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>-2.57</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>Setup from 1 bar ago, still near entry (-0.3 ATR since signal; stop beyond 217.90) | Bottoming tail, tail 59% of range | Major pivot zone (1 touch, 1.9x vol) @ 216.04 | High-volume node @ 216.25</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N78" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>AON</t>
-        </is>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C79" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D79" s="8" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="E79" s="7" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="F79" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G79" s="7" t="n">
-        <v>320.68</v>
-      </c>
-      <c r="H79" s="7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="I79" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="J79" s="7" t="n">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F79" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K79" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="L79" s="9" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 10 | Fib 50.0% retrace @ 323.90 | Prior pivot (1 touch, 1.3x vol) @ 324.30 | Volume POC @ 320.45 | Tagged upper Bollinger band | Extended 3.4 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M79" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N79" s="10" t="inlineStr">
+      <c r="G79" s="2" t="n">
+        <v>160.53</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>Setup from 1 bar ago, still near entry (+0.6 ATR since signal; stop beyond 156.20) | Bottoming tail, tail 50% of range | Fib 78.6% retrace @ 157.06 | Major pivot zone (3 touches, 2.4x vol) @ 156.30</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N79" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>GD</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C80" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="7" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="F80" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G80" s="7" t="n">
-        <v>367.7</v>
-      </c>
-      <c r="H80" s="7" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="I80" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="J80" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K80" s="7" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="L80" s="9" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 14 | Fib 61.8% retrace @ 368.42 | Prior pivot (1 touch, 1.6x vol) @ 372.24 | RSI overbought (71) | Tagged upper Bollinger band | Extended 3.6 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M80" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N80" s="10" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>IVZ</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>Failed at close</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>Setup from 1 bar ago, still near entry (+0.4 ATR since signal; stop beyond 28.20) | Bottoming tail, tail 68% of range | Fib 61.8% retrace @ 28.57 | Major pivot zone (3 touches, 1.5x vol) @ 28.54</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N80" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t>NXPI</t>
-        </is>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C81" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D81" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="7" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="F81" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G81" s="7" t="n">
-        <v>265.15</v>
-      </c>
-      <c r="H81" s="7" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="I81" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="J81" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K81" s="7" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="L81" s="9" t="inlineStr">
-        <is>
-          <t>Time count: 13 up bars since the last down bar | Fib 38.2% retrace @ 262.53 | Prior pivot (1 touch, 1.0x vol) @ 265.83 | Trendline (rising resistance) @ 263.21 | Tagged upper Bollinger band | Extended 2.5 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M81" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N81" s="10" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>SNPS</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed at close</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>490.19</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>Setup from 1 bar ago, still near entry (+0.4 ATR since signal; stop beyond 467.24) | Bottoming tail, tail 50% of range | Major pivot zone (2 touches, 2.1x vol) @ 465.90 | High-volume node @ 463.40</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N81" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5053,7 +5053,7 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>NI</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -5067,32 +5067,32 @@
         </is>
       </c>
       <c r="D82" s="8" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>5.75</v>
+        <v>7.25</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>44.81</v>
+        <v>316.58</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>2.13</v>
+        <v>13.37</v>
       </c>
       <c r="I82" s="7" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J82" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K82" s="7" t="n">
-        <v>74.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="L82" s="9" t="inlineStr">
         <is>
-          <t>Time count: TD setup 20 | Fib 61.8% retrace @ 44.89 | Major pivot zone (3 touches, 1.9x vol) @ 44.71 | RSI overbought (74) | Extended 3.2 ATR from 20 EMA</t>
+          <t>Time count: 11 up bars since the last down bar | Fib 78.6% retrace @ 319.32 | Prior pivot (1 touch, 1.2x vol) @ 322.62 | High-volume node @ 317.53 | RSI overbought (76) | Tagged upper Bollinger band | Extended 5.1 ATR from 20 EMA | Volume 3.0x average</t>
         </is>
       </c>
       <c r="M82" s="7" t="inlineStr">
@@ -5109,7 +5109,7 @@
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>NCLH</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
@@ -5123,32 +5123,32 @@
         </is>
       </c>
       <c r="D83" s="8" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>87.75</v>
+        <v>18.2</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>12.04</v>
+        <v>13.33</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J83" s="7" t="n">
         <v>4</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>76.5</v>
+        <v>73.8</v>
       </c>
       <c r="L83" s="9" t="inlineStr">
         <is>
-          <t>Time count: TD setup 13 | Volume POC @ 88.76 | RSI overbought (77) | Tagged upper Bollinger band | Extended 5.1 ATR from 20 EMA | Volume 2.0x average</t>
+          <t>Time count: 8 up bars since the last down bar | Fib 61.8% retrace @ 18.77 | High-volume node @ 18.57 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 3.2x average</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
@@ -5165,7 +5165,7 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>WEC</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -5179,32 +5179,32 @@
         </is>
       </c>
       <c r="D84" s="8" t="n">
-        <v>0.254</v>
+        <v>0</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>114.65</v>
+        <v>87.48</v>
       </c>
       <c r="H84" s="7" t="n">
-        <v>3.76</v>
+        <v>11.7</v>
       </c>
       <c r="I84" s="7" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J84" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K84" s="7" t="n">
-        <v>71.8</v>
+        <v>76.2</v>
       </c>
       <c r="L84" s="9" t="inlineStr">
         <is>
-          <t>Fib 78.6% retrace @ 114.79 | Major pivot zone (5 touches, 1.7x vol) @ 116.28 | RSI overbought (72) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 2.2x average</t>
+          <t>Time count: TD setup 13 | Fib 61.8% retrace @ 87.58 | Volume POC @ 88.76 | RSI overbought (76) | Tagged upper Bollinger band | Extended 5.1 ATR from 20 EMA | Volume 2.2x average</t>
         </is>
       </c>
       <c r="M84" s="7" t="inlineStr">
@@ -5221,7 +5221,7 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>DOV</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
@@ -5235,32 +5235,32 @@
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>209.85</v>
+        <v>280.27</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>0.89</v>
+        <v>5.76</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J85" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K85" s="7" t="n">
-        <v>73.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="L85" s="9" t="inlineStr">
         <is>
-          <t>Fib 50.0% retrace @ 208.52 | Major pivot zone (3 touches, 1.6x vol) @ 209.50 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.0 ATR from 20 EMA</t>
+          <t>Fib 61.8% retrace @ 288.65 | Major pivot zone (6 touches, 1.7x vol) @ 280.70 | Volume POC @ 289.56 | RSI overbought (72) | Tagged upper Bollinger band | Extended 3.8 ATR from 20 EMA | Volume 1.9x average</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
@@ -5277,7 +5277,7 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>TDY</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -5291,32 +5291,32 @@
         </is>
       </c>
       <c r="D86" s="8" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="E86" s="7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F86" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G86" s="7" t="n">
+        <v>677.41</v>
+      </c>
+      <c r="H86" s="7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I86" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="J86" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F86" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G86" s="7" t="n">
-        <v>307.26</v>
-      </c>
-      <c r="H86" s="7" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I86" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="J86" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="K86" s="7" t="n">
-        <v>60.2</v>
+        <v>75.8</v>
       </c>
       <c r="L86" s="9" t="inlineStr">
         <is>
-          <t>Time count: TD setup 10 | Fib 50.0% retrace @ 310.98 | Prior pivot (1 touch, 1.4x vol) @ 312.88 | High-volume node @ 311.94 | Tagged upper Bollinger band</t>
+          <t>Time count: TD setup 12 | Fib 78.6% retrace @ 674.65 | Major pivot zone (2 touches, 3.2x vol) @ 672.68 | RSI overbought (76) | Tagged upper Bollinger band | Extended 3.2 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M86" s="7" t="inlineStr">
@@ -5333,7 +5333,7 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -5347,32 +5347,32 @@
         </is>
       </c>
       <c r="D87" s="8" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>311.55</v>
+        <v>107.31</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J87" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>71.2</v>
+        <v>73.5</v>
       </c>
       <c r="L87" s="9" t="inlineStr">
         <is>
-          <t>Time count: 7 bars without a lower low | Fib 78.6% retrace @ 314.31 | Prior pivot (1 touch, 0.7x vol) @ 313.73 | RSI overbought (71) | Tagged upper Bollinger band</t>
+          <t>Time count: TD setup 15 | Fib 61.8% retrace @ 107.01 | Major pivot zone (3 touches, 3.0x vol) @ 107.05 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.1 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
@@ -5389,7 +5389,7 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>URI</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -5403,32 +5403,32 @@
         </is>
       </c>
       <c r="D88" s="8" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>1191.74</v>
+        <v>266</v>
       </c>
       <c r="H88" s="7" t="n">
-        <v>1.46</v>
+        <v>5.69</v>
       </c>
       <c r="I88" s="7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J88" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K88" s="7" t="n">
-        <v>72.5</v>
+        <v>69.8</v>
       </c>
       <c r="L88" s="9" t="inlineStr">
         <is>
-          <t>Time count: 7 up bars since the last down bar | Trendline (rising resistance) @ 1185.31 | RSI overbought (73) | Tagged upper Bollinger band | Extended 2.8 ATR from 20 EMA</t>
+          <t>Time count: 13 up bars since the last down bar | Fib 38.2% retrace @ 262.53 | Prior pivot (1 touch, 1.0x vol) @ 265.83 | Trendline (rising resistance) @ 263.21 | Tagged upper Bollinger band | Extended 2.6 ATR from 20 EMA | Volume 1.5x average</t>
         </is>
       </c>
       <c r="M88" s="7" t="inlineStr">
@@ -5443,14 +5443,14 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>TPR</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>LHX</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
         </is>
       </c>
       <c r="C89" s="13" t="inlineStr">
@@ -5458,41 +5458,41 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D89" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F89" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>117.76</v>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K89" s="2" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="L89" s="5" t="inlineStr">
-        <is>
-          <t>Time count: 9 down bars since the last up bar | Major pivot zone (2 touches, 1.9x vol) @ 112.16 | High-volume node @ 115.70 | Trendline (rising support) @ 115.23</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N89" s="6" t="inlineStr">
+      <c r="D89" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F89" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G89" s="7" t="n">
+        <v>278.65</v>
+      </c>
+      <c r="H89" s="7" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="I89" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="J89" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K89" s="7" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="L89" s="9" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 15 | Major pivot zone (1 touch, 2.0x vol) @ 281.06 | RSI overbought (78) | Tagged upper Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 1.7x average</t>
+        </is>
+      </c>
+      <c r="M89" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N89" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -5501,7 +5501,7 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>AON</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -5515,19 +5515,19 @@
         </is>
       </c>
       <c r="D90" s="8" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>119.98</v>
+        <v>321.66</v>
       </c>
       <c r="H90" s="7" t="n">
-        <v>1.3</v>
+        <v>1.88</v>
       </c>
       <c r="I90" s="7" t="n">
         <v>11</v>
@@ -5536,11 +5536,11 @@
         <v>3</v>
       </c>
       <c r="K90" s="7" t="n">
-        <v>74.2</v>
+        <v>69.5</v>
       </c>
       <c r="L90" s="9" t="inlineStr">
         <is>
-          <t>Time count: TD setup 10 | Prior pivot (2 touches, 0.9x vol) @ 119.91 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.2 ATR from 20 EMA</t>
+          <t>Time count: TD setup 10 | Fib 50.0% retrace @ 323.90 | Prior pivot (1 touch, 1.3x vol) @ 324.30 | Volume POC @ 320.45 | Tagged upper Bollinger band | Extended 3.4 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M90" s="7" t="inlineStr">
@@ -5557,7 +5557,7 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -5574,29 +5574,29 @@
         <v>0</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="F91" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G91" s="7" t="n">
+        <v>312.94</v>
+      </c>
+      <c r="H91" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J91" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G91" s="7" t="n">
-        <v>103.31</v>
-      </c>
-      <c r="H91" s="7" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="I91" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="J91" s="7" t="n">
-        <v>2</v>
-      </c>
       <c r="K91" s="7" t="n">
-        <v>76</v>
+        <v>71.8</v>
       </c>
       <c r="L91" s="9" t="inlineStr">
         <is>
-          <t>Time count: TD setup 12 | Prior pivot (1 touch, 1.0x vol) @ 103.78 | RSI overbought (76) | Tagged upper Bollinger band | Extended 3.1 ATR from 20 EMA</t>
+          <t>Time count: 7 bars without a lower low | Fib 78.6% retrace @ 314.31 | Prior pivot (1 touch, 0.7x vol) @ 313.73 | RSI overbought (72) | Tagged upper Bollinger band | Extended 2.6 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M91" s="7" t="inlineStr">
@@ -5613,7 +5613,7 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -5630,29 +5630,29 @@
         <v>0</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="F92" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G92" s="7" t="n">
+        <v>44.74</v>
+      </c>
+      <c r="H92" s="7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I92" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="J92" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G92" s="7" t="n">
-        <v>491.92</v>
-      </c>
-      <c r="H92" s="7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="I92" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="J92" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="K92" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="L92" s="9" t="inlineStr">
         <is>
-          <t>Time count: 13 up bars since the last down bar | Major pivot zone (2 touches, 1.8x vol) @ 492.74 | RSI overbought (73) | Extended 2.8 ATR from 20 EMA</t>
+          <t>Time count: TD setup 20 | Fib 61.8% retrace @ 44.89 | Major pivot zone (3 touches, 1.9x vol) @ 44.71 | RSI overbought (74) | Extended 3.2 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M92" s="7" t="inlineStr">
@@ -5667,336 +5667,336 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>FTNT</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>WEC</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C93" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F93" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G93" s="7" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="H93" s="7" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="I93" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" s="7" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="L93" s="9" t="inlineStr">
+        <is>
+          <t>Fib 78.6% retrace @ 114.79 | Major pivot zone (5 touches, 1.7x vol) @ 116.28 | RSI overbought (72) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 2.3x average</t>
+        </is>
+      </c>
+      <c r="M93" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N93" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>CNP</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C94" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F94" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G94" s="7" t="n">
+        <v>42.21</v>
+      </c>
+      <c r="H94" s="7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I94" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="J94" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" s="7" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="L94" s="9" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 20 | Prior pivot (2 touches, 1.1x vol) @ 42.24 | High-volume node @ 42.32 | RSI overbought (71) | Extended 3.2 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M94" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N94" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>DOV</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C95" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F95" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G95" s="7" t="n">
+        <v>210.37</v>
+      </c>
+      <c r="H95" s="7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I95" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J95" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K95" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="L95" s="9" t="inlineStr">
+        <is>
+          <t>Fib 50.0% retrace @ 208.52 | Major pivot zone (3 touches, 1.6x vol) @ 209.50 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.1 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M95" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N95" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>FDX</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C96" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F96" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G96" s="7" t="n">
+        <v>307.82</v>
+      </c>
+      <c r="H96" s="7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="I96" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="J96" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" s="7" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="L96" s="9" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 10 | Fib 50.0% retrace @ 310.98 | Prior pivot (1 touch, 1.4x vol) @ 312.88 | High-volume node @ 311.94 | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M96" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N96" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>URI</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C97" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F97" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G97" s="7" t="n">
+        <v>1198.19</v>
+      </c>
+      <c r="H97" s="7" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="I97" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J97" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K97" s="7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="L97" s="9" t="inlineStr">
+        <is>
+          <t>Time count: 7 up bars since the last down bar | Trendline (rising resistance) @ 1185.31 | RSI overbought (73) | Tagged upper Bollinger band | Extended 2.8 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M97" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N97" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>TPR</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="C93" s="13" t="inlineStr">
+      <c r="C98" s="13" t="inlineStr">
         <is>
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D93" s="4" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="E93" s="2" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="F93" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>135.83</v>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>-21.97</v>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="K93" s="2" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="L93" s="5" t="inlineStr">
-        <is>
-          <t>Fib 78.6% retrace @ 126.03 | Prior pivot (1 touch, 1.3x vol) @ 133.05 | RSI oversold (27) | Tagged lower Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 3.7x average</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N93" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>CAT</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C94" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D94" s="4" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="E94" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F94" s="2" t="n">
+      <c r="D98" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G94" s="2" t="n">
-        <v>643.77</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>-9.76</v>
-      </c>
-      <c r="I94" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J94" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K94" s="2" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="L94" s="5" t="inlineStr">
-        <is>
-          <t>Major pivot zone (2 touches, 1.8x vol) @ 619.81 | RSI oversold (26) | Tagged lower Bollinger band | Extended 3.5 ATR from 20 EMA | Volume 2.6x average</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N94" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>LII</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C95" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" s="2" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="F95" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>346.54</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J95" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K95" s="2" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="L95" s="5" t="inlineStr">
-        <is>
-          <t>Prior pivot (1 touch, 1.4x vol) @ 340.32 | Trendline (falling support) @ 319.68 | Bullish RSI divergence (42) | Tagged lower Bollinger band | Extended 2.6 ATR from 20 EMA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N95" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>RDDT</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C96" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D96" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="F96" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G96" s="2" t="n">
-        <v>128.54</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>-4.57</v>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>-7</v>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>-7</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="L96" s="5" t="inlineStr">
-        <is>
-          <t>Time count: 9 down bars since the last up bar | Prior pivot (2 touches, 1.7x vol) @ 128.64 | Tagged lower Bollinger band | Extended 2.7 ATR from 20 EMA | Volume 2.5x average</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N96" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>APP</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C97" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="E97" s="2" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="F97" s="2" t="n">
+      <c r="F98" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G97" s="2" t="n">
-        <v>254.93</v>
-      </c>
-      <c r="H97" s="2" t="n">
-        <v>-1.94</v>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>-7</v>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="K97" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="L97" s="5" t="inlineStr">
-        <is>
-          <t>Time count: 9 down bars since the last up bar | Trendline (falling support) @ 253.65 | Bullish RSI divergence (34) | Tagged lower Bollinger band</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N97" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="7" t="inlineStr">
-        <is>
-          <t>LLY</t>
-        </is>
-      </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
-        </is>
-      </c>
-      <c r="C98" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D98" s="8" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="E98" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F98" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G98" s="7" t="n">
-        <v>1372.84</v>
-      </c>
-      <c r="H98" s="7" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="I98" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J98" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K98" s="7" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="L98" s="9" t="inlineStr">
-        <is>
-          <t>Fib 1.27 extension @ 1424.82 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 1.6x average</t>
-        </is>
-      </c>
-      <c r="M98" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N98" s="10" t="inlineStr">
+      <c r="G98" s="2" t="n">
+        <v>117.8</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="L98" s="5" t="inlineStr">
+        <is>
+          <t>Time count: 9 down bars since the last up bar | Major pivot zone (2 touches, 1.9x vol) @ 112.16 | High-volume node @ 115.70 | Trendline (rising support) @ 115.23</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N98" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -6005,7 +6005,7 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>CRL</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
@@ -6019,32 +6019,32 @@
         </is>
       </c>
       <c r="D99" s="8" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>377.76</v>
+        <v>371.29</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>1.01</v>
+        <v>4.78</v>
       </c>
       <c r="I99" s="7" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J99" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K99" s="7" t="n">
-        <v>81</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="L99" s="9" t="inlineStr">
         <is>
-          <t>Time count: 8 up bars since the last down bar | RSI overbought (81) | Tagged upper Bollinger band | Extended 3.8 ATR from 20 EMA</t>
+          <t>Time count: TD setup 14 | Prior pivot (1 touch, 1.6x vol) @ 372.24 | RSI overbought (73) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M99" s="7" t="inlineStr">
@@ -6061,7 +6061,7 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>LYB</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
@@ -6075,152 +6075,152 @@
         </is>
       </c>
       <c r="D100" s="8" t="n">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="E100" s="7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F100" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G100" s="7" t="n">
+        <v>120.05</v>
+      </c>
+      <c r="H100" s="7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I100" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="J100" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K100" s="7" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="L100" s="9" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 10 | Prior pivot (2 touches, 0.9x vol) @ 119.91 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.2 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M100" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N100" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>SWK</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C101" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F101" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G101" s="7" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="H101" s="7" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="I101" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="J101" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K101" s="7" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="L101" s="9" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 12 | Prior pivot (1 touch, 1.0x vol) @ 103.78 | RSI overbought (76) | Tagged upper Bollinger band | Extended 3.1 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M101" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N101" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>MSI</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C102" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F102" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F100" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G100" s="7" t="n">
-        <v>65.06999999999999</v>
-      </c>
-      <c r="H100" s="7" t="n">
-        <v>-3.08</v>
-      </c>
-      <c r="I100" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J100" s="7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="K100" s="7" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="L100" s="9" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 19 | Fib 61.8% retrace @ 65.23 | Major pivot zone (3 touches, 1.6x vol) @ 67.19</t>
-        </is>
-      </c>
-      <c r="M100" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N100" s="10" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>BG</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C101" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>-3.37</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="K101" s="2" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="L101" s="5" t="inlineStr">
-        <is>
-          <t>Time count: 11 down bars since the last up bar | Prior pivot (2 touches, 1.0x vol) @ 95.80 | RSI oversold (29) | Tagged lower Bollinger band</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N101" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>ADM</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C102" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>76.26000000000001</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>-9</v>
-      </c>
-      <c r="J102" s="2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="K102" s="2" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="L102" s="5" t="inlineStr">
-        <is>
-          <t>Time count: 11 down bars since the last up bar | Major pivot zone (3 touches, 1.5x vol) @ 75.85 | Tagged lower Bollinger band</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N102" s="6" t="inlineStr">
+      <c r="G102" s="7" t="n">
+        <v>492.05</v>
+      </c>
+      <c r="H102" s="7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I102" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="J102" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K102" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="L102" s="9" t="inlineStr">
+        <is>
+          <t>Time count: 13 up bars since the last down bar | Major pivot zone (2 touches, 1.8x vol) @ 492.74 | RSI overbought (73) | Extended 2.9 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M102" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N102" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -6229,7 +6229,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -6243,32 +6243,32 @@
         </is>
       </c>
       <c r="D103" s="4" t="n">
-        <v>0.011</v>
+        <v>1</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>328.68</v>
+        <v>139.1</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>-2.03</v>
+        <v>-20.09</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>-2</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>43</v>
+        <v>27.6</v>
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>Fib 61.8% retrace @ 330.37 | Major pivot zone (6 touches, 3.1x vol) @ 327.50 | Volume POC @ 334.25</t>
+          <t>Fib 78.6% retrace @ 126.03 | Prior pivot (1 touch, 1.3x vol) @ 133.05 | RSI oversold (28) | Tagged lower Bollinger band | Extended 4.8 ATR from 20 EMA | Volume 4.3x average</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -6285,7 +6285,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -6299,32 +6299,32 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>0.721</v>
+        <v>0</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>627.34</v>
+        <v>95.98</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>2.42</v>
+        <v>-4.78</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>35.9</v>
+        <v>27</v>
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>Time count: 11 down bars since the last up bar | Fib 61.8% retrace @ 621.77 | High-volume node @ 620.94</t>
+          <t>Time count: 11 down bars since the last up bar | Prior pivot (2 touches, 1.0x vol) @ 95.80 | RSI oversold (27) | Tagged lower Bollinger band | Extended 2.5 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -6341,7 +6341,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -6355,32 +6355,32 @@
         </is>
       </c>
       <c r="D105" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>77.09</v>
+        <v>647.25</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>2.5</v>
+        <v>-9.27</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>50.7</v>
+        <v>26.6</v>
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>Fib 50.0% retrace @ 76.19 | Major pivot zone (3 touches, 1.0x vol) @ 75.26 | High-volume node @ 75.69</t>
+          <t>Major pivot zone (2 touches, 1.8x vol) @ 619.81 | RSI oversold (27) | Tagged lower Bollinger band | Extended 3.5 ATR from 20 EMA | Volume 2.7x average</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
@@ -6395,14 +6395,14 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="7" t="inlineStr">
-        <is>
-          <t>IRM</t>
-        </is>
-      </c>
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t>bearish</t>
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>LII</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
         </is>
       </c>
       <c r="C106" s="13" t="inlineStr">
@@ -6410,41 +6410,41 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D106" s="8" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E106" s="7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="F106" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G106" s="7" t="n">
-        <v>118.48</v>
-      </c>
-      <c r="H106" s="7" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="I106" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J106" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K106" s="7" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="L106" s="9" t="inlineStr">
-        <is>
-          <t>Fib 50.0% retrace @ 120.42 | Major pivot zone (7 touches, 1.6x vol) @ 118.99 | Tagged upper Bollinger band</t>
-        </is>
-      </c>
-      <c r="M106" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N106" s="10" t="inlineStr">
+      <c r="D106" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>348.15</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="L106" s="5" t="inlineStr">
+        <is>
+          <t>Prior pivot (1 touch, 1.4x vol) @ 340.32 | Trendline (falling support) @ 319.68 | Bullish RSI divergence (43) | Tagged lower Bollinger band | Extended 2.6 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N106" s="6" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -6453,7 +6453,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -6467,32 +6467,32 @@
         </is>
       </c>
       <c r="D107" s="4" t="n">
-        <v>0.364</v>
+        <v>0</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>3.25</v>
+        <v>4.25</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>61.92</v>
+        <v>254.91</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>-0.12</v>
+        <v>-1.95</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>30.1</v>
+        <v>34</v>
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>Time count: TD setup 9 | Trendline (falling support) @ 60.70 | Extended 3.0 ATR from 20 EMA</t>
+          <t>Time count: 9 down bars since the last up bar | Trendline (falling support) @ 253.65 | Bullish RSI divergence (34) | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
@@ -6507,14 +6507,14 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>TWLO</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
         </is>
       </c>
       <c r="C108" s="13" t="inlineStr">
@@ -6522,55 +6522,55 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D108" s="4" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="E108" s="2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="F108" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G108" s="2" t="n">
-        <v>238.13</v>
-      </c>
-      <c r="H108" s="2" t="n">
-        <v>-6.16</v>
-      </c>
-      <c r="I108" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J108" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="K108" s="2" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="L108" s="5" t="inlineStr">
-        <is>
-          <t>Fib 61.8% retrace @ 228.55 | Major pivot zone (3 touches, 1.4x vol) @ 238.69 | Tagged lower Bollinger band</t>
-        </is>
-      </c>
-      <c r="M108" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N108" s="6" t="inlineStr">
+      <c r="D108" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F108" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G108" s="7" t="n">
+        <v>1373</v>
+      </c>
+      <c r="H108" s="7" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="I108" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K108" s="7" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="L108" s="9" t="inlineStr">
+        <is>
+          <t>Fib 1.27 extension @ 1424.82 | RSI overbought (74) | Tagged upper Bollinger band | Extended 3.7 ATR from 20 EMA | Volume 1.6x average</t>
+        </is>
+      </c>
+      <c r="M108" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N108" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>VLO</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>NSC</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
         </is>
       </c>
       <c r="C109" s="13" t="inlineStr">
@@ -6578,41 +6578,41 @@
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D109" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E109" s="2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="F109" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G109" s="2" t="n">
-        <v>379.92</v>
-      </c>
-      <c r="H109" s="2" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="I109" s="2" t="n">
-        <v>-9</v>
-      </c>
-      <c r="J109" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K109" s="2" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="L109" s="5" t="inlineStr">
-        <is>
-          <t>Time count: TD setup 8 | Fib 38.2% retrace @ 373.38 | Tagged lower Bollinger band</t>
-        </is>
-      </c>
-      <c r="M109" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N109" s="6" t="inlineStr">
+      <c r="D109" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F109" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G109" s="7" t="n">
+        <v>342.19</v>
+      </c>
+      <c r="H109" s="7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="I109" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K109" s="7" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="L109" s="9" t="inlineStr">
+        <is>
+          <t>Major pivot zone (1 touch, 2.1x vol) @ 343.63 | Bearish RSI divergence (67) | Tagged upper Bollinger band | Extended 2.8 ATR from 20 EMA</t>
+        </is>
+      </c>
+      <c r="M109" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N109" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
@@ -6621,7 +6621,7 @@
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>ARES</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -6635,32 +6635,32 @@
         </is>
       </c>
       <c r="D110" s="8" t="n">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="E110" s="7" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="F110" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G110" s="7" t="n">
-        <v>126.85</v>
+        <v>1176.09</v>
       </c>
       <c r="H110" s="7" t="n">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="I110" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J110" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K110" s="7" t="n">
-        <v>62.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="L110" s="9" t="inlineStr">
         <is>
-          <t>Time count: 8 up bars since the last down bar | Prior pivot (2 touches, 1.3x vol) @ 129.72 | Tagged upper Bollinger band</t>
+          <t>Time count: 7 up bars since the last down bar | Prior pivot (2 touches, 1.0x vol) @ 1180.97 | Tagged upper Bollinger band | Extended 2.5 ATR from 20 EMA</t>
         </is>
       </c>
       <c r="M110" s="7" t="inlineStr">
@@ -6677,7 +6677,7 @@
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -6691,32 +6691,32 @@
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>0.386</v>
+        <v>0</v>
       </c>
       <c r="E111" s="7" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="F111" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>276.02</v>
+        <v>113.65</v>
       </c>
       <c r="H111" s="7" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="I111" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J111" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K111" s="7" t="n">
-        <v>63.6</v>
+        <v>59.7</v>
       </c>
       <c r="L111" s="9" t="inlineStr">
         <is>
-          <t>Time count: TD setup 8 | Prior pivot (1 touch, 1.0x vol) @ 281.07 | Tagged upper Bollinger band</t>
+          <t>Time count: 7 up bars since the last down bar | Major pivot zone (3 touches, 1.0x vol) @ 114.93 | Tagged upper Bollinger band</t>
         </is>
       </c>
       <c r="M111" s="7" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -6747,32 +6747,32 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="E112" s="2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F112" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F112" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="G112" s="2" t="n">
-        <v>280.67</v>
+        <v>76.19</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>-12.81</v>
+        <v>-1.35</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>21.7</v>
+        <v>32.6</v>
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>RSI oversold (22) | Tagged lower Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 4.9x average</t>
+          <t>Time count: 11 down bars since the last up bar | Major pivot zone (3 touches, 1.5x vol) @ 75.85 | Tagged lower Bollinger band</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
@@ -6789,285 +6789,1009 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C113" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="L113" s="5" t="inlineStr">
+        <is>
+          <t>Fib 38.2% retrace @ 83.44 | Major pivot zone (15 touches, 3.4x vol) @ 85.44 | High-volume node @ 82.23</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N113" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>KEYS</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C114" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>329.85</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="L114" s="5" t="inlineStr">
+        <is>
+          <t>Fib 61.8% retrace @ 330.37 | Major pivot zone (6 touches, 3.1x vol) @ 327.50 | Volume POC @ 334.25</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N114" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C115" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>624.52</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L115" s="5" t="inlineStr">
+        <is>
+          <t>Time count: 11 down bars since the last up bar | Fib 61.8% retrace @ 621.77 | High-volume node @ 620.94</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N115" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C116" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>76.94</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="L116" s="5" t="inlineStr">
+        <is>
+          <t>Fib 50.0% retrace @ 76.19 | Major pivot zone (3 touches, 1.0x vol) @ 75.26 | High-volume node @ 75.69</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N116" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>COF</t>
+        </is>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C117" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F117" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G117" s="7" t="n">
+        <v>208.78</v>
+      </c>
+      <c r="H117" s="7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I117" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J117" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K117" s="7" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="L117" s="9" t="inlineStr">
+        <is>
+          <t>Major pivot zone (8 touches, 1.8x vol) @ 210.88 | Trendline (falling resistance) @ 209.74 | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M117" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N117" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>VLO</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C118" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>384.77</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="L118" s="5" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 8 | Fib 38.2% retrace @ 373.38 | Tagged lower Bollinger band</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N118" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>ARES</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C119" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F119" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G119" s="7" t="n">
+        <v>127.45</v>
+      </c>
+      <c r="H119" s="7" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="I119" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J119" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K119" s="7" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="L119" s="9" t="inlineStr">
+        <is>
+          <t>Time count: 8 up bars since the last down bar | Prior pivot (2 touches, 1.3x vol) @ 129.72 | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M119" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N119" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>USB</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C120" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F120" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G120" s="7" t="n">
+        <v>60.65</v>
+      </c>
+      <c r="H120" s="7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I120" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K120" s="7" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="L120" s="9" t="inlineStr">
+        <is>
+          <t>Time count: 7 up bars since the last down bar | Prior pivot (1 touch, 0.8x vol) @ 60.89 | Tagged upper Bollinger band</t>
+        </is>
+      </c>
+      <c r="M120" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N120" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>LYB</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C121" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F121" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G121" s="7" t="n">
+        <v>65.37</v>
+      </c>
+      <c r="H121" s="7" t="n">
+        <v>-2.62</v>
+      </c>
+      <c r="I121" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J121" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K121" s="7" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="L121" s="9" t="inlineStr">
+        <is>
+          <t>Time count: TD setup 19 | Major pivot zone (3 touches, 1.6x vol) @ 67.19</t>
+        </is>
+      </c>
+      <c r="M121" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N121" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>FFIV</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C122" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>363.46</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="L122" s="5" t="inlineStr">
+        <is>
+          <t>RSI oversold (27) | Tagged lower Bollinger band | Extended 4.2 ATR from 20 EMA | Volume 2.8x average</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N122" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C123" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>282.32</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>-12.29</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="L123" s="5" t="inlineStr">
+        <is>
+          <t>RSI oversold (22) | Tagged lower Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 5.6x average</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N123" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>
       </c>
-      <c r="C113" s="13" t="inlineStr">
+      <c r="C124" s="13" t="inlineStr">
         <is>
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D113" s="4" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="E113" s="2" t="n">
+      <c r="D124" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F113" s="2" t="n">
+      <c r="F124" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G113" s="2" t="n">
-        <v>282.52</v>
-      </c>
-      <c r="H113" s="2" t="n">
-        <v>-13.04</v>
-      </c>
-      <c r="I113" s="2" t="n">
+      <c r="G124" s="2" t="n">
+        <v>283.82</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>-12.64</v>
+      </c>
+      <c r="I124" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="J113" s="2" t="n">
+      <c r="J124" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="K113" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="L113" s="5" t="inlineStr">
-        <is>
-          <t>RSI oversold (22) | Tagged lower Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 4.6x average</t>
-        </is>
-      </c>
-      <c r="M113" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N113" s="6" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="7" t="inlineStr">
+      <c r="K124" s="2" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="L124" s="5" t="inlineStr">
+        <is>
+          <t>RSI oversold (22) | Tagged lower Bollinger band | Extended 4.7 ATR from 20 EMA | Volume 5.2x average</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N124" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr">
         <is>
           <t>AZO</t>
         </is>
       </c>
-      <c r="B114" s="7" t="inlineStr">
+      <c r="B125" s="7" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>
       </c>
-      <c r="C114" s="13" t="inlineStr">
+      <c r="C125" s="13" t="inlineStr">
         <is>
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D114" s="8" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="E114" s="7" t="n">
+      <c r="D125" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="7" t="n">
         <v>2.5</v>
       </c>
-      <c r="F114" s="7" t="n">
+      <c r="F125" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G114" s="7" t="n">
-        <v>3145.11</v>
-      </c>
-      <c r="H114" s="7" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="I114" s="7" t="n">
+      <c r="G125" s="7" t="n">
+        <v>3138.41</v>
+      </c>
+      <c r="H125" s="7" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="I125" s="7" t="n">
         <v>-3</v>
       </c>
-      <c r="J114" s="7" t="n">
+      <c r="J125" s="7" t="n">
         <v>-1</v>
       </c>
-      <c r="K114" s="7" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="L114" s="9" t="inlineStr">
+      <c r="K125" s="7" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="L125" s="9" t="inlineStr">
         <is>
           <t>Fib 61.8% retrace @ 3243.91 | Major pivot zone (6 touches, 2.2x vol) @ 3190.97</t>
         </is>
       </c>
-      <c r="M114" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N114" s="10" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="7" t="inlineStr">
+      <c r="M125" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N125" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="C126" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D126" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F126" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G126" s="7" t="n">
+        <v>410.79</v>
+      </c>
+      <c r="H126" s="7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I126" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J126" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K126" s="7" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="L126" s="9" t="inlineStr">
+        <is>
+          <t>Fib 50.0% retrace @ 410.70 | Major pivot zone (2 touches, 2.0x vol) @ 411.73</t>
+        </is>
+      </c>
+      <c r="M126" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N126" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C127" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="L127" s="5" t="inlineStr">
+        <is>
+          <t>Fib 38.2% retrace @ 185.98 | Major pivot zone (10 touches, 2.3x vol) @ 180.72</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N127" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="inlineStr">
         <is>
           <t>CMI</t>
         </is>
       </c>
-      <c r="B115" s="7" t="inlineStr">
+      <c r="B128" s="7" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>
       </c>
-      <c r="C115" s="13" t="inlineStr">
+      <c r="C128" s="13" t="inlineStr">
         <is>
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D115" s="8" t="n">
-        <v>0.919</v>
-      </c>
-      <c r="E115" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F115" s="7" t="n">
+      <c r="D128" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" s="7" t="n">
+        <v>517.77</v>
+      </c>
+      <c r="H128" s="7" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="I128" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G115" s="7" t="n">
-        <v>515.16</v>
-      </c>
-      <c r="H115" s="7" t="n">
-        <v>-3.06</v>
-      </c>
-      <c r="I115" s="7" t="n">
+      <c r="J128" s="7" t="n">
         <v>-1</v>
       </c>
-      <c r="J115" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K115" s="7" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="L115" s="9" t="inlineStr">
-        <is>
-          <t>Topping tail, tail 67% of range | Volume POC @ 524.39</t>
-        </is>
-      </c>
-      <c r="M115" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N115" s="10" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="7" t="inlineStr">
-        <is>
-          <t>UNH</t>
-        </is>
-      </c>
-      <c r="B116" s="7" t="inlineStr">
+      <c r="K128" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="L128" s="9" t="inlineStr">
+        <is>
+          <t>Volume POC @ 524.39</t>
+        </is>
+      </c>
+      <c r="M128" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N128" s="10" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>PWR</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="C129" s="13" t="inlineStr">
+        <is>
+          <t>Signal faded</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>635.1799999999999</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="L129" s="5" t="inlineStr">
+        <is>
+          <t>Doji (indecision at extreme)</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N129" s="6" t="inlineStr">
+        <is>
+          <t>Open chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>TKO</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>
       </c>
-      <c r="C116" s="13" t="inlineStr">
+      <c r="C130" s="13" t="inlineStr">
         <is>
           <t>Signal faded</t>
         </is>
       </c>
-      <c r="D116" s="8" t="n">
-        <v>0.498</v>
-      </c>
-      <c r="E116" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F116" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G116" s="7" t="n">
-        <v>409.27</v>
-      </c>
-      <c r="H116" s="7" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="I116" s="7" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J116" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K116" s="7" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="L116" s="9" t="inlineStr">
-        <is>
-          <t>Fib 50.0% retrace @ 410.70 | Major pivot zone (2 touches, 2.0x vol) @ 411.73</t>
-        </is>
-      </c>
-      <c r="M116" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N116" s="10" t="inlineStr">
-        <is>
-          <t>Open chart</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>bullish</t>
-        </is>
-      </c>
-      <c r="C117" s="13" t="inlineStr">
-        <is>
-          <t>Signal faded</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="n">
-        <v>0.999</v>
-      </c>
-      <c r="E117" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F117" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G117" s="2" t="n">
-        <v>85.22</v>
-      </c>
-      <c r="H117" s="2" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="I117" s="2" t="n">
+      <c r="D130" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" s="7" t="n">
+        <v>178.77</v>
+      </c>
+      <c r="H130" s="7" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="I130" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J130" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="J117" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K117" s="2" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="L117" s="5" t="inlineStr">
-        <is>
-          <t>Fib 38.2% retrace @ 83.44 | High-volume node @ 82.23</t>
-        </is>
-      </c>
-      <c r="M117" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="N117" s="6" t="inlineStr">
+      <c r="K130" s="7" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="L130" s="9" t="inlineStr"/>
+      <c r="M130" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N130" s="10" t="inlineStr">
         <is>
           <t>Open chart</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N117"/>
+  <autoFilter ref="A1:N130"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -7185,6 +7909,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N115" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N116" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N130" r:id="rId129"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/reversal_signals.xlsx
+++ b/site/reversal_signals.xlsx
@@ -2544,7 +2544,7 @@
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>Topping tail forming at the high (tail 46% of range) | Time count 7: up bars since the last real down bar | RSI overbought (75)</t>
+          <t>Topping tail forming at the high (tail 47% of range) | Time count 7: up bars since the last real down bar | RSI overbought (75)</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3107,20 +3107,20 @@
         <v>65.12</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>65.84999999999999</v>
+        <v>65.84</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="M41" s="2" t="n">
         <v>59.3</v>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>Topping tail forming at the high (tail 61% of range) | Liquidity swept Major swing high @ 65.53</t>
+          <t>Topping tail forming at the high (tail 62% of range) | Liquidity swept Major swing high @ 65.53</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>Topping tail forming at the high (tail 50% of range) | Time count 1: up bars since the last real down bar | Liquidity swept Prior week's high @ 326.27</t>
+          <t>Topping tail forming at the high (tail 51% of range) | Time count 1: up bars since the last real down bar | Liquidity swept Prior week's high @ 326.27</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -3875,10 +3875,10 @@
         <v>196.42</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>189.59</v>
+        <v>189.6</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="L53" s="6" t="n">
         <v>3.18</v>
@@ -6633,7 +6633,7 @@
         <v>0.36</v>
       </c>
       <c r="L96" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="M96" s="2" t="n">
         <v>73.5</v>
